--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY111"/>
+  <dimension ref="A1:AY112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5706,10 +5706,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119851664</v>
+        <v>119850834</v>
       </c>
       <c r="B46" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5746,13 +5746,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>609125</v>
+        <v>609080</v>
       </c>
       <c r="R46" t="n">
-        <v>7062827</v>
+        <v>7062946</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119850321</v>
+        <v>119851664</v>
       </c>
       <c r="B47" t="n">
         <v>79607</v>
@@ -5848,13 +5848,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>609015</v>
+        <v>609125</v>
       </c>
       <c r="R47" t="n">
-        <v>7062798</v>
+        <v>7062827</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119851361</v>
+        <v>119850321</v>
       </c>
       <c r="B48" t="n">
         <v>79607</v>
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609100</v>
+        <v>609015</v>
       </c>
       <c r="R48" t="n">
-        <v>7062937</v>
+        <v>7062798</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6012,10 +6012,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119850834</v>
+        <v>119851361</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6028,21 +6028,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609080</v>
+        <v>609100</v>
       </c>
       <c r="R49" t="n">
-        <v>7062946</v>
+        <v>7062937</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6114,10 +6114,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119851274</v>
+        <v>119851251</v>
       </c>
       <c r="B50" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6130,39 +6130,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609039</v>
+        <v>609099</v>
       </c>
       <c r="R50" t="n">
-        <v>7062654</v>
+        <v>7062948</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6192,19 +6187,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6219,22 +6204,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119851329</v>
+        <v>119851421</v>
       </c>
       <c r="B51" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6243,25 +6228,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6271,13 +6256,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609091</v>
+        <v>609130</v>
       </c>
       <c r="R51" t="n">
-        <v>7062941</v>
+        <v>7062851</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6301,12 +6286,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6333,10 +6318,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119850436</v>
+        <v>119851684</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6345,25 +6330,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6373,10 +6358,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>609002</v>
+        <v>609149</v>
       </c>
       <c r="R52" t="n">
-        <v>7062810</v>
+        <v>7062828</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6435,10 +6420,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119851251</v>
+        <v>119851618</v>
       </c>
       <c r="B53" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6451,21 +6436,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6475,13 +6460,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>609099</v>
+        <v>609113</v>
       </c>
       <c r="R53" t="n">
-        <v>7062948</v>
+        <v>7062853</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6537,10 +6522,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119851421</v>
+        <v>119851274</v>
       </c>
       <c r="B54" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6553,37 +6538,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609130</v>
+        <v>609039</v>
       </c>
       <c r="R54" t="n">
-        <v>7062851</v>
+        <v>7062654</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6610,9 +6600,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6627,22 +6627,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119851684</v>
+        <v>119851329</v>
       </c>
       <c r="B55" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6651,25 +6651,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6679,13 +6679,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609149</v>
+        <v>609091</v>
       </c>
       <c r="R55" t="n">
-        <v>7062828</v>
+        <v>7062941</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6709,12 +6709,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6741,10 +6741,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119851618</v>
+        <v>119850436</v>
       </c>
       <c r="B56" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6753,25 +6753,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6781,10 +6781,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>609113</v>
+        <v>609002</v>
       </c>
       <c r="R56" t="n">
-        <v>7062853</v>
+        <v>7062810</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -7290,10 +7290,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119850096</v>
+        <v>119849724</v>
       </c>
       <c r="B61" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7302,42 +7302,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>608905</v>
+        <v>608908</v>
       </c>
       <c r="R61" t="n">
-        <v>7062586</v>
+        <v>7062658</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7369,7 +7365,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7379,7 +7375,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7508,10 +7504,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119849724</v>
+        <v>119850096</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7520,38 +7516,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>608908</v>
+        <v>608905</v>
       </c>
       <c r="R63" t="n">
-        <v>7062658</v>
+        <v>7062586</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7737,7 +7737,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119849952</v>
+        <v>119851732</v>
       </c>
       <c r="B65" t="n">
         <v>79607</v>
@@ -7777,13 +7777,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>608976</v>
+        <v>609149</v>
       </c>
       <c r="R65" t="n">
-        <v>7062742</v>
+        <v>7062808</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7839,7 +7839,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119851732</v>
+        <v>119849952</v>
       </c>
       <c r="B66" t="n">
         <v>79607</v>
@@ -7879,13 +7879,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609149</v>
+        <v>608976</v>
       </c>
       <c r="R66" t="n">
-        <v>7062808</v>
+        <v>7062742</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8471,10 +8471,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119851641</v>
+        <v>119849740</v>
       </c>
       <c r="B72" t="n">
-        <v>79643</v>
+        <v>97907</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8483,41 +8483,45 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>609109</v>
+        <v>608907</v>
       </c>
       <c r="R72" t="n">
-        <v>7062833</v>
+        <v>7062655</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8544,9 +8548,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8561,22 +8575,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119849740</v>
+        <v>119851641</v>
       </c>
       <c r="B73" t="n">
-        <v>97907</v>
+        <v>79643</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8585,45 +8599,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>608907</v>
+        <v>609109</v>
       </c>
       <c r="R73" t="n">
-        <v>7062655</v>
+        <v>7062833</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8650,19 +8660,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8677,22 +8677,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119849966</v>
+        <v>119849903</v>
       </c>
       <c r="B74" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8701,42 +8701,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>608853</v>
+        <v>608950</v>
       </c>
       <c r="R74" t="n">
-        <v>7062579</v>
+        <v>7062709</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8766,19 +8762,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8793,12 +8779,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8922,10 +8908,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119849903</v>
+        <v>119849973</v>
       </c>
       <c r="B76" t="n">
-        <v>90562</v>
+        <v>79636</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8934,25 +8920,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8962,13 +8948,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>608950</v>
+        <v>608986</v>
       </c>
       <c r="R76" t="n">
-        <v>7062709</v>
+        <v>7062749</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9024,10 +9010,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119849973</v>
+        <v>119849966</v>
       </c>
       <c r="B77" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9036,41 +9022,45 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>608986</v>
+        <v>608853</v>
       </c>
       <c r="R77" t="n">
-        <v>7062749</v>
+        <v>7062579</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9097,9 +9087,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9114,12 +9114,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -11152,10 +11152,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119851878</v>
+        <v>119851502</v>
       </c>
       <c r="B97" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11164,25 +11164,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11192,13 +11192,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>609153</v>
+        <v>609140</v>
       </c>
       <c r="R97" t="n">
-        <v>7062778</v>
+        <v>7062863</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11254,7 +11254,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119851502</v>
+        <v>119850411</v>
       </c>
       <c r="B98" t="n">
         <v>97907</v>
@@ -11294,13 +11294,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>609140</v>
+        <v>609003</v>
       </c>
       <c r="R98" t="n">
-        <v>7062863</v>
+        <v>7062803</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11356,7 +11356,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119850411</v>
+        <v>119851047</v>
       </c>
       <c r="B99" t="n">
         <v>97907</v>
@@ -11389,17 +11389,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>609003</v>
+        <v>609018</v>
       </c>
       <c r="R99" t="n">
-        <v>7062803</v>
+        <v>7062666</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11429,9 +11433,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11446,22 +11460,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119851047</v>
+        <v>119851878</v>
       </c>
       <c r="B100" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11470,42 +11484,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>609018</v>
+        <v>609153</v>
       </c>
       <c r="R100" t="n">
-        <v>7062666</v>
+        <v>7062778</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11535,19 +11545,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11562,22 +11562,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119850006</v>
+        <v>119850519</v>
       </c>
       <c r="B101" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11586,25 +11586,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11614,13 +11614,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>609003</v>
+        <v>609012</v>
       </c>
       <c r="R101" t="n">
-        <v>7062728</v>
+        <v>7062828</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119850519</v>
+        <v>119850720</v>
       </c>
       <c r="B102" t="n">
         <v>97907</v>
@@ -11709,17 +11709,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>609012</v>
+        <v>608957</v>
       </c>
       <c r="R102" t="n">
-        <v>7062828</v>
+        <v>7062678</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11749,9 +11753,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11766,19 +11780,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119850720</v>
+        <v>119851185</v>
       </c>
       <c r="B103" t="n">
         <v>97907</v>
@@ -11811,24 +11825,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>608957</v>
+        <v>609097</v>
       </c>
       <c r="R103" t="n">
-        <v>7062678</v>
+        <v>7062964</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11852,22 +11862,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11882,22 +11882,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119851185</v>
+        <v>119850006</v>
       </c>
       <c r="B104" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11906,25 +11906,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11934,10 +11934,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>609097</v>
+        <v>609003</v>
       </c>
       <c r="R104" t="n">
-        <v>7062964</v>
+        <v>7062728</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11964,12 +11964,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12723,6 +12723,122 @@
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>120091070</v>
+      </c>
+      <c r="B112" t="n">
+        <v>95775</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1841</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Vedflikmossa</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Lophozia guttulata</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>609206</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7062811</v>
+      </c>
+      <c r="S112" t="n">
+        <v>59</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-09-28</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Martin Bergström</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Martin Bergström</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -5706,10 +5706,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119850834</v>
+        <v>119851664</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5722,21 +5722,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5746,13 +5746,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>609080</v>
+        <v>609125</v>
       </c>
       <c r="R46" t="n">
-        <v>7062946</v>
+        <v>7062827</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119851664</v>
+        <v>119850321</v>
       </c>
       <c r="B47" t="n">
         <v>79607</v>
@@ -5848,13 +5848,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>609125</v>
+        <v>609015</v>
       </c>
       <c r="R47" t="n">
-        <v>7062827</v>
+        <v>7062798</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119850321</v>
+        <v>119851361</v>
       </c>
       <c r="B48" t="n">
         <v>79607</v>
@@ -5950,10 +5950,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609015</v>
+        <v>609100</v>
       </c>
       <c r="R48" t="n">
-        <v>7062798</v>
+        <v>7062937</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6012,10 +6012,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119851361</v>
+        <v>119850834</v>
       </c>
       <c r="B49" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6028,21 +6028,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6052,10 +6052,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609100</v>
+        <v>609080</v>
       </c>
       <c r="R49" t="n">
-        <v>7062937</v>
+        <v>7062946</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7737,7 +7737,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119851732</v>
+        <v>119849952</v>
       </c>
       <c r="B65" t="n">
         <v>79607</v>
@@ -7777,13 +7777,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609149</v>
+        <v>608976</v>
       </c>
       <c r="R65" t="n">
-        <v>7062808</v>
+        <v>7062742</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7839,7 +7839,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119849952</v>
+        <v>119851732</v>
       </c>
       <c r="B66" t="n">
         <v>79607</v>
@@ -7879,13 +7879,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>608976</v>
+        <v>609149</v>
       </c>
       <c r="R66" t="n">
-        <v>7062742</v>
+        <v>7062808</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7909,12 +7909,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8689,10 +8689,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119849903</v>
+        <v>119849966</v>
       </c>
       <c r="B74" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8701,38 +8701,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>608950</v>
+        <v>608853</v>
       </c>
       <c r="R74" t="n">
-        <v>7062709</v>
+        <v>7062579</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8762,9 +8766,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8779,12 +8793,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8908,10 +8922,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119849973</v>
+        <v>119849903</v>
       </c>
       <c r="B76" t="n">
-        <v>79636</v>
+        <v>90562</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8920,25 +8934,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8948,13 +8962,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>608986</v>
+        <v>608950</v>
       </c>
       <c r="R76" t="n">
-        <v>7062749</v>
+        <v>7062709</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9010,10 +9024,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119849966</v>
+        <v>119849973</v>
       </c>
       <c r="B77" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9022,45 +9036,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>608853</v>
+        <v>608986</v>
       </c>
       <c r="R77" t="n">
-        <v>7062579</v>
+        <v>7062749</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9087,19 +9097,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9114,12 +9114,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -10948,10 +10948,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119849829</v>
+        <v>119852025</v>
       </c>
       <c r="B95" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10964,21 +10964,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10988,10 +10988,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>608941</v>
+        <v>609136</v>
       </c>
       <c r="R95" t="n">
-        <v>7062708</v>
+        <v>7062753</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11050,10 +11050,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119852025</v>
+        <v>119849829</v>
       </c>
       <c r="B96" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11066,21 +11066,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11090,10 +11090,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>609136</v>
+        <v>608941</v>
       </c>
       <c r="R96" t="n">
-        <v>7062753</v>
+        <v>7062708</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11574,10 +11574,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119850519</v>
+        <v>119850006</v>
       </c>
       <c r="B101" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11586,25 +11586,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11614,13 +11614,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>609012</v>
+        <v>609003</v>
       </c>
       <c r="R101" t="n">
-        <v>7062828</v>
+        <v>7062728</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119850720</v>
+        <v>119850519</v>
       </c>
       <c r="B102" t="n">
         <v>97907</v>
@@ -11709,21 +11709,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>608957</v>
+        <v>609012</v>
       </c>
       <c r="R102" t="n">
-        <v>7062678</v>
+        <v>7062828</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11753,19 +11749,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11780,19 +11766,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119851185</v>
+        <v>119850720</v>
       </c>
       <c r="B103" t="n">
         <v>97907</v>
@@ -11825,20 +11811,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>609097</v>
+        <v>608957</v>
       </c>
       <c r="R103" t="n">
-        <v>7062964</v>
+        <v>7062678</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11862,12 +11852,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11882,22 +11882,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119850006</v>
+        <v>119851185</v>
       </c>
       <c r="B104" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11906,25 +11906,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11934,10 +11934,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>609003</v>
+        <v>609097</v>
       </c>
       <c r="R104" t="n">
-        <v>7062728</v>
+        <v>7062964</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11964,12 +11964,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD104" t="b">

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -5390,10 +5390,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119850656</v>
+        <v>119851618</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5402,25 +5402,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5430,13 +5430,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>609048</v>
+        <v>609113</v>
       </c>
       <c r="R43" t="n">
-        <v>7062921</v>
+        <v>7062853</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119850955</v>
+        <v>119849721</v>
       </c>
       <c r="B44" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5508,21 +5508,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5532,10 +5532,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>609006</v>
+        <v>608918</v>
       </c>
       <c r="R44" t="n">
-        <v>7062681</v>
+        <v>7062673</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5565,19 +5565,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5592,22 +5582,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119849721</v>
+        <v>119852068</v>
       </c>
       <c r="B45" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5620,21 +5610,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5644,10 +5634,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>608918</v>
+        <v>609119</v>
       </c>
       <c r="R45" t="n">
-        <v>7062673</v>
+        <v>7062737</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5706,10 +5696,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119851664</v>
+        <v>119850188</v>
       </c>
       <c r="B46" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5718,25 +5708,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5746,13 +5736,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>609125</v>
+        <v>608997</v>
       </c>
       <c r="R46" t="n">
-        <v>7062827</v>
+        <v>7062738</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5808,10 +5798,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119850321</v>
+        <v>119850115</v>
       </c>
       <c r="B47" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5820,25 +5810,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5848,10 +5838,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>609015</v>
+        <v>609002</v>
       </c>
       <c r="R47" t="n">
-        <v>7062798</v>
+        <v>7062743</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5910,10 +5900,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119851361</v>
+        <v>119851047</v>
       </c>
       <c r="B48" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5922,41 +5912,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609100</v>
+        <v>609018</v>
       </c>
       <c r="R48" t="n">
-        <v>7062937</v>
+        <v>7062666</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5980,12 +5974,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6000,22 +6004,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119850834</v>
+        <v>119850568</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6024,25 +6028,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6052,13 +6056,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609080</v>
+        <v>609033</v>
       </c>
       <c r="R49" t="n">
-        <v>7062946</v>
+        <v>7062884</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6114,10 +6118,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119851251</v>
+        <v>119850955</v>
       </c>
       <c r="B50" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6130,21 +6134,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6154,10 +6158,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609099</v>
+        <v>609006</v>
       </c>
       <c r="R50" t="n">
-        <v>7062948</v>
+        <v>7062681</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6187,9 +6191,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6204,19 +6218,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119851421</v>
+        <v>119850321</v>
       </c>
       <c r="B51" t="n">
         <v>79607</v>
@@ -6256,10 +6270,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609130</v>
+        <v>609015</v>
       </c>
       <c r="R51" t="n">
-        <v>7062851</v>
+        <v>7062798</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6420,10 +6434,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119851618</v>
+        <v>119849708</v>
       </c>
       <c r="B53" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6436,21 +6450,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6460,13 +6474,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>609113</v>
+        <v>608910</v>
       </c>
       <c r="R53" t="n">
-        <v>7062853</v>
+        <v>7062662</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6522,7 +6536,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119851274</v>
+        <v>119851413</v>
       </c>
       <c r="B54" t="n">
         <v>57310</v>
@@ -6567,10 +6581,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609039</v>
+        <v>609070</v>
       </c>
       <c r="R54" t="n">
-        <v>7062654</v>
+        <v>7062653</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6602,7 +6616,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6612,7 +6626,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6639,10 +6653,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119851329</v>
+        <v>119849903</v>
       </c>
       <c r="B55" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6651,25 +6665,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6679,10 +6693,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609091</v>
+        <v>608950</v>
       </c>
       <c r="R55" t="n">
-        <v>7062941</v>
+        <v>7062709</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6709,12 +6723,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6741,7 +6755,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119850436</v>
+        <v>119850656</v>
       </c>
       <c r="B56" t="n">
         <v>97907</v>
@@ -6781,13 +6795,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>609002</v>
+        <v>609048</v>
       </c>
       <c r="R56" t="n">
-        <v>7062810</v>
+        <v>7062921</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6843,10 +6857,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119849717</v>
+        <v>119851329</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6855,25 +6869,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6883,10 +6897,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>608896</v>
+        <v>609091</v>
       </c>
       <c r="R57" t="n">
-        <v>7062656</v>
+        <v>7062941</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6913,27 +6927,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:18</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6948,22 +6947,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119849858</v>
+        <v>119851973</v>
       </c>
       <c r="B58" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6972,42 +6971,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>608877</v>
+        <v>609151</v>
       </c>
       <c r="R58" t="n">
-        <v>7062639</v>
+        <v>7062747</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7037,19 +7032,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7064,19 +7049,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119851290</v>
+        <v>119849952</v>
       </c>
       <c r="B59" t="n">
         <v>79607</v>
@@ -7116,13 +7101,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>609054</v>
+        <v>608976</v>
       </c>
       <c r="R59" t="n">
-        <v>7062684</v>
+        <v>7062742</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7146,22 +7131,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7176,19 +7151,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119851235</v>
+        <v>119850782</v>
       </c>
       <c r="B60" t="n">
         <v>97907</v>
@@ -7221,20 +7196,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>609101</v>
+        <v>608954</v>
       </c>
       <c r="R60" t="n">
-        <v>7062955</v>
+        <v>7062685</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7261,9 +7240,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7278,22 +7267,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119849724</v>
+        <v>119849658</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7306,34 +7295,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>608908</v>
+        <v>608890</v>
       </c>
       <c r="R61" t="n">
-        <v>7062658</v>
+        <v>7062664</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7365,7 +7359,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7375,7 +7369,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7402,10 +7396,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119851993</v>
+        <v>119850926</v>
       </c>
       <c r="B62" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7418,34 +7412,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609135</v>
+        <v>609003</v>
       </c>
       <c r="R62" t="n">
-        <v>7062752</v>
+        <v>7062700</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7475,9 +7474,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7492,22 +7501,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119850096</v>
+        <v>119849755</v>
       </c>
       <c r="B63" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7516,45 +7525,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>608905</v>
+        <v>608914</v>
       </c>
       <c r="R63" t="n">
-        <v>7062586</v>
+        <v>7062689</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7581,19 +7586,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7608,22 +7603,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119851413</v>
+        <v>119850720</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7632,31 +7627,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7665,10 +7659,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609070</v>
+        <v>608957</v>
       </c>
       <c r="R64" t="n">
-        <v>7062653</v>
+        <v>7062678</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7700,7 +7694,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7710,7 +7704,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7737,10 +7731,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119849952</v>
+        <v>119851185</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7749,25 +7743,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7777,10 +7771,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>608976</v>
+        <v>609097</v>
       </c>
       <c r="R65" t="n">
-        <v>7062742</v>
+        <v>7062964</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7807,12 +7801,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7839,10 +7833,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119851732</v>
+        <v>119851502</v>
       </c>
       <c r="B66" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7851,25 +7845,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7879,13 +7873,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609149</v>
+        <v>609140</v>
       </c>
       <c r="R66" t="n">
-        <v>7062808</v>
+        <v>7062863</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7941,10 +7935,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119851861</v>
+        <v>119851104</v>
       </c>
       <c r="B67" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7957,21 +7951,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7981,13 +7975,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>609153</v>
+        <v>609085</v>
       </c>
       <c r="R67" t="n">
-        <v>7062783</v>
+        <v>7062996</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8017,6 +8011,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8043,10 +8042,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119850115</v>
+        <v>119850850</v>
       </c>
       <c r="B68" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8055,25 +8054,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8083,13 +8082,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>609002</v>
+        <v>609076</v>
       </c>
       <c r="R68" t="n">
-        <v>7062743</v>
+        <v>7062968</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8145,10 +8144,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119849905</v>
+        <v>119851732</v>
       </c>
       <c r="B69" t="n">
-        <v>90582</v>
+        <v>79607</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8161,21 +8160,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8185,10 +8184,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>608876</v>
+        <v>609149</v>
       </c>
       <c r="R69" t="n">
-        <v>7062635</v>
+        <v>7062808</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8218,19 +8217,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8245,22 +8234,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119849742</v>
+        <v>119851878</v>
       </c>
       <c r="B70" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8273,21 +8262,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8297,13 +8286,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>608916</v>
+        <v>609153</v>
       </c>
       <c r="R70" t="n">
-        <v>7062680</v>
+        <v>7062778</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8359,10 +8348,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119850562</v>
+        <v>119851928</v>
       </c>
       <c r="B71" t="n">
-        <v>91128</v>
+        <v>79607</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8371,25 +8360,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8399,10 +8388,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>608992</v>
+        <v>609172</v>
       </c>
       <c r="R71" t="n">
-        <v>7062626</v>
+        <v>7062778</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8432,19 +8421,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8459,22 +8438,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119849740</v>
+        <v>119850459</v>
       </c>
       <c r="B72" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8483,30 +8462,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8515,10 +8495,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>608907</v>
+        <v>608949</v>
       </c>
       <c r="R72" t="n">
-        <v>7062655</v>
+        <v>7062585</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8550,7 +8530,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8560,7 +8540,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8587,10 +8567,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119851641</v>
+        <v>119850220</v>
       </c>
       <c r="B73" t="n">
-        <v>79643</v>
+        <v>90562</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8599,25 +8579,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8627,13 +8607,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>609109</v>
+        <v>608994</v>
       </c>
       <c r="R73" t="n">
-        <v>7062833</v>
+        <v>7062775</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8657,12 +8637,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8689,10 +8669,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119849966</v>
+        <v>119851421</v>
       </c>
       <c r="B74" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8701,45 +8681,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>608853</v>
+        <v>609130</v>
       </c>
       <c r="R74" t="n">
-        <v>7062579</v>
+        <v>7062851</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8766,19 +8742,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8793,22 +8759,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119849658</v>
+        <v>119851377</v>
       </c>
       <c r="B75" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8821,39 +8787,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>608890</v>
+        <v>609065</v>
       </c>
       <c r="R75" t="n">
-        <v>7062664</v>
+        <v>7062657</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8885,7 +8846,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8895,7 +8856,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8922,10 +8883,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119849903</v>
+        <v>119849717</v>
       </c>
       <c r="B76" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8938,21 +8899,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8962,10 +8923,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>608950</v>
+        <v>608896</v>
       </c>
       <c r="R76" t="n">
-        <v>7062709</v>
+        <v>7062656</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8995,9 +8956,24 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9012,22 +8988,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119849973</v>
+        <v>119850876</v>
       </c>
       <c r="B77" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9036,25 +9012,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9064,13 +9040,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>608986</v>
+        <v>609066</v>
       </c>
       <c r="R77" t="n">
-        <v>7062749</v>
+        <v>7062980</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9126,10 +9102,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119850876</v>
+        <v>119850006</v>
       </c>
       <c r="B78" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9142,21 +9118,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9166,13 +9142,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>609066</v>
+        <v>609003</v>
       </c>
       <c r="R78" t="n">
-        <v>7062980</v>
+        <v>7062728</v>
       </c>
       <c r="S78" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9228,10 +9204,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119851377</v>
+        <v>119851235</v>
       </c>
       <c r="B79" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9240,25 +9216,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9268,13 +9244,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>609065</v>
+        <v>609101</v>
       </c>
       <c r="R79" t="n">
-        <v>7062657</v>
+        <v>7062955</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9301,19 +9277,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9328,19 +9294,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119851306</v>
+        <v>119850411</v>
       </c>
       <c r="B80" t="n">
         <v>97907</v>
@@ -9373,21 +9339,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>609039</v>
+        <v>609003</v>
       </c>
       <c r="R80" t="n">
-        <v>7062664</v>
+        <v>7062803</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9417,19 +9379,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9444,22 +9396,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119850459</v>
+        <v>119849829</v>
       </c>
       <c r="B81" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9472,39 +9424,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>608949</v>
+        <v>608941</v>
       </c>
       <c r="R81" t="n">
-        <v>7062585</v>
+        <v>7062708</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9534,19 +9481,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9561,22 +9498,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119850926</v>
+        <v>119850562</v>
       </c>
       <c r="B82" t="n">
-        <v>57310</v>
+        <v>91128</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9585,43 +9522,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>609003</v>
+        <v>608992</v>
       </c>
       <c r="R82" t="n">
-        <v>7062700</v>
+        <v>7062626</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9653,7 +9585,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9663,7 +9595,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9690,10 +9622,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119850782</v>
+        <v>119851290</v>
       </c>
       <c r="B83" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9702,42 +9634,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>608954</v>
+        <v>609054</v>
       </c>
       <c r="R83" t="n">
-        <v>7062685</v>
+        <v>7062684</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9769,7 +9697,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9779,7 +9707,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9806,10 +9734,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119851802</v>
+        <v>119849973</v>
       </c>
       <c r="B84" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9818,25 +9746,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9846,13 +9774,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>609143</v>
+        <v>608986</v>
       </c>
       <c r="R84" t="n">
-        <v>7062799</v>
+        <v>7062749</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9908,10 +9836,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119849971</v>
+        <v>119849724</v>
       </c>
       <c r="B85" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9924,21 +9852,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9948,10 +9876,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>608977</v>
+        <v>608908</v>
       </c>
       <c r="R85" t="n">
-        <v>7062755</v>
+        <v>7062658</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9981,9 +9909,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9998,22 +9936,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119850220</v>
+        <v>119851664</v>
       </c>
       <c r="B86" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10026,21 +9964,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10050,10 +9988,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>608994</v>
+        <v>609125</v>
       </c>
       <c r="R86" t="n">
-        <v>7062775</v>
+        <v>7062827</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10080,12 +10018,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10112,10 +10050,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119851428</v>
+        <v>119851695</v>
       </c>
       <c r="B87" t="n">
-        <v>79643</v>
+        <v>57463</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10124,41 +10062,46 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>609133</v>
+        <v>609150</v>
       </c>
       <c r="R87" t="n">
-        <v>7062851</v>
+        <v>7062808</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10214,10 +10157,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119851160</v>
+        <v>119849740</v>
       </c>
       <c r="B88" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10226,31 +10169,30 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10259,10 +10201,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>609023</v>
+        <v>608907</v>
       </c>
       <c r="R88" t="n">
-        <v>7062674</v>
+        <v>7062655</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10294,7 +10236,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10304,7 +10246,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10331,10 +10273,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119852068</v>
+        <v>119849966</v>
       </c>
       <c r="B89" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10343,38 +10285,42 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>609119</v>
+        <v>608853</v>
       </c>
       <c r="R89" t="n">
-        <v>7062737</v>
+        <v>7062579</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10404,9 +10350,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10421,22 +10377,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119851928</v>
+        <v>119850096</v>
       </c>
       <c r="B90" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10445,38 +10401,42 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>609172</v>
+        <v>608905</v>
       </c>
       <c r="R90" t="n">
-        <v>7062778</v>
+        <v>7062586</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10506,9 +10466,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10523,22 +10493,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119851973</v>
+        <v>119850752</v>
       </c>
       <c r="B91" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10547,25 +10517,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10575,10 +10545,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>609151</v>
+        <v>609068</v>
       </c>
       <c r="R91" t="n">
-        <v>7062747</v>
+        <v>7062927</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10605,12 +10575,17 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10637,7 +10612,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119850752</v>
+        <v>119849858</v>
       </c>
       <c r="B92" t="n">
         <v>97907</v>
@@ -10670,17 +10645,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>609068</v>
+        <v>608877</v>
       </c>
       <c r="R92" t="n">
-        <v>7062927</v>
+        <v>7062639</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10707,17 +10686,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10732,22 +10716,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119849708</v>
+        <v>119849630</v>
       </c>
       <c r="B93" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10760,21 +10744,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10784,13 +10768,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>608910</v>
+        <v>608895</v>
       </c>
       <c r="R93" t="n">
-        <v>7062662</v>
+        <v>7062683</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10820,6 +10804,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10846,10 +10835,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119850188</v>
+        <v>119851251</v>
       </c>
       <c r="B94" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10858,25 +10847,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10886,13 +10875,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>608997</v>
+        <v>609099</v>
       </c>
       <c r="R94" t="n">
-        <v>7062738</v>
+        <v>7062948</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10948,10 +10937,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119852025</v>
+        <v>119851160</v>
       </c>
       <c r="B95" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10964,34 +10953,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>609136</v>
+        <v>609023</v>
       </c>
       <c r="R95" t="n">
-        <v>7062753</v>
+        <v>7062674</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11021,9 +11015,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11038,22 +11042,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119849829</v>
+        <v>119850519</v>
       </c>
       <c r="B96" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11062,25 +11066,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11090,10 +11094,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>608941</v>
+        <v>609012</v>
       </c>
       <c r="R96" t="n">
-        <v>7062708</v>
+        <v>7062828</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11152,10 +11156,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119851502</v>
+        <v>119851861</v>
       </c>
       <c r="B97" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11164,25 +11168,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11192,10 +11196,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>609140</v>
+        <v>609153</v>
       </c>
       <c r="R97" t="n">
-        <v>7062863</v>
+        <v>7062783</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -11254,10 +11258,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119850411</v>
+        <v>119849905</v>
       </c>
       <c r="B98" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11266,25 +11270,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11294,10 +11298,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>609003</v>
+        <v>608876</v>
       </c>
       <c r="R98" t="n">
-        <v>7062803</v>
+        <v>7062635</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11327,9 +11331,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11344,22 +11358,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119851047</v>
+        <v>119849971</v>
       </c>
       <c r="B99" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11368,42 +11382,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>609018</v>
+        <v>608977</v>
       </c>
       <c r="R99" t="n">
-        <v>7062666</v>
+        <v>7062755</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11433,19 +11443,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11460,22 +11460,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119851878</v>
+        <v>119851428</v>
       </c>
       <c r="B100" t="n">
-        <v>79607</v>
+        <v>79643</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11484,25 +11484,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11512,13 +11512,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>609153</v>
+        <v>609133</v>
       </c>
       <c r="R100" t="n">
-        <v>7062778</v>
+        <v>7062851</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11574,10 +11574,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119850006</v>
+        <v>119849742</v>
       </c>
       <c r="B101" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11590,21 +11590,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11614,10 +11614,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>609003</v>
+        <v>608916</v>
       </c>
       <c r="R101" t="n">
-        <v>7062728</v>
+        <v>7062680</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11676,10 +11676,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119850519</v>
+        <v>119851641</v>
       </c>
       <c r="B102" t="n">
-        <v>97907</v>
+        <v>79643</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11688,25 +11688,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11716,13 +11716,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>609012</v>
+        <v>609109</v>
       </c>
       <c r="R102" t="n">
-        <v>7062828</v>
+        <v>7062833</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11778,10 +11778,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119850720</v>
+        <v>119850834</v>
       </c>
       <c r="B103" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11790,45 +11790,41 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>608957</v>
+        <v>609080</v>
       </c>
       <c r="R103" t="n">
-        <v>7062678</v>
+        <v>7062946</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11855,19 +11851,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11882,19 +11868,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119851185</v>
+        <v>119851306</v>
       </c>
       <c r="B104" t="n">
         <v>97907</v>
@@ -11927,20 +11913,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>609097</v>
+        <v>609039</v>
       </c>
       <c r="R104" t="n">
-        <v>7062964</v>
+        <v>7062664</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11964,12 +11954,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11984,22 +11984,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119851695</v>
+        <v>119850436</v>
       </c>
       <c r="B105" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12008,46 +12008,41 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>609150</v>
+        <v>609002</v>
       </c>
       <c r="R105" t="n">
-        <v>7062808</v>
+        <v>7062810</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12103,7 +12098,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119851950</v>
+        <v>119851361</v>
       </c>
       <c r="B106" t="n">
         <v>79607</v>
@@ -12143,10 +12138,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>609160</v>
+        <v>609100</v>
       </c>
       <c r="R106" t="n">
-        <v>7062762</v>
+        <v>7062937</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -12173,12 +12168,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12205,7 +12200,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119850850</v>
+        <v>119852025</v>
       </c>
       <c r="B107" t="n">
         <v>79607</v>
@@ -12245,10 +12240,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>609076</v>
+        <v>609136</v>
       </c>
       <c r="R107" t="n">
-        <v>7062968</v>
+        <v>7062753</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12307,10 +12302,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119849755</v>
+        <v>119851993</v>
       </c>
       <c r="B108" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12323,21 +12318,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12347,13 +12342,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>608914</v>
+        <v>609135</v>
       </c>
       <c r="R108" t="n">
-        <v>7062689</v>
+        <v>7062752</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12409,10 +12404,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119851104</v>
+        <v>119851802</v>
       </c>
       <c r="B109" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12425,21 +12420,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12449,13 +12444,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>609085</v>
+        <v>609143</v>
       </c>
       <c r="R109" t="n">
-        <v>7062996</v>
+        <v>7062799</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12485,11 +12480,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12516,10 +12506,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119849630</v>
+        <v>119851950</v>
       </c>
       <c r="B110" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12532,21 +12522,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12556,13 +12546,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>608895</v>
+        <v>609160</v>
       </c>
       <c r="R110" t="n">
-        <v>7062683</v>
+        <v>7062762</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12592,11 +12582,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12623,10 +12608,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119850568</v>
+        <v>119851274</v>
       </c>
       <c r="B111" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12635,38 +12620,43 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>609033</v>
+        <v>609039</v>
       </c>
       <c r="R111" t="n">
-        <v>7062884</v>
+        <v>7062654</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12696,9 +12686,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12713,12 +12713,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -8669,10 +8669,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119851421</v>
+        <v>119850876</v>
       </c>
       <c r="B74" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8685,21 +8685,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8709,13 +8709,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>609130</v>
+        <v>609066</v>
       </c>
       <c r="R74" t="n">
-        <v>7062851</v>
+        <v>7062980</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119851377</v>
+        <v>119851421</v>
       </c>
       <c r="B75" t="n">
         <v>79607</v>
@@ -8811,13 +8811,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>609065</v>
+        <v>609130</v>
       </c>
       <c r="R75" t="n">
-        <v>7062657</v>
+        <v>7062851</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8844,19 +8844,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8871,22 +8861,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119849717</v>
+        <v>119851377</v>
       </c>
       <c r="B76" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8899,21 +8889,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8923,10 +8913,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>608896</v>
+        <v>609065</v>
       </c>
       <c r="R76" t="n">
-        <v>7062656</v>
+        <v>7062657</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8958,7 +8948,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8968,12 +8958,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9000,10 +8985,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119850876</v>
+        <v>119849717</v>
       </c>
       <c r="B77" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9016,21 +9001,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9040,13 +9025,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>609066</v>
+        <v>608896</v>
       </c>
       <c r="R77" t="n">
-        <v>7062980</v>
+        <v>7062656</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9073,9 +9058,24 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9090,12 +9090,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9306,10 +9306,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119850411</v>
+        <v>119849829</v>
       </c>
       <c r="B80" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9318,25 +9318,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9346,10 +9346,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>609003</v>
+        <v>608941</v>
       </c>
       <c r="R80" t="n">
-        <v>7062803</v>
+        <v>7062708</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9408,10 +9408,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119849829</v>
+        <v>119850562</v>
       </c>
       <c r="B81" t="n">
-        <v>90562</v>
+        <v>91128</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9420,25 +9420,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9448,10 +9448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>608941</v>
+        <v>608992</v>
       </c>
       <c r="R81" t="n">
-        <v>7062708</v>
+        <v>7062626</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9481,9 +9481,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9498,22 +9508,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119850562</v>
+        <v>119851290</v>
       </c>
       <c r="B82" t="n">
-        <v>91128</v>
+        <v>79607</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9522,25 +9532,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9550,10 +9560,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>608992</v>
+        <v>609054</v>
       </c>
       <c r="R82" t="n">
-        <v>7062626</v>
+        <v>7062684</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9585,7 +9595,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9595,7 +9605,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9622,10 +9632,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119851290</v>
+        <v>119850411</v>
       </c>
       <c r="B83" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9634,25 +9644,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9662,10 +9672,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>609054</v>
+        <v>609003</v>
       </c>
       <c r="R83" t="n">
-        <v>7062684</v>
+        <v>7062803</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9695,19 +9705,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9722,12 +9722,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9836,10 +9836,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119849724</v>
+        <v>119849740</v>
       </c>
       <c r="B85" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9848,38 +9848,42 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>608908</v>
+        <v>608907</v>
       </c>
       <c r="R85" t="n">
-        <v>7062658</v>
+        <v>7062655</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9911,7 +9915,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9921,7 +9925,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9948,10 +9952,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119851664</v>
+        <v>119849966</v>
       </c>
       <c r="B86" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9960,38 +9964,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>609125</v>
+        <v>608853</v>
       </c>
       <c r="R86" t="n">
-        <v>7062827</v>
+        <v>7062579</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10021,9 +10029,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10038,22 +10056,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119851695</v>
+        <v>119850096</v>
       </c>
       <c r="B87" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10062,31 +10080,30 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -10095,13 +10112,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>609150</v>
+        <v>608905</v>
       </c>
       <c r="R87" t="n">
-        <v>7062808</v>
+        <v>7062586</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10128,9 +10145,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10145,19 +10172,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119849740</v>
+        <v>119850752</v>
       </c>
       <c r="B88" t="n">
         <v>97907</v>
@@ -10190,21 +10217,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>608907</v>
+        <v>609068</v>
       </c>
       <c r="R88" t="n">
-        <v>7062655</v>
+        <v>7062927</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10231,22 +10254,17 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10261,22 +10279,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119849966</v>
+        <v>119849724</v>
       </c>
       <c r="B89" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10285,42 +10303,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>608853</v>
+        <v>608908</v>
       </c>
       <c r="R89" t="n">
-        <v>7062579</v>
+        <v>7062658</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10352,7 +10366,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10362,7 +10376,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10389,10 +10403,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119850096</v>
+        <v>119851664</v>
       </c>
       <c r="B90" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10401,42 +10415,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>608905</v>
+        <v>609125</v>
       </c>
       <c r="R90" t="n">
-        <v>7062586</v>
+        <v>7062827</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10466,19 +10476,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10493,22 +10493,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119850752</v>
+        <v>119851695</v>
       </c>
       <c r="B91" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10517,41 +10517,46 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>609068</v>
+        <v>609150</v>
       </c>
       <c r="R91" t="n">
-        <v>7062927</v>
+        <v>7062808</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10575,17 +10580,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10728,10 +10728,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119849630</v>
+        <v>119851160</v>
       </c>
       <c r="B93" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10744,37 +10744,42 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>608895</v>
+        <v>609023</v>
       </c>
       <c r="R93" t="n">
-        <v>7062683</v>
+        <v>7062674</v>
       </c>
       <c r="S93" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10801,14 +10806,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, även på tall.</t>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10823,12 +10833,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
@@ -10937,10 +10947,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119851160</v>
+        <v>119849630</v>
       </c>
       <c r="B95" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10953,42 +10963,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>609023</v>
+        <v>608895</v>
       </c>
       <c r="R95" t="n">
-        <v>7062674</v>
+        <v>7062683</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11015,19 +11020,14 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>14:47</t>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11042,12 +11042,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11156,10 +11156,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119851861</v>
+        <v>119849905</v>
       </c>
       <c r="B97" t="n">
-        <v>79607</v>
+        <v>90582</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11172,21 +11172,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11196,13 +11196,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>609153</v>
+        <v>608876</v>
       </c>
       <c r="R97" t="n">
-        <v>7062783</v>
+        <v>7062635</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11229,9 +11229,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11246,22 +11256,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119849905</v>
+        <v>119851861</v>
       </c>
       <c r="B98" t="n">
-        <v>90582</v>
+        <v>79607</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11274,21 +11284,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11298,13 +11308,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>608876</v>
+        <v>609153</v>
       </c>
       <c r="R98" t="n">
-        <v>7062635</v>
+        <v>7062783</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11331,19 +11341,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11358,22 +11358,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119849971</v>
+        <v>119851428</v>
       </c>
       <c r="B99" t="n">
-        <v>79607</v>
+        <v>79643</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11382,25 +11382,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11410,13 +11410,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>608977</v>
+        <v>609133</v>
       </c>
       <c r="R99" t="n">
-        <v>7062755</v>
+        <v>7062851</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11472,10 +11472,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119851428</v>
+        <v>119849971</v>
       </c>
       <c r="B100" t="n">
-        <v>79643</v>
+        <v>79607</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11484,25 +11484,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11512,13 +11512,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>609133</v>
+        <v>608977</v>
       </c>
       <c r="R100" t="n">
-        <v>7062851</v>
+        <v>7062755</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -5390,10 +5390,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119851618</v>
+        <v>119849858</v>
       </c>
       <c r="B43" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5402,41 +5402,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>609113</v>
+        <v>608877</v>
       </c>
       <c r="R43" t="n">
-        <v>7062853</v>
+        <v>7062639</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5463,9 +5467,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5480,22 +5494,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119849721</v>
+        <v>119851306</v>
       </c>
       <c r="B44" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5504,38 +5518,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>608918</v>
+        <v>609039</v>
       </c>
       <c r="R44" t="n">
-        <v>7062673</v>
+        <v>7062664</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5565,9 +5583,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5582,22 +5610,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119852068</v>
+        <v>119850188</v>
       </c>
       <c r="B45" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5606,25 +5634,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5634,13 +5662,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>609119</v>
+        <v>608997</v>
       </c>
       <c r="R45" t="n">
-        <v>7062737</v>
+        <v>7062738</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5696,10 +5724,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119850188</v>
+        <v>119851732</v>
       </c>
       <c r="B46" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5708,25 +5736,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5736,13 +5764,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>608997</v>
+        <v>609149</v>
       </c>
       <c r="R46" t="n">
-        <v>7062738</v>
+        <v>7062808</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5900,10 +5928,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119851047</v>
+        <v>119851664</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5912,42 +5940,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609018</v>
+        <v>609125</v>
       </c>
       <c r="R48" t="n">
-        <v>7062666</v>
+        <v>7062827</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5977,19 +6001,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6004,22 +6018,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119850568</v>
+        <v>119850876</v>
       </c>
       <c r="B49" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6028,25 +6042,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6056,13 +6070,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609033</v>
+        <v>609066</v>
       </c>
       <c r="R49" t="n">
-        <v>7062884</v>
+        <v>7062980</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6118,7 +6132,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119850955</v>
+        <v>119851928</v>
       </c>
       <c r="B50" t="n">
         <v>79607</v>
@@ -6158,10 +6172,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609006</v>
+        <v>609172</v>
       </c>
       <c r="R50" t="n">
-        <v>7062681</v>
+        <v>7062778</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6191,19 +6205,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6218,22 +6222,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119850321</v>
+        <v>119849742</v>
       </c>
       <c r="B51" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6246,21 +6250,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6270,10 +6274,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609015</v>
+        <v>608916</v>
       </c>
       <c r="R51" t="n">
-        <v>7062798</v>
+        <v>7062680</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -6332,10 +6336,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119851684</v>
+        <v>119849755</v>
       </c>
       <c r="B52" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6348,21 +6352,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6372,10 +6376,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>609149</v>
+        <v>608914</v>
       </c>
       <c r="R52" t="n">
-        <v>7062828</v>
+        <v>7062689</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6434,10 +6438,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119849708</v>
+        <v>119849829</v>
       </c>
       <c r="B53" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6450,21 +6454,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6474,10 +6478,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>608910</v>
+        <v>608941</v>
       </c>
       <c r="R53" t="n">
-        <v>7062662</v>
+        <v>7062708</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6536,10 +6540,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119851413</v>
+        <v>119849966</v>
       </c>
       <c r="B54" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6548,31 +6552,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6581,10 +6584,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609070</v>
+        <v>608853</v>
       </c>
       <c r="R54" t="n">
-        <v>7062653</v>
+        <v>7062579</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6616,7 +6619,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6626,7 +6629,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6653,10 +6656,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119849903</v>
+        <v>119850006</v>
       </c>
       <c r="B55" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6669,21 +6672,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6693,13 +6696,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>608950</v>
+        <v>609003</v>
       </c>
       <c r="R55" t="n">
-        <v>7062709</v>
+        <v>7062728</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6755,10 +6758,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119850656</v>
+        <v>119851802</v>
       </c>
       <c r="B56" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6767,25 +6770,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6795,10 +6798,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>609048</v>
+        <v>609143</v>
       </c>
       <c r="R56" t="n">
-        <v>7062921</v>
+        <v>7062799</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6857,7 +6860,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119851329</v>
+        <v>119850568</v>
       </c>
       <c r="B57" t="n">
         <v>97907</v>
@@ -6897,10 +6900,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609091</v>
+        <v>609033</v>
       </c>
       <c r="R57" t="n">
-        <v>7062941</v>
+        <v>7062884</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6927,12 +6930,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6959,7 +6962,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119851973</v>
+        <v>119849952</v>
       </c>
       <c r="B58" t="n">
         <v>79607</v>
@@ -6999,13 +7002,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>609151</v>
+        <v>608976</v>
       </c>
       <c r="R58" t="n">
-        <v>7062747</v>
+        <v>7062742</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7029,12 +7032,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>1970-01-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7061,10 +7064,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119849952</v>
+        <v>119849740</v>
       </c>
       <c r="B59" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7073,41 +7076,45 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>608976</v>
+        <v>608907</v>
       </c>
       <c r="R59" t="n">
-        <v>7062742</v>
+        <v>7062655</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7131,12 +7138,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7151,22 +7168,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119850782</v>
+        <v>119851973</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7175,42 +7192,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>608954</v>
+        <v>609151</v>
       </c>
       <c r="R60" t="n">
-        <v>7062685</v>
+        <v>7062747</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7240,19 +7253,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:27</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7267,22 +7270,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119849658</v>
+        <v>119851421</v>
       </c>
       <c r="B61" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7295,42 +7298,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>608890</v>
+        <v>609130</v>
       </c>
       <c r="R61" t="n">
-        <v>7062664</v>
+        <v>7062851</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7357,19 +7355,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7384,22 +7372,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119850926</v>
+        <v>119851684</v>
       </c>
       <c r="B62" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7412,42 +7400,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609003</v>
+        <v>609149</v>
       </c>
       <c r="R62" t="n">
-        <v>7062700</v>
+        <v>7062828</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7474,19 +7457,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7501,22 +7474,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119849755</v>
+        <v>119851878</v>
       </c>
       <c r="B63" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7529,21 +7502,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7553,13 +7526,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>608914</v>
+        <v>609153</v>
       </c>
       <c r="R63" t="n">
-        <v>7062689</v>
+        <v>7062778</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7615,7 +7588,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119850720</v>
+        <v>119851329</v>
       </c>
       <c r="B64" t="n">
         <v>97907</v>
@@ -7648,21 +7621,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>608957</v>
+        <v>609091</v>
       </c>
       <c r="R64" t="n">
-        <v>7062678</v>
+        <v>7062941</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7689,22 +7658,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:23</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7719,22 +7678,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119851185</v>
+        <v>119849630</v>
       </c>
       <c r="B65" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7743,25 +7702,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7771,13 +7730,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609097</v>
+        <v>608895</v>
       </c>
       <c r="R65" t="n">
-        <v>7062964</v>
+        <v>7062683</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7801,12 +7760,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7833,10 +7797,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119851502</v>
+        <v>119851861</v>
       </c>
       <c r="B66" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7845,25 +7809,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7873,10 +7837,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609140</v>
+        <v>609153</v>
       </c>
       <c r="R66" t="n">
-        <v>7062863</v>
+        <v>7062783</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7935,10 +7899,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119851104</v>
+        <v>119849973</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7947,25 +7911,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7975,13 +7939,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>609085</v>
+        <v>608986</v>
       </c>
       <c r="R67" t="n">
-        <v>7062996</v>
+        <v>7062749</v>
       </c>
       <c r="S67" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8011,11 +7975,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8042,10 +8001,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119850850</v>
+        <v>119850096</v>
       </c>
       <c r="B68" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8054,38 +8013,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>609076</v>
+        <v>608905</v>
       </c>
       <c r="R68" t="n">
-        <v>7062968</v>
+        <v>7062586</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8115,9 +8078,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8132,22 +8105,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119851732</v>
+        <v>119851235</v>
       </c>
       <c r="B69" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8156,25 +8129,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8184,13 +8157,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>609149</v>
+        <v>609101</v>
       </c>
       <c r="R69" t="n">
-        <v>7062808</v>
+        <v>7062955</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8246,10 +8219,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119851878</v>
+        <v>119851428</v>
       </c>
       <c r="B70" t="n">
-        <v>79607</v>
+        <v>79643</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8258,25 +8231,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8286,13 +8259,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>609153</v>
+        <v>609133</v>
       </c>
       <c r="R70" t="n">
-        <v>7062778</v>
+        <v>7062851</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8348,7 +8321,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119851928</v>
+        <v>119851950</v>
       </c>
       <c r="B71" t="n">
         <v>79607</v>
@@ -8388,13 +8361,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609172</v>
+        <v>609160</v>
       </c>
       <c r="R71" t="n">
-        <v>7062778</v>
+        <v>7062762</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8450,10 +8423,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119850459</v>
+        <v>119852025</v>
       </c>
       <c r="B72" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8466,39 +8439,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>608949</v>
+        <v>609136</v>
       </c>
       <c r="R72" t="n">
-        <v>7062585</v>
+        <v>7062753</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8528,19 +8496,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8555,22 +8513,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119850220</v>
+        <v>119849724</v>
       </c>
       <c r="B73" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8583,21 +8541,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8607,10 +8565,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>608994</v>
+        <v>608908</v>
       </c>
       <c r="R73" t="n">
-        <v>7062775</v>
+        <v>7062658</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8637,12 +8595,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8657,22 +8625,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119850876</v>
+        <v>119850220</v>
       </c>
       <c r="B74" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8685,21 +8653,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8709,13 +8677,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>609066</v>
+        <v>608994</v>
       </c>
       <c r="R74" t="n">
-        <v>7062980</v>
+        <v>7062775</v>
       </c>
       <c r="S74" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8739,12 +8707,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8771,10 +8739,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119851421</v>
+        <v>119849717</v>
       </c>
       <c r="B75" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8787,21 +8755,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8811,13 +8779,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>609130</v>
+        <v>608896</v>
       </c>
       <c r="R75" t="n">
-        <v>7062851</v>
+        <v>7062656</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8844,9 +8812,24 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8861,22 +8844,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119851377</v>
+        <v>119850834</v>
       </c>
       <c r="B76" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8889,21 +8872,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8913,13 +8896,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>609065</v>
+        <v>609080</v>
       </c>
       <c r="R76" t="n">
-        <v>7062657</v>
+        <v>7062946</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8946,19 +8929,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8973,22 +8946,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119849717</v>
+        <v>119851377</v>
       </c>
       <c r="B77" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9001,21 +8974,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9025,10 +8998,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>608896</v>
+        <v>609065</v>
       </c>
       <c r="R77" t="n">
-        <v>7062656</v>
+        <v>7062657</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9060,7 +9033,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9070,12 +9043,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9102,7 +9070,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119850006</v>
+        <v>119852068</v>
       </c>
       <c r="B78" t="n">
         <v>79607</v>
@@ -9142,13 +9110,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>609003</v>
+        <v>609119</v>
       </c>
       <c r="R78" t="n">
-        <v>7062728</v>
+        <v>7062737</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9204,10 +9172,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119851235</v>
+        <v>119851361</v>
       </c>
       <c r="B79" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9216,25 +9184,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9244,13 +9212,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>609101</v>
+        <v>609100</v>
       </c>
       <c r="R79" t="n">
-        <v>7062955</v>
+        <v>7062937</v>
       </c>
       <c r="S79" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9274,12 +9242,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9306,10 +9274,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119849829</v>
+        <v>119851104</v>
       </c>
       <c r="B80" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9322,21 +9290,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9346,13 +9314,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>608941</v>
+        <v>609085</v>
       </c>
       <c r="R80" t="n">
-        <v>7062708</v>
+        <v>7062996</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9382,6 +9350,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9408,10 +9381,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119850562</v>
+        <v>119851290</v>
       </c>
       <c r="B81" t="n">
-        <v>91128</v>
+        <v>79607</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9420,25 +9393,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9448,10 +9421,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>608992</v>
+        <v>609054</v>
       </c>
       <c r="R81" t="n">
-        <v>7062626</v>
+        <v>7062684</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9483,7 +9456,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9493,7 +9466,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9520,10 +9493,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119851290</v>
+        <v>119851274</v>
       </c>
       <c r="B82" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9536,34 +9509,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>609054</v>
+        <v>609039</v>
       </c>
       <c r="R82" t="n">
-        <v>7062684</v>
+        <v>7062654</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9595,7 +9573,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9605,7 +9583,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9632,10 +9610,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119850411</v>
+        <v>119849708</v>
       </c>
       <c r="B83" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9644,25 +9622,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9672,10 +9650,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>609003</v>
+        <v>608910</v>
       </c>
       <c r="R83" t="n">
-        <v>7062803</v>
+        <v>7062662</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9734,10 +9712,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119849973</v>
+        <v>119851185</v>
       </c>
       <c r="B84" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9746,25 +9724,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9774,10 +9752,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>608986</v>
+        <v>609097</v>
       </c>
       <c r="R84" t="n">
-        <v>7062749</v>
+        <v>7062964</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9804,12 +9782,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9836,7 +9814,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119849740</v>
+        <v>119850411</v>
       </c>
       <c r="B85" t="n">
         <v>97907</v>
@@ -9869,21 +9847,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>608907</v>
+        <v>609003</v>
       </c>
       <c r="R85" t="n">
-        <v>7062655</v>
+        <v>7062803</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9913,19 +9887,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9940,22 +9904,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119849966</v>
+        <v>119851695</v>
       </c>
       <c r="B86" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9964,30 +9928,31 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9996,13 +9961,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>608853</v>
+        <v>609150</v>
       </c>
       <c r="R86" t="n">
-        <v>7062579</v>
+        <v>7062808</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10029,19 +9994,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10056,19 +10011,19 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119850096</v>
+        <v>119850752</v>
       </c>
       <c r="B87" t="n">
         <v>97907</v>
@@ -10101,21 +10056,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>608905</v>
+        <v>609068</v>
       </c>
       <c r="R87" t="n">
-        <v>7062586</v>
+        <v>7062927</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10142,22 +10093,17 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10172,19 +10118,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119850752</v>
+        <v>119851502</v>
       </c>
       <c r="B88" t="n">
         <v>97907</v>
@@ -10224,13 +10170,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>609068</v>
+        <v>609140</v>
       </c>
       <c r="R88" t="n">
-        <v>7062927</v>
+        <v>7062863</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10254,17 +10200,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10291,10 +10232,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119849724</v>
+        <v>119851641</v>
       </c>
       <c r="B89" t="n">
-        <v>78526</v>
+        <v>79643</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10303,25 +10244,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10331,13 +10272,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>608908</v>
+        <v>609109</v>
       </c>
       <c r="R89" t="n">
-        <v>7062658</v>
+        <v>7062833</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10364,19 +10305,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10391,19 +10322,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119851664</v>
+        <v>119850321</v>
       </c>
       <c r="B90" t="n">
         <v>79607</v>
@@ -10443,13 +10374,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>609125</v>
+        <v>609015</v>
       </c>
       <c r="R90" t="n">
-        <v>7062827</v>
+        <v>7062798</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10505,10 +10436,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119851695</v>
+        <v>119851160</v>
       </c>
       <c r="B91" t="n">
-        <v>57463</v>
+        <v>57310</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10521,27 +10452,27 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10550,13 +10481,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>609150</v>
+        <v>609023</v>
       </c>
       <c r="R91" t="n">
-        <v>7062808</v>
+        <v>7062674</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10583,9 +10514,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10600,22 +10541,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119849858</v>
+        <v>119850926</v>
       </c>
       <c r="B92" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10624,30 +10565,31 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10656,10 +10598,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>608877</v>
+        <v>609003</v>
       </c>
       <c r="R92" t="n">
-        <v>7062639</v>
+        <v>7062700</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10691,7 +10633,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10701,7 +10643,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10728,10 +10670,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119851160</v>
+        <v>119851047</v>
       </c>
       <c r="B93" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10740,31 +10682,30 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10773,10 +10714,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>609023</v>
+        <v>609018</v>
       </c>
       <c r="R93" t="n">
-        <v>7062674</v>
+        <v>7062666</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10808,7 +10749,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10818,7 +10759,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10845,10 +10786,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119851251</v>
+        <v>119850782</v>
       </c>
       <c r="B94" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10857,38 +10798,42 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>609099</v>
+        <v>608954</v>
       </c>
       <c r="R94" t="n">
-        <v>7062948</v>
+        <v>7062685</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10918,9 +10863,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10935,22 +10890,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119849630</v>
+        <v>119849905</v>
       </c>
       <c r="B95" t="n">
-        <v>78526</v>
+        <v>90582</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10963,21 +10918,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,13 +10942,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>608895</v>
+        <v>608876</v>
       </c>
       <c r="R95" t="n">
-        <v>7062683</v>
+        <v>7062635</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11020,14 +10975,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, även på tall.</t>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11042,22 +11002,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119850519</v>
+        <v>119850850</v>
       </c>
       <c r="B96" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11066,25 +11026,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11094,10 +11054,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>609012</v>
+        <v>609076</v>
       </c>
       <c r="R96" t="n">
-        <v>7062828</v>
+        <v>7062968</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11156,10 +11116,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119849905</v>
+        <v>119849721</v>
       </c>
       <c r="B97" t="n">
-        <v>90582</v>
+        <v>90562</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11172,21 +11132,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11196,10 +11156,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>608876</v>
+        <v>608918</v>
       </c>
       <c r="R97" t="n">
-        <v>7062635</v>
+        <v>7062673</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11229,19 +11189,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11256,19 +11206,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119851861</v>
+        <v>119851993</v>
       </c>
       <c r="B98" t="n">
         <v>79607</v>
@@ -11308,13 +11258,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>609153</v>
+        <v>609135</v>
       </c>
       <c r="R98" t="n">
-        <v>7062783</v>
+        <v>7062752</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11370,10 +11320,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119851428</v>
+        <v>119850459</v>
       </c>
       <c r="B99" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11382,41 +11332,46 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>609133</v>
+        <v>608949</v>
       </c>
       <c r="R99" t="n">
-        <v>7062851</v>
+        <v>7062585</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11443,9 +11398,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11460,22 +11425,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119849971</v>
+        <v>119849903</v>
       </c>
       <c r="B100" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11488,21 +11453,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11512,10 +11477,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>608977</v>
+        <v>608950</v>
       </c>
       <c r="R100" t="n">
-        <v>7062755</v>
+        <v>7062709</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11574,10 +11539,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119849742</v>
+        <v>119850562</v>
       </c>
       <c r="B101" t="n">
-        <v>90846</v>
+        <v>91128</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11586,25 +11551,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>658</v>
+        <v>760</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11614,13 +11579,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>608916</v>
+        <v>608992</v>
       </c>
       <c r="R101" t="n">
-        <v>7062680</v>
+        <v>7062626</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11647,9 +11612,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11664,22 +11639,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119851641</v>
+        <v>119850656</v>
       </c>
       <c r="B102" t="n">
-        <v>79643</v>
+        <v>97907</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11688,25 +11663,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11716,13 +11691,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>609109</v>
+        <v>609048</v>
       </c>
       <c r="R102" t="n">
-        <v>7062833</v>
+        <v>7062921</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11778,10 +11753,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119850834</v>
+        <v>119850436</v>
       </c>
       <c r="B103" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11790,25 +11765,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11818,10 +11793,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>609080</v>
+        <v>609002</v>
       </c>
       <c r="R103" t="n">
-        <v>7062946</v>
+        <v>7062810</v>
       </c>
       <c r="S103" t="n">
         <v>15</v>
@@ -11880,10 +11855,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119851306</v>
+        <v>119851251</v>
       </c>
       <c r="B104" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11892,42 +11867,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>609039</v>
+        <v>609099</v>
       </c>
       <c r="R104" t="n">
-        <v>7062664</v>
+        <v>7062948</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11957,19 +11928,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11984,22 +11945,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119850436</v>
+        <v>119851618</v>
       </c>
       <c r="B105" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12008,25 +11969,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12036,10 +11997,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>609002</v>
+        <v>609113</v>
       </c>
       <c r="R105" t="n">
-        <v>7062810</v>
+        <v>7062853</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -12098,10 +12059,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119851361</v>
+        <v>119850720</v>
       </c>
       <c r="B106" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12110,41 +12071,45 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>609100</v>
+        <v>608957</v>
       </c>
       <c r="R106" t="n">
-        <v>7062937</v>
+        <v>7062678</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12168,12 +12133,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12188,22 +12163,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119852025</v>
+        <v>119851413</v>
       </c>
       <c r="B107" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12216,34 +12191,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>609136</v>
+        <v>609070</v>
       </c>
       <c r="R107" t="n">
-        <v>7062753</v>
+        <v>7062653</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12273,9 +12253,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12290,22 +12280,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119851993</v>
+        <v>119850519</v>
       </c>
       <c r="B108" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12314,25 +12304,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12342,10 +12332,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>609135</v>
+        <v>609012</v>
       </c>
       <c r="R108" t="n">
-        <v>7062752</v>
+        <v>7062828</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12404,7 +12394,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119851802</v>
+        <v>119849971</v>
       </c>
       <c r="B109" t="n">
         <v>79607</v>
@@ -12444,10 +12434,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>609143</v>
+        <v>608977</v>
       </c>
       <c r="R109" t="n">
-        <v>7062799</v>
+        <v>7062755</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12506,10 +12496,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119851950</v>
+        <v>119849658</v>
       </c>
       <c r="B110" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12522,37 +12512,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>609160</v>
+        <v>608890</v>
       </c>
       <c r="R110" t="n">
-        <v>7062762</v>
+        <v>7062664</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12579,9 +12574,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12596,22 +12601,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119851274</v>
+        <v>119850955</v>
       </c>
       <c r="B111" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12624,39 +12629,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>609039</v>
+        <v>609006</v>
       </c>
       <c r="R111" t="n">
-        <v>7062654</v>
+        <v>7062681</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD111" t="b">

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -5928,10 +5928,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119851664</v>
+        <v>119849742</v>
       </c>
       <c r="B48" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5944,21 +5944,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5968,13 +5968,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609125</v>
+        <v>608916</v>
       </c>
       <c r="R48" t="n">
-        <v>7062827</v>
+        <v>7062680</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6030,10 +6030,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119850876</v>
+        <v>119851664</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6046,21 +6046,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6070,13 +6070,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609066</v>
+        <v>609125</v>
       </c>
       <c r="R49" t="n">
-        <v>7062980</v>
+        <v>7062827</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6132,10 +6132,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119851928</v>
+        <v>119850876</v>
       </c>
       <c r="B50" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6148,21 +6148,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6172,13 +6172,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609172</v>
+        <v>609066</v>
       </c>
       <c r="R50" t="n">
-        <v>7062778</v>
+        <v>7062980</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6234,10 +6234,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119849742</v>
+        <v>119851928</v>
       </c>
       <c r="B51" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6250,21 +6250,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6274,13 +6274,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>608916</v>
+        <v>609172</v>
       </c>
       <c r="R51" t="n">
-        <v>7062680</v>
+        <v>7062778</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119849755</v>
+        <v>119849966</v>
       </c>
       <c r="B52" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6348,41 +6348,45 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>608914</v>
+        <v>608853</v>
       </c>
       <c r="R52" t="n">
-        <v>7062689</v>
+        <v>7062579</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6409,9 +6413,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6426,19 +6440,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119849829</v>
+        <v>119849755</v>
       </c>
       <c r="B53" t="n">
         <v>90562</v>
@@ -6478,13 +6492,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>608941</v>
+        <v>608914</v>
       </c>
       <c r="R53" t="n">
-        <v>7062708</v>
+        <v>7062689</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6540,10 +6554,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119849966</v>
+        <v>119849829</v>
       </c>
       <c r="B54" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6552,42 +6566,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>608853</v>
+        <v>608941</v>
       </c>
       <c r="R54" t="n">
-        <v>7062579</v>
+        <v>7062708</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6617,19 +6627,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6644,12 +6644,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -8001,10 +8001,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119850096</v>
+        <v>119849724</v>
       </c>
       <c r="B68" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8013,42 +8013,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>608905</v>
+        <v>608908</v>
       </c>
       <c r="R68" t="n">
-        <v>7062586</v>
+        <v>7062658</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8080,7 +8076,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8090,7 +8086,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8117,10 +8113,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119851235</v>
+        <v>119851428</v>
       </c>
       <c r="B69" t="n">
-        <v>97907</v>
+        <v>79643</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8129,25 +8125,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8157,13 +8153,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>609101</v>
+        <v>609133</v>
       </c>
       <c r="R69" t="n">
-        <v>7062955</v>
+        <v>7062851</v>
       </c>
       <c r="S69" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8219,10 +8215,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119851428</v>
+        <v>119851950</v>
       </c>
       <c r="B70" t="n">
-        <v>79643</v>
+        <v>79607</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8231,25 +8227,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8259,10 +8255,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>609133</v>
+        <v>609160</v>
       </c>
       <c r="R70" t="n">
-        <v>7062851</v>
+        <v>7062762</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8321,7 +8317,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119851950</v>
+        <v>119852025</v>
       </c>
       <c r="B71" t="n">
         <v>79607</v>
@@ -8361,13 +8357,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609160</v>
+        <v>609136</v>
       </c>
       <c r="R71" t="n">
-        <v>7062762</v>
+        <v>7062753</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8423,10 +8419,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119852025</v>
+        <v>119851235</v>
       </c>
       <c r="B72" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8435,25 +8431,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8463,13 +8459,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>609136</v>
+        <v>609101</v>
       </c>
       <c r="R72" t="n">
-        <v>7062753</v>
+        <v>7062955</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8525,10 +8521,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119849724</v>
+        <v>119850096</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8537,38 +8533,42 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>608908</v>
+        <v>608905</v>
       </c>
       <c r="R73" t="n">
-        <v>7062658</v>
+        <v>7062586</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8600,7 +8600,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9274,10 +9274,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119851104</v>
+        <v>119851274</v>
       </c>
       <c r="B80" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9290,37 +9290,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>609085</v>
+        <v>609039</v>
       </c>
       <c r="R80" t="n">
-        <v>7062996</v>
+        <v>7062654</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9347,14 +9352,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9369,22 +9379,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119851290</v>
+        <v>119851104</v>
       </c>
       <c r="B81" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9397,21 +9407,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9421,13 +9431,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>609054</v>
+        <v>609085</v>
       </c>
       <c r="R81" t="n">
-        <v>7062684</v>
+        <v>7062996</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9454,19 +9464,14 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:01</t>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9481,22 +9486,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119851274</v>
+        <v>119851290</v>
       </c>
       <c r="B82" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9509,39 +9514,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>609039</v>
+        <v>609054</v>
       </c>
       <c r="R82" t="n">
-        <v>7062654</v>
+        <v>7062684</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9573,7 +9573,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10130,10 +10130,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119851502</v>
+        <v>119850926</v>
       </c>
       <c r="B88" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10142,41 +10142,46 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>609140</v>
+        <v>609003</v>
       </c>
       <c r="R88" t="n">
-        <v>7062863</v>
+        <v>7062700</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10203,9 +10208,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10220,12 +10235,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10553,10 +10568,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119850926</v>
+        <v>119851502</v>
       </c>
       <c r="B92" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10565,46 +10580,41 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>609003</v>
+        <v>609140</v>
       </c>
       <c r="R92" t="n">
-        <v>7062700</v>
+        <v>7062863</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10631,19 +10641,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>14:35</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10658,12 +10658,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10902,10 +10902,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119849905</v>
+        <v>119850850</v>
       </c>
       <c r="B95" t="n">
-        <v>90582</v>
+        <v>79607</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10918,21 +10918,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10942,10 +10942,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>608876</v>
+        <v>609076</v>
       </c>
       <c r="R95" t="n">
-        <v>7062635</v>
+        <v>7062968</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10975,19 +10975,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11002,22 +10992,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119850850</v>
+        <v>119849905</v>
       </c>
       <c r="B96" t="n">
-        <v>79607</v>
+        <v>90582</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11030,21 +11020,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11054,10 +11044,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>609076</v>
+        <v>608876</v>
       </c>
       <c r="R96" t="n">
-        <v>7062968</v>
+        <v>7062635</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11087,9 +11077,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11104,22 +11104,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119849721</v>
+        <v>119851993</v>
       </c>
       <c r="B97" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11132,21 +11132,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11156,10 +11156,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>608918</v>
+        <v>609135</v>
       </c>
       <c r="R97" t="n">
-        <v>7062673</v>
+        <v>7062752</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11218,10 +11218,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119851993</v>
+        <v>119849721</v>
       </c>
       <c r="B98" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11234,21 +11234,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11258,10 +11258,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>609135</v>
+        <v>608918</v>
       </c>
       <c r="R98" t="n">
-        <v>7062752</v>
+        <v>7062673</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -5390,10 +5390,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119849858</v>
+        <v>119850220</v>
       </c>
       <c r="B43" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5402,42 +5402,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>608877</v>
+        <v>608994</v>
       </c>
       <c r="R43" t="n">
-        <v>7062639</v>
+        <v>7062775</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5464,22 +5460,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:27</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5494,19 +5480,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119851306</v>
+        <v>119851185</v>
       </c>
       <c r="B44" t="n">
         <v>97907</v>
@@ -5539,24 +5525,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>609039</v>
+        <v>609097</v>
       </c>
       <c r="R44" t="n">
-        <v>7062664</v>
+        <v>7062964</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5580,22 +5562,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:03</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5610,22 +5582,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119850188</v>
+        <v>119850926</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5634,41 +5606,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>608997</v>
+        <v>609003</v>
       </c>
       <c r="R45" t="n">
-        <v>7062738</v>
+        <v>7062700</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5695,9 +5672,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5712,22 +5699,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119851732</v>
+        <v>119849755</v>
       </c>
       <c r="B46" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5740,21 +5727,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5764,13 +5751,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>609149</v>
+        <v>608914</v>
       </c>
       <c r="R46" t="n">
-        <v>7062808</v>
+        <v>7062689</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5826,10 +5813,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119850115</v>
+        <v>119851861</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5838,25 +5825,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5866,10 +5853,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>609002</v>
+        <v>609153</v>
       </c>
       <c r="R47" t="n">
-        <v>7062743</v>
+        <v>7062783</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5928,10 +5915,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119849742</v>
+        <v>119850834</v>
       </c>
       <c r="B48" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5944,21 +5931,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5968,10 +5955,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>608916</v>
+        <v>609080</v>
       </c>
       <c r="R48" t="n">
-        <v>7062680</v>
+        <v>7062946</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -6030,10 +6017,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119851664</v>
+        <v>119850876</v>
       </c>
       <c r="B49" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6046,21 +6033,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6070,13 +6057,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609125</v>
+        <v>609066</v>
       </c>
       <c r="R49" t="n">
-        <v>7062827</v>
+        <v>7062980</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6132,10 +6119,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119850876</v>
+        <v>119849973</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6144,25 +6131,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6172,13 +6159,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609066</v>
+        <v>608986</v>
       </c>
       <c r="R50" t="n">
-        <v>7062980</v>
+        <v>7062749</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6234,10 +6221,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119851928</v>
+        <v>119849905</v>
       </c>
       <c r="B51" t="n">
-        <v>79607</v>
+        <v>90582</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6250,21 +6237,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6274,10 +6261,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609172</v>
+        <v>608876</v>
       </c>
       <c r="R51" t="n">
-        <v>7062778</v>
+        <v>7062635</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6307,9 +6294,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6324,22 +6321,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119849966</v>
+        <v>119851950</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6348,45 +6345,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>608853</v>
+        <v>609160</v>
       </c>
       <c r="R52" t="n">
-        <v>7062579</v>
+        <v>7062762</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6413,19 +6406,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6440,22 +6423,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119849755</v>
+        <v>119851413</v>
       </c>
       <c r="B53" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6468,37 +6451,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>608914</v>
+        <v>609070</v>
       </c>
       <c r="R53" t="n">
-        <v>7062689</v>
+        <v>7062653</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6525,9 +6513,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6542,22 +6540,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119849829</v>
+        <v>119849717</v>
       </c>
       <c r="B54" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6570,21 +6568,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6594,10 +6592,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>608941</v>
+        <v>608896</v>
       </c>
       <c r="R54" t="n">
-        <v>7062708</v>
+        <v>7062656</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6627,9 +6625,24 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6644,22 +6657,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119850006</v>
+        <v>119850096</v>
       </c>
       <c r="B55" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6668,41 +6681,45 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609003</v>
+        <v>608905</v>
       </c>
       <c r="R55" t="n">
-        <v>7062728</v>
+        <v>7062586</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6729,9 +6746,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6746,22 +6773,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119851802</v>
+        <v>119850720</v>
       </c>
       <c r="B56" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6770,38 +6797,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>609143</v>
+        <v>608957</v>
       </c>
       <c r="R56" t="n">
-        <v>7062799</v>
+        <v>7062678</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6831,9 +6862,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6848,22 +6889,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119850568</v>
+        <v>119850562</v>
       </c>
       <c r="B57" t="n">
-        <v>97907</v>
+        <v>91128</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6876,21 +6917,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6900,10 +6941,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609033</v>
+        <v>608992</v>
       </c>
       <c r="R57" t="n">
-        <v>7062884</v>
+        <v>7062626</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6933,9 +6974,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6950,22 +7001,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119849952</v>
+        <v>119850459</v>
       </c>
       <c r="B58" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6978,37 +7029,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>608976</v>
+        <v>608949</v>
       </c>
       <c r="R58" t="n">
-        <v>7062742</v>
+        <v>7062585</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7032,12 +7088,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7052,19 +7118,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119849740</v>
+        <v>119850436</v>
       </c>
       <c r="B59" t="n">
         <v>97907</v>
@@ -7097,24 +7163,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>608907</v>
+        <v>609002</v>
       </c>
       <c r="R59" t="n">
-        <v>7062655</v>
+        <v>7062810</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7141,19 +7203,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7168,22 +7220,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119851973</v>
+        <v>119851235</v>
       </c>
       <c r="B60" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7192,25 +7244,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7220,13 +7272,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>609151</v>
+        <v>609101</v>
       </c>
       <c r="R60" t="n">
-        <v>7062747</v>
+        <v>7062955</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7384,7 +7436,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119851684</v>
+        <v>119850850</v>
       </c>
       <c r="B62" t="n">
         <v>79607</v>
@@ -7424,13 +7476,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609149</v>
+        <v>609076</v>
       </c>
       <c r="R62" t="n">
-        <v>7062828</v>
+        <v>7062968</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7486,7 +7538,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119851878</v>
+        <v>119851802</v>
       </c>
       <c r="B63" t="n">
         <v>79607</v>
@@ -7526,10 +7578,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609153</v>
+        <v>609143</v>
       </c>
       <c r="R63" t="n">
-        <v>7062778</v>
+        <v>7062799</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7588,10 +7640,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119851329</v>
+        <v>119851160</v>
       </c>
       <c r="B64" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7600,38 +7652,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609091</v>
+        <v>609023</v>
       </c>
       <c r="R64" t="n">
-        <v>7062941</v>
+        <v>7062674</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7658,12 +7715,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7678,22 +7745,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119849630</v>
+        <v>119850752</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7702,25 +7769,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7730,13 +7797,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>608895</v>
+        <v>609068</v>
       </c>
       <c r="R65" t="n">
-        <v>7062683</v>
+        <v>7062927</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7760,17 +7827,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Riklig förekomst, även på tall.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7797,10 +7864,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119851861</v>
+        <v>119850568</v>
       </c>
       <c r="B66" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7809,25 +7876,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7837,13 +7904,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609153</v>
+        <v>609033</v>
       </c>
       <c r="R66" t="n">
-        <v>7062783</v>
+        <v>7062884</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7899,10 +7966,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119849973</v>
+        <v>119849740</v>
       </c>
       <c r="B67" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7911,41 +7978,45 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>608986</v>
+        <v>608907</v>
       </c>
       <c r="R67" t="n">
-        <v>7062749</v>
+        <v>7062655</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7972,9 +8043,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7989,19 +8070,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119849724</v>
+        <v>119851104</v>
       </c>
       <c r="B68" t="n">
         <v>78526</v>
@@ -8041,13 +8122,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>608908</v>
+        <v>609085</v>
       </c>
       <c r="R68" t="n">
-        <v>7062658</v>
+        <v>7062996</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8074,19 +8155,14 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:20</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8101,22 +8177,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119851428</v>
+        <v>119849829</v>
       </c>
       <c r="B69" t="n">
-        <v>79643</v>
+        <v>90562</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8125,25 +8201,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8153,13 +8229,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>609133</v>
+        <v>608941</v>
       </c>
       <c r="R69" t="n">
-        <v>7062851</v>
+        <v>7062708</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8215,7 +8291,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119851950</v>
+        <v>119852068</v>
       </c>
       <c r="B70" t="n">
         <v>79607</v>
@@ -8255,13 +8331,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>609160</v>
+        <v>609119</v>
       </c>
       <c r="R70" t="n">
-        <v>7062762</v>
+        <v>7062737</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8317,7 +8393,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119852025</v>
+        <v>119851664</v>
       </c>
       <c r="B71" t="n">
         <v>79607</v>
@@ -8357,10 +8433,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609136</v>
+        <v>609125</v>
       </c>
       <c r="R71" t="n">
-        <v>7062753</v>
+        <v>7062827</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8419,10 +8495,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119851235</v>
+        <v>119851290</v>
       </c>
       <c r="B72" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8431,25 +8507,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8459,13 +8535,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>609101</v>
+        <v>609054</v>
       </c>
       <c r="R72" t="n">
-        <v>7062955</v>
+        <v>7062684</v>
       </c>
       <c r="S72" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8492,9 +8568,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8509,19 +8595,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119850096</v>
+        <v>119850519</v>
       </c>
       <c r="B73" t="n">
         <v>97907</v>
@@ -8554,21 +8640,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>608905</v>
+        <v>609012</v>
       </c>
       <c r="R73" t="n">
-        <v>7062586</v>
+        <v>7062828</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8598,19 +8680,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8625,22 +8697,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119850220</v>
+        <v>119850955</v>
       </c>
       <c r="B74" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8653,21 +8725,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8677,10 +8749,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>608994</v>
+        <v>609006</v>
       </c>
       <c r="R74" t="n">
-        <v>7062775</v>
+        <v>7062681</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8707,12 +8779,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8727,22 +8809,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119849717</v>
+        <v>119851878</v>
       </c>
       <c r="B75" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8755,21 +8837,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8779,10 +8861,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>608896</v>
+        <v>609153</v>
       </c>
       <c r="R75" t="n">
-        <v>7062656</v>
+        <v>7062778</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8812,24 +8894,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8844,22 +8911,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119850834</v>
+        <v>119851306</v>
       </c>
       <c r="B76" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8868,41 +8935,45 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>609080</v>
+        <v>609039</v>
       </c>
       <c r="R76" t="n">
-        <v>7062946</v>
+        <v>7062664</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8929,9 +9000,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8946,22 +9027,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119851377</v>
+        <v>119851502</v>
       </c>
       <c r="B77" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8970,25 +9051,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8998,13 +9079,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>609065</v>
+        <v>609140</v>
       </c>
       <c r="R77" t="n">
-        <v>7062657</v>
+        <v>7062863</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9031,19 +9112,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9058,22 +9129,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119852068</v>
+        <v>119851641</v>
       </c>
       <c r="B78" t="n">
-        <v>79607</v>
+        <v>79643</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9082,25 +9153,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9110,13 +9181,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>609119</v>
+        <v>609109</v>
       </c>
       <c r="R78" t="n">
-        <v>7062737</v>
+        <v>7062833</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9172,7 +9243,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119851361</v>
+        <v>119850006</v>
       </c>
       <c r="B79" t="n">
         <v>79607</v>
@@ -9212,10 +9283,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>609100</v>
+        <v>609003</v>
       </c>
       <c r="R79" t="n">
-        <v>7062937</v>
+        <v>7062728</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -9242,12 +9313,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9274,10 +9345,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119851274</v>
+        <v>119852025</v>
       </c>
       <c r="B80" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9290,39 +9361,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>609039</v>
+        <v>609136</v>
       </c>
       <c r="R80" t="n">
-        <v>7062654</v>
+        <v>7062753</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9352,19 +9418,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9379,22 +9435,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119851104</v>
+        <v>119849658</v>
       </c>
       <c r="B81" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9407,37 +9463,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>609085</v>
+        <v>608890</v>
       </c>
       <c r="R81" t="n">
-        <v>7062996</v>
+        <v>7062664</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9464,14 +9525,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9486,22 +9552,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119851290</v>
+        <v>119849630</v>
       </c>
       <c r="B82" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9514,21 +9580,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9538,13 +9604,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>609054</v>
+        <v>608895</v>
       </c>
       <c r="R82" t="n">
-        <v>7062684</v>
+        <v>7062683</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9571,19 +9637,14 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>15:01</t>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9598,22 +9659,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119849708</v>
+        <v>119851329</v>
       </c>
       <c r="B83" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9622,25 +9683,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9650,10 +9711,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>608910</v>
+        <v>609091</v>
       </c>
       <c r="R83" t="n">
-        <v>7062662</v>
+        <v>7062941</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9680,12 +9741,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9712,10 +9773,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119851185</v>
+        <v>119851928</v>
       </c>
       <c r="B84" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9724,25 +9785,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9752,13 +9813,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>609097</v>
+        <v>609172</v>
       </c>
       <c r="R84" t="n">
-        <v>7062964</v>
+        <v>7062778</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9782,12 +9843,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9814,7 +9875,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119850411</v>
+        <v>119849858</v>
       </c>
       <c r="B85" t="n">
         <v>97907</v>
@@ -9847,17 +9908,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>609003</v>
+        <v>608877</v>
       </c>
       <c r="R85" t="n">
-        <v>7062803</v>
+        <v>7062639</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9887,9 +9952,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9904,22 +9979,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119851695</v>
+        <v>119849708</v>
       </c>
       <c r="B86" t="n">
-        <v>57463</v>
+        <v>90846</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9932,42 +10007,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>609150</v>
+        <v>608910</v>
       </c>
       <c r="R86" t="n">
-        <v>7062808</v>
+        <v>7062662</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10023,10 +10093,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119850752</v>
+        <v>119850321</v>
       </c>
       <c r="B87" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10035,25 +10105,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10063,13 +10133,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>609068</v>
+        <v>609015</v>
       </c>
       <c r="R87" t="n">
-        <v>7062927</v>
+        <v>7062798</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10093,17 +10163,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10130,10 +10195,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119850926</v>
+        <v>119849721</v>
       </c>
       <c r="B88" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10146,39 +10211,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>609003</v>
+        <v>608918</v>
       </c>
       <c r="R88" t="n">
-        <v>7062700</v>
+        <v>7062673</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10208,19 +10268,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>14:35</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10235,22 +10285,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119851641</v>
+        <v>119849724</v>
       </c>
       <c r="B89" t="n">
-        <v>79643</v>
+        <v>78526</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10259,25 +10309,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10287,13 +10337,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>609109</v>
+        <v>608908</v>
       </c>
       <c r="R89" t="n">
-        <v>7062833</v>
+        <v>7062658</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10320,9 +10370,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10337,22 +10397,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119850321</v>
+        <v>119850656</v>
       </c>
       <c r="B90" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10361,25 +10421,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10389,13 +10449,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>609015</v>
+        <v>609048</v>
       </c>
       <c r="R90" t="n">
-        <v>7062798</v>
+        <v>7062921</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10451,10 +10511,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119851160</v>
+        <v>119850782</v>
       </c>
       <c r="B91" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10463,31 +10523,30 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10496,10 +10555,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>609023</v>
+        <v>608954</v>
       </c>
       <c r="R91" t="n">
-        <v>7062674</v>
+        <v>7062685</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10531,7 +10590,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10541,7 +10600,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10568,10 +10627,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119851502</v>
+        <v>119851428</v>
       </c>
       <c r="B92" t="n">
-        <v>97907</v>
+        <v>79643</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10580,25 +10639,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10608,10 +10667,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>609140</v>
+        <v>609133</v>
       </c>
       <c r="R92" t="n">
-        <v>7062863</v>
+        <v>7062851</v>
       </c>
       <c r="S92" t="n">
         <v>15</v>
@@ -10670,7 +10729,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119851047</v>
+        <v>119850115</v>
       </c>
       <c r="B93" t="n">
         <v>97907</v>
@@ -10703,24 +10762,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>609018</v>
+        <v>609002</v>
       </c>
       <c r="R93" t="n">
-        <v>7062666</v>
+        <v>7062743</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10747,19 +10802,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10774,19 +10819,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119850782</v>
+        <v>119849966</v>
       </c>
       <c r="B94" t="n">
         <v>97907</v>
@@ -10821,7 +10866,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10830,10 +10875,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>608954</v>
+        <v>608853</v>
       </c>
       <c r="R94" t="n">
-        <v>7062685</v>
+        <v>7062579</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10865,7 +10910,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10875,7 +10920,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10902,7 +10947,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119850850</v>
+        <v>119851973</v>
       </c>
       <c r="B95" t="n">
         <v>79607</v>
@@ -10942,10 +10987,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>609076</v>
+        <v>609151</v>
       </c>
       <c r="R95" t="n">
-        <v>7062968</v>
+        <v>7062747</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11004,10 +11049,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119849905</v>
+        <v>119851732</v>
       </c>
       <c r="B96" t="n">
-        <v>90582</v>
+        <v>79607</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11020,21 +11065,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11044,10 +11089,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>608876</v>
+        <v>609149</v>
       </c>
       <c r="R96" t="n">
-        <v>7062635</v>
+        <v>7062808</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11077,19 +11122,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11104,22 +11139,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119851993</v>
+        <v>119850188</v>
       </c>
       <c r="B97" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11128,25 +11163,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11156,13 +11191,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>609135</v>
+        <v>608997</v>
       </c>
       <c r="R97" t="n">
-        <v>7062752</v>
+        <v>7062738</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11218,10 +11253,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119849721</v>
+        <v>119851361</v>
       </c>
       <c r="B98" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11234,21 +11269,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11258,13 +11293,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>608918</v>
+        <v>609100</v>
       </c>
       <c r="R98" t="n">
-        <v>7062673</v>
+        <v>7062937</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11288,12 +11323,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11320,10 +11355,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119850459</v>
+        <v>119851684</v>
       </c>
       <c r="B99" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11336,42 +11371,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>608949</v>
+        <v>609149</v>
       </c>
       <c r="R99" t="n">
-        <v>7062585</v>
+        <v>7062828</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11398,19 +11428,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11425,19 +11445,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119849903</v>
+        <v>119851251</v>
       </c>
       <c r="B100" t="n">
         <v>90562</v>
@@ -11477,10 +11497,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>608950</v>
+        <v>609099</v>
       </c>
       <c r="R100" t="n">
-        <v>7062709</v>
+        <v>7062948</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11539,10 +11559,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119850562</v>
+        <v>119851047</v>
       </c>
       <c r="B101" t="n">
-        <v>91128</v>
+        <v>97907</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11555,34 +11575,38 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>608992</v>
+        <v>609018</v>
       </c>
       <c r="R101" t="n">
-        <v>7062626</v>
+        <v>7062666</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11614,7 +11638,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11624,7 +11648,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11651,10 +11675,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119850656</v>
+        <v>119851618</v>
       </c>
       <c r="B102" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11663,25 +11687,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11691,13 +11715,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>609048</v>
+        <v>609113</v>
       </c>
       <c r="R102" t="n">
-        <v>7062921</v>
+        <v>7062853</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11753,10 +11777,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119850436</v>
+        <v>119851993</v>
       </c>
       <c r="B103" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11765,25 +11789,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11793,13 +11817,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>609002</v>
+        <v>609135</v>
       </c>
       <c r="R103" t="n">
-        <v>7062810</v>
+        <v>7062752</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11855,10 +11879,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119851251</v>
+        <v>119849742</v>
       </c>
       <c r="B104" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11871,21 +11895,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11895,13 +11919,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>609099</v>
+        <v>608916</v>
       </c>
       <c r="R104" t="n">
-        <v>7062948</v>
+        <v>7062680</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11957,7 +11981,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119851618</v>
+        <v>119849971</v>
       </c>
       <c r="B105" t="n">
         <v>79607</v>
@@ -11997,13 +12021,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>609113</v>
+        <v>608977</v>
       </c>
       <c r="R105" t="n">
-        <v>7062853</v>
+        <v>7062755</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12059,10 +12083,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119850720</v>
+        <v>119851695</v>
       </c>
       <c r="B106" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12071,30 +12095,31 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -12103,13 +12128,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>608957</v>
+        <v>609150</v>
       </c>
       <c r="R106" t="n">
-        <v>7062678</v>
+        <v>7062808</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12136,19 +12161,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12163,22 +12178,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119851413</v>
+        <v>119850411</v>
       </c>
       <c r="B107" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12187,43 +12202,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>609070</v>
+        <v>609003</v>
       </c>
       <c r="R107" t="n">
-        <v>7062653</v>
+        <v>7062803</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12253,19 +12263,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12280,22 +12280,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119850519</v>
+        <v>119851377</v>
       </c>
       <c r="B108" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12304,25 +12304,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12332,10 +12332,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>609012</v>
+        <v>609065</v>
       </c>
       <c r="R108" t="n">
-        <v>7062828</v>
+        <v>7062657</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12365,9 +12365,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12382,22 +12392,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119849971</v>
+        <v>119851274</v>
       </c>
       <c r="B109" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12410,34 +12420,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>608977</v>
+        <v>609039</v>
       </c>
       <c r="R109" t="n">
-        <v>7062755</v>
+        <v>7062654</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12467,9 +12482,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12484,22 +12509,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119849658</v>
+        <v>119849903</v>
       </c>
       <c r="B110" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12512,39 +12537,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>608890</v>
+        <v>608950</v>
       </c>
       <c r="R110" t="n">
-        <v>7062664</v>
+        <v>7062709</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12574,19 +12594,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12601,22 +12611,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119850955</v>
+        <v>120091070</v>
       </c>
       <c r="B111" t="n">
-        <v>79607</v>
+        <v>95775</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12629,37 +12639,41 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>1841</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Skalberget, Skalberget, Ång</t>
+          <t>Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>609006</v>
+        <v>609206</v>
       </c>
       <c r="R111" t="n">
-        <v>7062681</v>
+        <v>7062811</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12683,22 +12697,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-28</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12713,22 +12727,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Martin Bergström</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Martin Bergström</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120091070</v>
+        <v>119849952</v>
       </c>
       <c r="B112" t="n">
-        <v>95775</v>
+        <v>79607</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12741,41 +12755,40 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1841</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Skalberget, Ång</t>
+          <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>609206</v>
+        <v>608976</v>
       </c>
       <c r="R112" t="n">
-        <v>7062811</v>
+        <v>7062742</v>
       </c>
       <c r="S112" t="n">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12799,22 +12812,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-09-28</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>16:40</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12823,18 +12826,19 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Bergström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Bergström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -7334,10 +7334,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119851421</v>
+        <v>119851160</v>
       </c>
       <c r="B61" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7350,37 +7350,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609130</v>
+        <v>609023</v>
       </c>
       <c r="R61" t="n">
-        <v>7062851</v>
+        <v>7062674</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7407,9 +7412,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7424,19 +7439,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119850850</v>
+        <v>119851421</v>
       </c>
       <c r="B62" t="n">
         <v>79607</v>
@@ -7476,13 +7491,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609076</v>
+        <v>609130</v>
       </c>
       <c r="R62" t="n">
-        <v>7062968</v>
+        <v>7062851</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7538,7 +7553,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119851802</v>
+        <v>119850850</v>
       </c>
       <c r="B63" t="n">
         <v>79607</v>
@@ -7578,10 +7593,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609143</v>
+        <v>609076</v>
       </c>
       <c r="R63" t="n">
-        <v>7062799</v>
+        <v>7062968</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7640,10 +7655,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119851160</v>
+        <v>119851802</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7656,39 +7671,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609023</v>
+        <v>609143</v>
       </c>
       <c r="R64" t="n">
-        <v>7062674</v>
+        <v>7062799</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7718,19 +7728,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7745,22 +7745,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119850752</v>
+        <v>119851104</v>
       </c>
       <c r="B65" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7769,25 +7769,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7797,13 +7797,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609068</v>
+        <v>609085</v>
       </c>
       <c r="R65" t="n">
-        <v>7062927</v>
+        <v>7062996</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7827,12 +7827,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7864,7 +7864,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119850568</v>
+        <v>119850752</v>
       </c>
       <c r="B66" t="n">
         <v>97907</v>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609033</v>
+        <v>609068</v>
       </c>
       <c r="R66" t="n">
-        <v>7062884</v>
+        <v>7062927</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7934,12 +7934,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,7 +7971,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119849740</v>
+        <v>119850568</v>
       </c>
       <c r="B67" t="n">
         <v>97907</v>
@@ -7999,21 +8004,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>608907</v>
+        <v>609033</v>
       </c>
       <c r="R67" t="n">
-        <v>7062655</v>
+        <v>7062884</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8043,19 +8044,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8070,22 +8061,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119851104</v>
+        <v>119849740</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8094,41 +8085,45 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>609085</v>
+        <v>608907</v>
       </c>
       <c r="R68" t="n">
-        <v>7062996</v>
+        <v>7062655</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8155,14 +8150,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8177,12 +8177,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -10947,10 +10947,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119851973</v>
+        <v>119850188</v>
       </c>
       <c r="B95" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10959,25 +10959,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>609151</v>
+        <v>608997</v>
       </c>
       <c r="R95" t="n">
-        <v>7062747</v>
+        <v>7062738</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119851732</v>
+        <v>119851973</v>
       </c>
       <c r="B96" t="n">
         <v>79607</v>
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>609149</v>
+        <v>609151</v>
       </c>
       <c r="R96" t="n">
-        <v>7062808</v>
+        <v>7062747</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11151,10 +11151,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119850188</v>
+        <v>119851732</v>
       </c>
       <c r="B97" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11163,25 +11163,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11191,13 +11191,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>608997</v>
+        <v>609149</v>
       </c>
       <c r="R97" t="n">
-        <v>7062738</v>
+        <v>7062808</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11981,10 +11981,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119849971</v>
+        <v>119851695</v>
       </c>
       <c r="B105" t="n">
-        <v>79607</v>
+        <v>57463</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11997,37 +11997,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>608977</v>
+        <v>609150</v>
       </c>
       <c r="R105" t="n">
-        <v>7062755</v>
+        <v>7062808</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12083,10 +12088,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119851695</v>
+        <v>119850411</v>
       </c>
       <c r="B106" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12095,46 +12100,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>609150</v>
+        <v>609003</v>
       </c>
       <c r="R106" t="n">
-        <v>7062808</v>
+        <v>7062803</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12190,10 +12190,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119850411</v>
+        <v>119849971</v>
       </c>
       <c r="B107" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12202,25 +12202,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12230,10 +12230,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>609003</v>
+        <v>608977</v>
       </c>
       <c r="R107" t="n">
-        <v>7062803</v>
+        <v>7062755</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12292,10 +12292,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119851377</v>
+        <v>119851274</v>
       </c>
       <c r="B108" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12308,34 +12308,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>609065</v>
+        <v>609039</v>
       </c>
       <c r="R108" t="n">
-        <v>7062657</v>
+        <v>7062654</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12367,7 +12372,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12377,7 +12382,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12404,10 +12409,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119851274</v>
+        <v>119849903</v>
       </c>
       <c r="B109" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12420,39 +12425,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>609039</v>
+        <v>608950</v>
       </c>
       <c r="R109" t="n">
-        <v>7062654</v>
+        <v>7062709</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12482,19 +12482,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12509,22 +12499,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119849903</v>
+        <v>119851377</v>
       </c>
       <c r="B110" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12537,21 +12527,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12561,10 +12551,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>608950</v>
+        <v>609065</v>
       </c>
       <c r="R110" t="n">
-        <v>7062709</v>
+        <v>7062657</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12594,9 +12584,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12611,12 +12611,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -7757,10 +7757,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119851104</v>
+        <v>119850752</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7769,25 +7769,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7797,13 +7797,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609085</v>
+        <v>609068</v>
       </c>
       <c r="R65" t="n">
-        <v>7062996</v>
+        <v>7062927</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7827,12 +7827,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7864,7 +7864,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119850752</v>
+        <v>119850568</v>
       </c>
       <c r="B66" t="n">
         <v>97907</v>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609068</v>
+        <v>609033</v>
       </c>
       <c r="R66" t="n">
-        <v>7062927</v>
+        <v>7062884</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7934,17 +7934,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7971,7 +7966,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119850568</v>
+        <v>119849740</v>
       </c>
       <c r="B67" t="n">
         <v>97907</v>
@@ -8004,17 +7999,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>609033</v>
+        <v>608907</v>
       </c>
       <c r="R67" t="n">
-        <v>7062884</v>
+        <v>7062655</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8044,9 +8043,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8061,22 +8070,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119849740</v>
+        <v>119851104</v>
       </c>
       <c r="B68" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8085,45 +8094,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>608907</v>
+        <v>609085</v>
       </c>
       <c r="R68" t="n">
-        <v>7062655</v>
+        <v>7062996</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8150,19 +8155,14 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:22</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8177,12 +8177,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -10947,10 +10947,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119850188</v>
+        <v>119851973</v>
       </c>
       <c r="B95" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10959,25 +10959,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>608997</v>
+        <v>609151</v>
       </c>
       <c r="R95" t="n">
-        <v>7062738</v>
+        <v>7062747</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119851973</v>
+        <v>119851732</v>
       </c>
       <c r="B96" t="n">
         <v>79607</v>
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>609151</v>
+        <v>609149</v>
       </c>
       <c r="R96" t="n">
-        <v>7062747</v>
+        <v>7062808</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11151,10 +11151,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119851732</v>
+        <v>119850188</v>
       </c>
       <c r="B97" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11163,25 +11163,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11191,13 +11191,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>609149</v>
+        <v>608997</v>
       </c>
       <c r="R97" t="n">
-        <v>7062808</v>
+        <v>7062738</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11253,10 +11253,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119851361</v>
+        <v>119851047</v>
       </c>
       <c r="B98" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11265,41 +11265,45 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>609100</v>
+        <v>609018</v>
       </c>
       <c r="R98" t="n">
-        <v>7062937</v>
+        <v>7062666</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11323,12 +11327,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11343,19 +11357,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119851684</v>
+        <v>119851361</v>
       </c>
       <c r="B99" t="n">
         <v>79607</v>
@@ -11395,10 +11409,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>609149</v>
+        <v>609100</v>
       </c>
       <c r="R99" t="n">
-        <v>7062828</v>
+        <v>7062937</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11425,12 +11439,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11457,10 +11471,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119851251</v>
+        <v>119851684</v>
       </c>
       <c r="B100" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11473,21 +11487,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11497,13 +11511,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>609099</v>
+        <v>609149</v>
       </c>
       <c r="R100" t="n">
-        <v>7062948</v>
+        <v>7062828</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11559,10 +11573,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119851047</v>
+        <v>119851251</v>
       </c>
       <c r="B101" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11571,42 +11585,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>609018</v>
+        <v>609099</v>
       </c>
       <c r="R101" t="n">
-        <v>7062666</v>
+        <v>7062948</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11636,19 +11646,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11663,12 +11663,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11981,10 +11981,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119851695</v>
+        <v>119849971</v>
       </c>
       <c r="B105" t="n">
-        <v>57463</v>
+        <v>79607</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11997,42 +11997,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>609150</v>
+        <v>608977</v>
       </c>
       <c r="R105" t="n">
-        <v>7062808</v>
+        <v>7062755</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12088,10 +12083,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119850411</v>
+        <v>119851695</v>
       </c>
       <c r="B106" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12100,41 +12095,46 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>609003</v>
+        <v>609150</v>
       </c>
       <c r="R106" t="n">
-        <v>7062803</v>
+        <v>7062808</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12190,10 +12190,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119849971</v>
+        <v>119850411</v>
       </c>
       <c r="B107" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12202,25 +12202,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12230,10 +12230,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>608977</v>
+        <v>609003</v>
       </c>
       <c r="R107" t="n">
-        <v>7062755</v>
+        <v>7062803</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12292,10 +12292,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119851274</v>
+        <v>119851377</v>
       </c>
       <c r="B108" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12308,39 +12308,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>609039</v>
+        <v>609065</v>
       </c>
       <c r="R108" t="n">
-        <v>7062654</v>
+        <v>7062657</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12372,7 +12367,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12382,7 +12377,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12409,10 +12404,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119849903</v>
+        <v>119851274</v>
       </c>
       <c r="B109" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12425,34 +12420,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>608950</v>
+        <v>609039</v>
       </c>
       <c r="R109" t="n">
-        <v>7062709</v>
+        <v>7062654</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12482,9 +12482,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12499,22 +12509,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119851377</v>
+        <v>119849903</v>
       </c>
       <c r="B110" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12527,21 +12537,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12551,10 +12561,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>609065</v>
+        <v>608950</v>
       </c>
       <c r="R110" t="n">
-        <v>7062657</v>
+        <v>7062709</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12584,19 +12594,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12611,12 +12611,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -5594,10 +5594,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119850926</v>
+        <v>119851861</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5610,42 +5610,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>609003</v>
+        <v>609153</v>
       </c>
       <c r="R45" t="n">
-        <v>7062700</v>
+        <v>7062783</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5672,19 +5667,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5699,22 +5684,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119849755</v>
+        <v>119850834</v>
       </c>
       <c r="B46" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5727,21 +5712,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5751,10 +5736,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>608914</v>
+        <v>609080</v>
       </c>
       <c r="R46" t="n">
-        <v>7062689</v>
+        <v>7062946</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5813,10 +5798,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119851861</v>
+        <v>119850876</v>
       </c>
       <c r="B47" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5829,21 +5814,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5853,13 +5838,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>609153</v>
+        <v>609066</v>
       </c>
       <c r="R47" t="n">
-        <v>7062783</v>
+        <v>7062980</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5915,10 +5900,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119850834</v>
+        <v>119849905</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>90582</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5931,21 +5916,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5955,13 +5940,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609080</v>
+        <v>608876</v>
       </c>
       <c r="R48" t="n">
-        <v>7062946</v>
+        <v>7062635</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5988,9 +5973,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6005,22 +6000,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119850876</v>
+        <v>119850926</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6033,37 +6028,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609066</v>
+        <v>609003</v>
       </c>
       <c r="R49" t="n">
-        <v>7062980</v>
+        <v>7062700</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6090,9 +6090,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6107,22 +6117,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119849973</v>
+        <v>119849755</v>
       </c>
       <c r="B50" t="n">
-        <v>79636</v>
+        <v>90562</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6131,25 +6141,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6159,10 +6169,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>608986</v>
+        <v>608914</v>
       </c>
       <c r="R50" t="n">
-        <v>7062749</v>
+        <v>7062689</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6221,10 +6231,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119849905</v>
+        <v>119849973</v>
       </c>
       <c r="B51" t="n">
-        <v>90582</v>
+        <v>79636</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6233,25 +6243,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6261,13 +6271,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>608876</v>
+        <v>608986</v>
       </c>
       <c r="R51" t="n">
-        <v>7062635</v>
+        <v>7062749</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6294,19 +6304,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6321,22 +6321,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119851950</v>
+        <v>119850096</v>
       </c>
       <c r="B52" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6345,41 +6345,45 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>609160</v>
+        <v>608905</v>
       </c>
       <c r="R52" t="n">
-        <v>7062762</v>
+        <v>7062586</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6406,9 +6410,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6423,22 +6437,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119851413</v>
+        <v>119850720</v>
       </c>
       <c r="B53" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6447,31 +6461,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6480,10 +6493,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>609070</v>
+        <v>608957</v>
       </c>
       <c r="R53" t="n">
-        <v>7062653</v>
+        <v>7062678</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6515,7 +6528,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6525,7 +6538,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6552,10 +6565,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119849717</v>
+        <v>119851950</v>
       </c>
       <c r="B54" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6568,21 +6581,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6592,13 +6605,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>608896</v>
+        <v>609160</v>
       </c>
       <c r="R54" t="n">
-        <v>7062656</v>
+        <v>7062762</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6625,24 +6638,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6657,22 +6655,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119850096</v>
+        <v>119851413</v>
       </c>
       <c r="B55" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6681,30 +6679,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6713,10 +6712,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>608905</v>
+        <v>609070</v>
       </c>
       <c r="R55" t="n">
-        <v>7062586</v>
+        <v>7062653</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6748,7 +6747,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6758,7 +6757,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6785,10 +6784,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119850720</v>
+        <v>119849717</v>
       </c>
       <c r="B56" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6797,42 +6796,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>608957</v>
+        <v>608896</v>
       </c>
       <c r="R56" t="n">
-        <v>7062678</v>
+        <v>7062656</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6864,7 +6859,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6874,7 +6869,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7334,10 +7334,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119851160</v>
+        <v>119851421</v>
       </c>
       <c r="B61" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7350,42 +7350,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609023</v>
+        <v>609130</v>
       </c>
       <c r="R61" t="n">
-        <v>7062674</v>
+        <v>7062851</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7412,19 +7407,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7439,19 +7424,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119851421</v>
+        <v>119850850</v>
       </c>
       <c r="B62" t="n">
         <v>79607</v>
@@ -7491,13 +7476,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609130</v>
+        <v>609076</v>
       </c>
       <c r="R62" t="n">
-        <v>7062851</v>
+        <v>7062968</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7553,7 +7538,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119850850</v>
+        <v>119851802</v>
       </c>
       <c r="B63" t="n">
         <v>79607</v>
@@ -7593,10 +7578,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609076</v>
+        <v>609143</v>
       </c>
       <c r="R63" t="n">
-        <v>7062968</v>
+        <v>7062799</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7655,10 +7640,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119851802</v>
+        <v>119851160</v>
       </c>
       <c r="B64" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7671,34 +7656,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609143</v>
+        <v>609023</v>
       </c>
       <c r="R64" t="n">
-        <v>7062799</v>
+        <v>7062674</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7728,9 +7718,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7745,12 +7745,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119849708</v>
+        <v>119850321</v>
       </c>
       <c r="B86" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10007,21 +10007,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10031,13 +10031,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>608910</v>
+        <v>609015</v>
       </c>
       <c r="R86" t="n">
-        <v>7062662</v>
+        <v>7062798</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10093,10 +10093,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119850321</v>
+        <v>119849708</v>
       </c>
       <c r="B87" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10109,21 +10109,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10133,13 +10133,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>609015</v>
+        <v>608910</v>
       </c>
       <c r="R87" t="n">
-        <v>7062798</v>
+        <v>7062662</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10947,10 +10947,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119851973</v>
+        <v>119850188</v>
       </c>
       <c r="B95" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10959,25 +10959,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>609151</v>
+        <v>608997</v>
       </c>
       <c r="R95" t="n">
-        <v>7062747</v>
+        <v>7062738</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11049,7 +11049,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119851732</v>
+        <v>119851973</v>
       </c>
       <c r="B96" t="n">
         <v>79607</v>
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>609149</v>
+        <v>609151</v>
       </c>
       <c r="R96" t="n">
-        <v>7062808</v>
+        <v>7062747</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11151,10 +11151,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119850188</v>
+        <v>119851732</v>
       </c>
       <c r="B97" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11163,25 +11163,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11191,13 +11191,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>608997</v>
+        <v>609149</v>
       </c>
       <c r="R97" t="n">
-        <v>7062738</v>
+        <v>7062808</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11253,10 +11253,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119851047</v>
+        <v>119851361</v>
       </c>
       <c r="B98" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11265,45 +11265,41 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>609018</v>
+        <v>609100</v>
       </c>
       <c r="R98" t="n">
-        <v>7062666</v>
+        <v>7062937</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11327,22 +11323,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>14:45</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11357,19 +11343,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119851361</v>
+        <v>119851684</v>
       </c>
       <c r="B99" t="n">
         <v>79607</v>
@@ -11409,10 +11395,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>609100</v>
+        <v>609149</v>
       </c>
       <c r="R99" t="n">
-        <v>7062937</v>
+        <v>7062828</v>
       </c>
       <c r="S99" t="n">
         <v>15</v>
@@ -11439,12 +11425,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11471,10 +11457,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119851684</v>
+        <v>119851251</v>
       </c>
       <c r="B100" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11487,21 +11473,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11511,13 +11497,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>609149</v>
+        <v>609099</v>
       </c>
       <c r="R100" t="n">
-        <v>7062828</v>
+        <v>7062948</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11573,10 +11559,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119851251</v>
+        <v>119851047</v>
       </c>
       <c r="B101" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11585,38 +11571,42 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>609099</v>
+        <v>609018</v>
       </c>
       <c r="R101" t="n">
-        <v>7062948</v>
+        <v>7062666</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11646,9 +11636,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11663,12 +11663,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -11981,10 +11981,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119849971</v>
+        <v>119851695</v>
       </c>
       <c r="B105" t="n">
-        <v>79607</v>
+        <v>57463</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11997,37 +11997,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>608977</v>
+        <v>609150</v>
       </c>
       <c r="R105" t="n">
-        <v>7062755</v>
+        <v>7062808</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12083,10 +12088,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119851695</v>
+        <v>119850411</v>
       </c>
       <c r="B106" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12095,46 +12100,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>609150</v>
+        <v>609003</v>
       </c>
       <c r="R106" t="n">
-        <v>7062808</v>
+        <v>7062803</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12190,10 +12190,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119850411</v>
+        <v>119849971</v>
       </c>
       <c r="B107" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12202,25 +12202,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12230,10 +12230,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>609003</v>
+        <v>608977</v>
       </c>
       <c r="R107" t="n">
-        <v>7062803</v>
+        <v>7062755</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -7757,10 +7757,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119850752</v>
+        <v>119851104</v>
       </c>
       <c r="B65" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7769,25 +7769,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7797,13 +7797,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609068</v>
+        <v>609085</v>
       </c>
       <c r="R65" t="n">
-        <v>7062927</v>
+        <v>7062996</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7827,12 +7827,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7864,7 +7864,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119850568</v>
+        <v>119850752</v>
       </c>
       <c r="B66" t="n">
         <v>97907</v>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609033</v>
+        <v>609068</v>
       </c>
       <c r="R66" t="n">
-        <v>7062884</v>
+        <v>7062927</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7934,12 +7934,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7966,7 +7971,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119849740</v>
+        <v>119850568</v>
       </c>
       <c r="B67" t="n">
         <v>97907</v>
@@ -7999,21 +8004,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>608907</v>
+        <v>609033</v>
       </c>
       <c r="R67" t="n">
-        <v>7062655</v>
+        <v>7062884</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8043,19 +8044,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8070,22 +8061,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119851104</v>
+        <v>119849740</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8094,41 +8085,45 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>609085</v>
+        <v>608907</v>
       </c>
       <c r="R68" t="n">
-        <v>7062996</v>
+        <v>7062655</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8155,14 +8150,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8177,12 +8177,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -9141,10 +9141,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119851641</v>
+        <v>119850006</v>
       </c>
       <c r="B78" t="n">
-        <v>79643</v>
+        <v>79607</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9153,25 +9153,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>609109</v>
+        <v>609003</v>
       </c>
       <c r="R78" t="n">
-        <v>7062833</v>
+        <v>7062728</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -9243,7 +9243,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119850006</v>
+        <v>119852025</v>
       </c>
       <c r="B79" t="n">
         <v>79607</v>
@@ -9283,13 +9283,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>609003</v>
+        <v>609136</v>
       </c>
       <c r="R79" t="n">
-        <v>7062728</v>
+        <v>7062753</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9345,10 +9345,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119852025</v>
+        <v>119851641</v>
       </c>
       <c r="B80" t="n">
-        <v>79607</v>
+        <v>79643</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9357,25 +9357,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9385,13 +9385,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>609136</v>
+        <v>609109</v>
       </c>
       <c r="R80" t="n">
-        <v>7062753</v>
+        <v>7062833</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119850321</v>
+        <v>119849708</v>
       </c>
       <c r="B86" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10007,21 +10007,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10031,13 +10031,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>609015</v>
+        <v>608910</v>
       </c>
       <c r="R86" t="n">
-        <v>7062798</v>
+        <v>7062662</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10093,10 +10093,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119849708</v>
+        <v>119850321</v>
       </c>
       <c r="B87" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10109,21 +10109,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10133,13 +10133,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>608910</v>
+        <v>609015</v>
       </c>
       <c r="R87" t="n">
-        <v>7062662</v>
+        <v>7062798</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -11981,10 +11981,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119851695</v>
+        <v>119849971</v>
       </c>
       <c r="B105" t="n">
-        <v>57463</v>
+        <v>79607</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11997,42 +11997,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>609150</v>
+        <v>608977</v>
       </c>
       <c r="R105" t="n">
-        <v>7062808</v>
+        <v>7062755</v>
       </c>
       <c r="S105" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12088,10 +12083,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119850411</v>
+        <v>119851695</v>
       </c>
       <c r="B106" t="n">
-        <v>97907</v>
+        <v>57463</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12100,41 +12095,46 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>609003</v>
+        <v>609150</v>
       </c>
       <c r="R106" t="n">
-        <v>7062803</v>
+        <v>7062808</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12190,10 +12190,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119849971</v>
+        <v>119850411</v>
       </c>
       <c r="B107" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12202,25 +12202,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12230,10 +12230,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>608977</v>
+        <v>609003</v>
       </c>
       <c r="R107" t="n">
-        <v>7062755</v>
+        <v>7062803</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12292,10 +12292,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119851377</v>
+        <v>119851274</v>
       </c>
       <c r="B108" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12308,34 +12308,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>609065</v>
+        <v>609039</v>
       </c>
       <c r="R108" t="n">
-        <v>7062657</v>
+        <v>7062654</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12367,7 +12372,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12377,7 +12382,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12404,10 +12409,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119851274</v>
+        <v>119849903</v>
       </c>
       <c r="B109" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12420,39 +12425,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>609039</v>
+        <v>608950</v>
       </c>
       <c r="R109" t="n">
-        <v>7062654</v>
+        <v>7062709</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12482,19 +12482,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12509,22 +12499,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119849903</v>
+        <v>119851377</v>
       </c>
       <c r="B110" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12537,21 +12527,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12561,10 +12551,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>608950</v>
+        <v>609065</v>
       </c>
       <c r="R110" t="n">
-        <v>7062709</v>
+        <v>7062657</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12594,9 +12584,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12611,12 +12611,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -7334,10 +7334,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119851421</v>
+        <v>119851160</v>
       </c>
       <c r="B61" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7350,37 +7350,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609130</v>
+        <v>609023</v>
       </c>
       <c r="R61" t="n">
-        <v>7062851</v>
+        <v>7062674</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7407,9 +7412,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7424,19 +7439,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119850850</v>
+        <v>119851421</v>
       </c>
       <c r="B62" t="n">
         <v>79607</v>
@@ -7476,13 +7491,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609076</v>
+        <v>609130</v>
       </c>
       <c r="R62" t="n">
-        <v>7062968</v>
+        <v>7062851</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7538,7 +7553,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119851802</v>
+        <v>119850850</v>
       </c>
       <c r="B63" t="n">
         <v>79607</v>
@@ -7578,10 +7593,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609143</v>
+        <v>609076</v>
       </c>
       <c r="R63" t="n">
-        <v>7062799</v>
+        <v>7062968</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7640,10 +7655,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119851160</v>
+        <v>119851802</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7656,39 +7671,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609023</v>
+        <v>609143</v>
       </c>
       <c r="R64" t="n">
-        <v>7062674</v>
+        <v>7062799</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7718,19 +7728,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7745,22 +7745,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119851104</v>
+        <v>119850752</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7769,25 +7769,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7797,13 +7797,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609085</v>
+        <v>609068</v>
       </c>
       <c r="R65" t="n">
-        <v>7062996</v>
+        <v>7062927</v>
       </c>
       <c r="S65" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7827,12 +7827,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7864,7 +7864,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119850752</v>
+        <v>119850568</v>
       </c>
       <c r="B66" t="n">
         <v>97907</v>
@@ -7904,10 +7904,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609068</v>
+        <v>609033</v>
       </c>
       <c r="R66" t="n">
-        <v>7062927</v>
+        <v>7062884</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7934,17 +7934,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7971,7 +7966,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119850568</v>
+        <v>119849740</v>
       </c>
       <c r="B67" t="n">
         <v>97907</v>
@@ -8004,17 +7999,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>609033</v>
+        <v>608907</v>
       </c>
       <c r="R67" t="n">
-        <v>7062884</v>
+        <v>7062655</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8044,9 +8043,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8061,22 +8070,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119849740</v>
+        <v>119851104</v>
       </c>
       <c r="B68" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8085,45 +8094,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>608907</v>
+        <v>609085</v>
       </c>
       <c r="R68" t="n">
-        <v>7062655</v>
+        <v>7062996</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8150,19 +8155,14 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>13:22</t>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8177,12 +8177,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -5594,10 +5594,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119851861</v>
+        <v>119850926</v>
       </c>
       <c r="B45" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5610,37 +5610,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>609153</v>
+        <v>609003</v>
       </c>
       <c r="R45" t="n">
-        <v>7062783</v>
+        <v>7062700</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5667,9 +5672,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5684,22 +5699,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119850834</v>
+        <v>119849755</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>90562</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5712,21 +5727,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5736,10 +5751,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>609080</v>
+        <v>608914</v>
       </c>
       <c r="R46" t="n">
-        <v>7062946</v>
+        <v>7062689</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5798,10 +5813,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119850876</v>
+        <v>119851861</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5814,21 +5829,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5838,13 +5853,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>609066</v>
+        <v>609153</v>
       </c>
       <c r="R47" t="n">
-        <v>7062980</v>
+        <v>7062783</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5900,10 +5915,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119849905</v>
+        <v>119850834</v>
       </c>
       <c r="B48" t="n">
-        <v>90582</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5916,21 +5931,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5940,13 +5955,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>608876</v>
+        <v>609080</v>
       </c>
       <c r="R48" t="n">
-        <v>7062635</v>
+        <v>7062946</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5973,19 +5988,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6000,22 +6005,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119850926</v>
+        <v>119850876</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6028,42 +6033,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609003</v>
+        <v>609066</v>
       </c>
       <c r="R49" t="n">
-        <v>7062700</v>
+        <v>7062980</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6090,19 +6090,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:35</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6117,22 +6107,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119849755</v>
+        <v>119849973</v>
       </c>
       <c r="B50" t="n">
-        <v>90562</v>
+        <v>79636</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6141,25 +6131,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6169,10 +6159,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>608914</v>
+        <v>608986</v>
       </c>
       <c r="R50" t="n">
-        <v>7062689</v>
+        <v>7062749</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6231,10 +6221,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119849973</v>
+        <v>119849905</v>
       </c>
       <c r="B51" t="n">
-        <v>79636</v>
+        <v>90582</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6243,25 +6233,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6271,13 +6261,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>608986</v>
+        <v>608876</v>
       </c>
       <c r="R51" t="n">
-        <v>7062749</v>
+        <v>7062635</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6304,9 +6294,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6321,12 +6321,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -7334,10 +7334,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119851160</v>
+        <v>119851421</v>
       </c>
       <c r="B61" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7350,42 +7350,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609023</v>
+        <v>609130</v>
       </c>
       <c r="R61" t="n">
-        <v>7062674</v>
+        <v>7062851</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7412,19 +7407,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7439,19 +7424,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119851421</v>
+        <v>119850850</v>
       </c>
       <c r="B62" t="n">
         <v>79607</v>
@@ -7491,13 +7476,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609130</v>
+        <v>609076</v>
       </c>
       <c r="R62" t="n">
-        <v>7062851</v>
+        <v>7062968</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7553,7 +7538,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119850850</v>
+        <v>119851802</v>
       </c>
       <c r="B63" t="n">
         <v>79607</v>
@@ -7593,10 +7578,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609076</v>
+        <v>609143</v>
       </c>
       <c r="R63" t="n">
-        <v>7062968</v>
+        <v>7062799</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7655,10 +7640,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119851802</v>
+        <v>119851160</v>
       </c>
       <c r="B64" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7671,34 +7656,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609143</v>
+        <v>609023</v>
       </c>
       <c r="R64" t="n">
-        <v>7062799</v>
+        <v>7062674</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7728,9 +7718,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7745,12 +7745,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -9991,10 +9991,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119849708</v>
+        <v>119850321</v>
       </c>
       <c r="B86" t="n">
-        <v>90846</v>
+        <v>79607</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10007,21 +10007,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10031,13 +10031,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>608910</v>
+        <v>609015</v>
       </c>
       <c r="R86" t="n">
-        <v>7062662</v>
+        <v>7062798</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10093,10 +10093,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119850321</v>
+        <v>119849708</v>
       </c>
       <c r="B87" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10109,21 +10109,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10133,13 +10133,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>609015</v>
+        <v>608910</v>
       </c>
       <c r="R87" t="n">
-        <v>7062798</v>
+        <v>7062662</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -5390,10 +5390,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119850220</v>
+        <v>119850876</v>
       </c>
       <c r="B43" t="n">
-        <v>90562</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5406,21 +5406,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5430,13 +5430,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>608994</v>
+        <v>609066</v>
       </c>
       <c r="R43" t="n">
-        <v>7062775</v>
+        <v>7062980</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5460,12 +5460,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5492,10 +5492,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119851185</v>
+        <v>119851695</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>57473</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5504,41 +5504,46 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>609097</v>
+        <v>609150</v>
       </c>
       <c r="R44" t="n">
-        <v>7062964</v>
+        <v>7062808</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5562,12 +5567,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5597,7 +5602,7 @@
         <v>119850926</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5711,10 +5716,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119849755</v>
+        <v>119850188</v>
       </c>
       <c r="B46" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5723,25 +5728,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5751,10 +5756,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>608914</v>
+        <v>608997</v>
       </c>
       <c r="R46" t="n">
-        <v>7062689</v>
+        <v>7062738</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5813,10 +5818,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119851861</v>
+        <v>119851047</v>
       </c>
       <c r="B47" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5825,41 +5830,45 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>609153</v>
+        <v>609018</v>
       </c>
       <c r="R47" t="n">
-        <v>7062783</v>
+        <v>7062666</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5886,9 +5895,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5903,22 +5922,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119850834</v>
+        <v>119849858</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5927,41 +5946,45 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609080</v>
+        <v>608877</v>
       </c>
       <c r="R48" t="n">
-        <v>7062946</v>
+        <v>7062639</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5988,9 +6011,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6005,22 +6038,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119850876</v>
+        <v>119849721</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6033,21 +6066,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6057,13 +6090,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609066</v>
+        <v>608918</v>
       </c>
       <c r="R49" t="n">
-        <v>7062980</v>
+        <v>7062673</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6119,10 +6152,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119849973</v>
+        <v>119851306</v>
       </c>
       <c r="B50" t="n">
-        <v>79636</v>
+        <v>97930</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6131,41 +6164,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>608986</v>
+        <v>609039</v>
       </c>
       <c r="R50" t="n">
-        <v>7062749</v>
+        <v>7062664</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6192,9 +6229,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6209,22 +6256,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119849905</v>
+        <v>119851413</v>
       </c>
       <c r="B51" t="n">
-        <v>90582</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6237,34 +6284,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>608876</v>
+        <v>609070</v>
       </c>
       <c r="R51" t="n">
-        <v>7062635</v>
+        <v>7062653</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6296,7 +6348,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6306,7 +6358,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6333,10 +6385,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119850096</v>
+        <v>119850459</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6345,30 +6397,31 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6377,10 +6430,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>608905</v>
+        <v>608949</v>
       </c>
       <c r="R52" t="n">
-        <v>7062586</v>
+        <v>7062585</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6412,7 +6465,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6422,7 +6475,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6449,10 +6502,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119850720</v>
+        <v>119849966</v>
       </c>
       <c r="B53" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6493,10 +6546,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>608957</v>
+        <v>608853</v>
       </c>
       <c r="R53" t="n">
-        <v>7062678</v>
+        <v>7062579</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6528,7 +6581,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6538,7 +6591,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6565,10 +6618,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119851950</v>
+        <v>119851377</v>
       </c>
       <c r="B54" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6605,13 +6658,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609160</v>
+        <v>609065</v>
       </c>
       <c r="R54" t="n">
-        <v>7062762</v>
+        <v>7062657</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6638,9 +6691,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6655,22 +6718,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119851413</v>
+        <v>119850568</v>
       </c>
       <c r="B55" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6679,43 +6742,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609070</v>
+        <v>609033</v>
       </c>
       <c r="R55" t="n">
-        <v>7062653</v>
+        <v>7062884</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6745,19 +6803,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6772,12 +6820,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6787,7 +6835,7 @@
         <v>119849717</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6901,10 +6949,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119850562</v>
+        <v>119849708</v>
       </c>
       <c r="B57" t="n">
-        <v>91128</v>
+        <v>90864</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6913,25 +6961,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>760</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6941,10 +6989,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>608992</v>
+        <v>608910</v>
       </c>
       <c r="R57" t="n">
-        <v>7062626</v>
+        <v>7062662</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6974,19 +7022,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7001,22 +7039,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119850459</v>
+        <v>119851361</v>
       </c>
       <c r="B58" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7029,42 +7067,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>608949</v>
+        <v>609100</v>
       </c>
       <c r="R58" t="n">
-        <v>7062585</v>
+        <v>7062937</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7088,22 +7121,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7118,22 +7141,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119850436</v>
+        <v>119850562</v>
       </c>
       <c r="B59" t="n">
-        <v>97907</v>
+        <v>91146</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7146,21 +7169,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7170,13 +7193,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>609002</v>
+        <v>608992</v>
       </c>
       <c r="R59" t="n">
-        <v>7062810</v>
+        <v>7062626</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7203,9 +7226,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7220,22 +7253,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119851235</v>
+        <v>119851861</v>
       </c>
       <c r="B60" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7244,25 +7277,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7272,13 +7305,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>609101</v>
+        <v>609153</v>
       </c>
       <c r="R60" t="n">
-        <v>7062955</v>
+        <v>7062783</v>
       </c>
       <c r="S60" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7334,10 +7367,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119851421</v>
+        <v>119850850</v>
       </c>
       <c r="B61" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7374,13 +7407,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609130</v>
+        <v>609076</v>
       </c>
       <c r="R61" t="n">
-        <v>7062851</v>
+        <v>7062968</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7436,10 +7469,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119850850</v>
+        <v>119850006</v>
       </c>
       <c r="B62" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7476,13 +7509,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609076</v>
+        <v>609003</v>
       </c>
       <c r="R62" t="n">
-        <v>7062968</v>
+        <v>7062728</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7538,10 +7571,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119851802</v>
+        <v>119850834</v>
       </c>
       <c r="B63" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7554,21 +7587,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7578,13 +7611,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609143</v>
+        <v>609080</v>
       </c>
       <c r="R63" t="n">
-        <v>7062799</v>
+        <v>7062946</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7640,10 +7673,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119851160</v>
+        <v>119850752</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7652,43 +7685,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609023</v>
+        <v>609068</v>
       </c>
       <c r="R64" t="n">
-        <v>7062674</v>
+        <v>7062927</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7715,22 +7743,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7745,22 +7768,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119850752</v>
+        <v>119849724</v>
       </c>
       <c r="B65" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7769,25 +7792,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7797,10 +7820,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609068</v>
+        <v>608908</v>
       </c>
       <c r="R65" t="n">
-        <v>7062927</v>
+        <v>7062658</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7827,17 +7850,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7852,22 +7880,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119850568</v>
+        <v>119850782</v>
       </c>
       <c r="B66" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7897,17 +7925,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>609033</v>
+        <v>608954</v>
       </c>
       <c r="R66" t="n">
-        <v>7062884</v>
+        <v>7062685</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7937,9 +7969,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7954,22 +7996,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119849740</v>
+        <v>119851950</v>
       </c>
       <c r="B67" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7978,45 +8020,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>608907</v>
+        <v>609160</v>
       </c>
       <c r="R67" t="n">
-        <v>7062655</v>
+        <v>7062762</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8043,19 +8081,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8070,22 +8098,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119851104</v>
+        <v>119850220</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8098,21 +8126,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8122,13 +8150,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>609085</v>
+        <v>608994</v>
       </c>
       <c r="R68" t="n">
-        <v>7062996</v>
+        <v>7062775</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8152,17 +8180,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8189,10 +8212,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119849829</v>
+        <v>119851973</v>
       </c>
       <c r="B69" t="n">
-        <v>90562</v>
+        <v>79623</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8205,21 +8228,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8229,10 +8252,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>608941</v>
+        <v>609151</v>
       </c>
       <c r="R69" t="n">
-        <v>7062708</v>
+        <v>7062747</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8291,10 +8314,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119852068</v>
+        <v>119851421</v>
       </c>
       <c r="B70" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8331,13 +8354,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>609119</v>
+        <v>609130</v>
       </c>
       <c r="R70" t="n">
-        <v>7062737</v>
+        <v>7062851</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8393,10 +8416,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119851664</v>
+        <v>119850321</v>
       </c>
       <c r="B71" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8433,13 +8456,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609125</v>
+        <v>609015</v>
       </c>
       <c r="R71" t="n">
-        <v>7062827</v>
+        <v>7062798</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8495,10 +8518,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119851290</v>
+        <v>119851732</v>
       </c>
       <c r="B72" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8535,10 +8558,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>609054</v>
+        <v>609149</v>
       </c>
       <c r="R72" t="n">
-        <v>7062684</v>
+        <v>7062808</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8568,19 +8591,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8595,22 +8608,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119850519</v>
+        <v>119851160</v>
       </c>
       <c r="B73" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8619,38 +8632,43 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>609012</v>
+        <v>609023</v>
       </c>
       <c r="R73" t="n">
-        <v>7062828</v>
+        <v>7062674</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8680,9 +8698,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8697,22 +8725,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119850955</v>
+        <v>119850096</v>
       </c>
       <c r="B74" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8721,38 +8749,42 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>609006</v>
+        <v>608905</v>
       </c>
       <c r="R74" t="n">
-        <v>7062681</v>
+        <v>7062586</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8784,7 +8816,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8794,7 +8826,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8821,10 +8853,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119851878</v>
+        <v>119850955</v>
       </c>
       <c r="B75" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8861,10 +8893,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>609153</v>
+        <v>609006</v>
       </c>
       <c r="R75" t="n">
-        <v>7062778</v>
+        <v>7062681</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8894,9 +8926,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8911,22 +8953,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119851306</v>
+        <v>119851664</v>
       </c>
       <c r="B76" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8935,42 +8977,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>609039</v>
+        <v>609125</v>
       </c>
       <c r="R76" t="n">
-        <v>7062664</v>
+        <v>7062827</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9000,19 +9038,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9027,22 +9055,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119851502</v>
+        <v>119852025</v>
       </c>
       <c r="B77" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9051,25 +9079,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9079,13 +9107,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>609140</v>
+        <v>609136</v>
       </c>
       <c r="R77" t="n">
-        <v>7062863</v>
+        <v>7062753</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9141,10 +9169,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119850006</v>
+        <v>119851684</v>
       </c>
       <c r="B78" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9181,10 +9209,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>609003</v>
+        <v>609149</v>
       </c>
       <c r="R78" t="n">
-        <v>7062728</v>
+        <v>7062828</v>
       </c>
       <c r="S78" t="n">
         <v>15</v>
@@ -9243,10 +9271,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119852025</v>
+        <v>119851878</v>
       </c>
       <c r="B79" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9283,10 +9311,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>609136</v>
+        <v>609153</v>
       </c>
       <c r="R79" t="n">
-        <v>7062753</v>
+        <v>7062778</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9345,10 +9373,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119851641</v>
+        <v>119851274</v>
       </c>
       <c r="B80" t="n">
-        <v>79643</v>
+        <v>57320</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9357,41 +9385,46 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>609109</v>
+        <v>609039</v>
       </c>
       <c r="R80" t="n">
-        <v>7062833</v>
+        <v>7062654</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9418,9 +9451,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9435,22 +9478,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119849658</v>
+        <v>119850519</v>
       </c>
       <c r="B81" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9459,43 +9502,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>608890</v>
+        <v>609012</v>
       </c>
       <c r="R81" t="n">
-        <v>7062664</v>
+        <v>7062828</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9525,19 +9563,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9552,22 +9580,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119849630</v>
+        <v>119850411</v>
       </c>
       <c r="B82" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9576,25 +9604,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9604,13 +9632,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>608895</v>
+        <v>609003</v>
       </c>
       <c r="R82" t="n">
-        <v>7062683</v>
+        <v>7062803</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9640,11 +9668,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9671,10 +9694,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119851329</v>
+        <v>119850115</v>
       </c>
       <c r="B83" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9711,13 +9734,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>609091</v>
+        <v>609002</v>
       </c>
       <c r="R83" t="n">
-        <v>7062941</v>
+        <v>7062743</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9741,12 +9764,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9773,10 +9796,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119851928</v>
+        <v>119851329</v>
       </c>
       <c r="B84" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9785,25 +9808,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9813,10 +9836,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>609172</v>
+        <v>609091</v>
       </c>
       <c r="R84" t="n">
-        <v>7062778</v>
+        <v>7062941</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9843,12 +9866,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9875,10 +9898,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119849858</v>
+        <v>119850436</v>
       </c>
       <c r="B85" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9908,24 +9931,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>608877</v>
+        <v>609002</v>
       </c>
       <c r="R85" t="n">
-        <v>7062639</v>
+        <v>7062810</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9952,19 +9971,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9979,22 +9988,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119850321</v>
+        <v>119849630</v>
       </c>
       <c r="B86" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10007,21 +10016,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10031,13 +10040,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>609015</v>
+        <v>608895</v>
       </c>
       <c r="R86" t="n">
-        <v>7062798</v>
+        <v>7062683</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10067,6 +10076,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10093,10 +10107,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119849708</v>
+        <v>119849973</v>
       </c>
       <c r="B87" t="n">
-        <v>90846</v>
+        <v>79652</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10105,25 +10119,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10133,13 +10147,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>608910</v>
+        <v>608986</v>
       </c>
       <c r="R87" t="n">
-        <v>7062662</v>
+        <v>7062749</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10195,10 +10209,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119849721</v>
+        <v>119851251</v>
       </c>
       <c r="B88" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10235,10 +10249,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>608918</v>
+        <v>609099</v>
       </c>
       <c r="R88" t="n">
-        <v>7062673</v>
+        <v>7062948</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10297,10 +10311,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119849724</v>
+        <v>119851993</v>
       </c>
       <c r="B89" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10313,21 +10327,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10337,10 +10351,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>608908</v>
+        <v>609135</v>
       </c>
       <c r="R89" t="n">
-        <v>7062658</v>
+        <v>7062752</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10370,19 +10384,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10397,22 +10401,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119850656</v>
+        <v>119851290</v>
       </c>
       <c r="B90" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10421,25 +10425,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10449,10 +10453,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>609048</v>
+        <v>609054</v>
       </c>
       <c r="R90" t="n">
-        <v>7062921</v>
+        <v>7062684</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10482,9 +10486,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10499,22 +10513,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119850782</v>
+        <v>119849742</v>
       </c>
       <c r="B91" t="n">
-        <v>97907</v>
+        <v>90864</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10523,45 +10537,41 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>608954</v>
+        <v>608916</v>
       </c>
       <c r="R91" t="n">
-        <v>7062685</v>
+        <v>7062680</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10588,19 +10598,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:27</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10615,22 +10615,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119851428</v>
+        <v>119849740</v>
       </c>
       <c r="B92" t="n">
-        <v>79643</v>
+        <v>97930</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10639,41 +10639,45 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>609133</v>
+        <v>608907</v>
       </c>
       <c r="R92" t="n">
-        <v>7062851</v>
+        <v>7062655</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10700,9 +10704,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10717,22 +10731,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119850115</v>
+        <v>119851618</v>
       </c>
       <c r="B93" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10741,25 +10755,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10769,10 +10783,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>609002</v>
+        <v>609113</v>
       </c>
       <c r="R93" t="n">
-        <v>7062743</v>
+        <v>7062853</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10831,10 +10845,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119849966</v>
+        <v>119849971</v>
       </c>
       <c r="B94" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10843,42 +10857,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>608853</v>
+        <v>608977</v>
       </c>
       <c r="R94" t="n">
-        <v>7062579</v>
+        <v>7062755</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10908,19 +10918,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10935,22 +10935,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119850188</v>
+        <v>119849903</v>
       </c>
       <c r="B95" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10959,25 +10959,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>608997</v>
+        <v>608950</v>
       </c>
       <c r="R95" t="n">
-        <v>7062738</v>
+        <v>7062709</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11049,10 +11049,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119851973</v>
+        <v>119851928</v>
       </c>
       <c r="B96" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11089,10 +11089,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>609151</v>
+        <v>609172</v>
       </c>
       <c r="R96" t="n">
-        <v>7062747</v>
+        <v>7062778</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11151,10 +11151,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119851732</v>
+        <v>119851641</v>
       </c>
       <c r="B97" t="n">
-        <v>79607</v>
+        <v>79659</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11163,25 +11163,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11191,13 +11191,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>609149</v>
+        <v>609109</v>
       </c>
       <c r="R97" t="n">
-        <v>7062808</v>
+        <v>7062833</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11253,10 +11253,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119851361</v>
+        <v>119851428</v>
       </c>
       <c r="B98" t="n">
-        <v>79607</v>
+        <v>79659</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11265,25 +11265,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11293,10 +11293,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>609100</v>
+        <v>609133</v>
       </c>
       <c r="R98" t="n">
-        <v>7062937</v>
+        <v>7062851</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -11323,12 +11323,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11355,10 +11355,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119851684</v>
+        <v>119850656</v>
       </c>
       <c r="B99" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11367,25 +11367,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11395,13 +11395,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>609149</v>
+        <v>609048</v>
       </c>
       <c r="R99" t="n">
-        <v>7062828</v>
+        <v>7062921</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11457,10 +11457,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119851251</v>
+        <v>119851235</v>
       </c>
       <c r="B100" t="n">
-        <v>90562</v>
+        <v>97930</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11469,25 +11469,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11497,13 +11497,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>609099</v>
+        <v>609101</v>
       </c>
       <c r="R100" t="n">
-        <v>7062948</v>
+        <v>7062955</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11559,10 +11559,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119851047</v>
+        <v>119849905</v>
       </c>
       <c r="B101" t="n">
-        <v>97907</v>
+        <v>90600</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11571,42 +11571,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>609018</v>
+        <v>608876</v>
       </c>
       <c r="R101" t="n">
-        <v>7062666</v>
+        <v>7062635</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11638,7 +11634,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11648,7 +11644,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11675,10 +11671,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119851618</v>
+        <v>119849829</v>
       </c>
       <c r="B102" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11691,21 +11687,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11715,13 +11711,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>609113</v>
+        <v>608941</v>
       </c>
       <c r="R102" t="n">
-        <v>7062853</v>
+        <v>7062708</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11777,10 +11773,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119851993</v>
+        <v>119851104</v>
       </c>
       <c r="B103" t="n">
-        <v>79607</v>
+        <v>78542</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11793,21 +11789,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11817,13 +11813,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>609135</v>
+        <v>609085</v>
       </c>
       <c r="R103" t="n">
-        <v>7062752</v>
+        <v>7062996</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11853,6 +11849,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11879,10 +11880,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119849742</v>
+        <v>119851802</v>
       </c>
       <c r="B104" t="n">
-        <v>90846</v>
+        <v>79623</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11895,21 +11896,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11919,13 +11920,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>608916</v>
+        <v>609143</v>
       </c>
       <c r="R104" t="n">
-        <v>7062680</v>
+        <v>7062799</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11981,10 +11982,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119849971</v>
+        <v>119850720</v>
       </c>
       <c r="B105" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11993,38 +11994,42 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>608977</v>
+        <v>608957</v>
       </c>
       <c r="R105" t="n">
-        <v>7062755</v>
+        <v>7062678</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12054,9 +12059,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12071,22 +12086,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119851695</v>
+        <v>119849658</v>
       </c>
       <c r="B106" t="n">
-        <v>57463</v>
+        <v>57320</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12099,27 +12114,27 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="M106" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -12128,13 +12143,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>609150</v>
+        <v>608890</v>
       </c>
       <c r="R106" t="n">
-        <v>7062808</v>
+        <v>7062664</v>
       </c>
       <c r="S106" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12161,9 +12176,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12178,22 +12203,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119850411</v>
+        <v>119851502</v>
       </c>
       <c r="B107" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12230,13 +12255,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>609003</v>
+        <v>609140</v>
       </c>
       <c r="R107" t="n">
-        <v>7062803</v>
+        <v>7062863</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12292,10 +12317,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119851274</v>
+        <v>119851185</v>
       </c>
       <c r="B108" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12304,46 +12329,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>609039</v>
+        <v>609097</v>
       </c>
       <c r="R108" t="n">
-        <v>7062654</v>
+        <v>7062964</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12367,22 +12387,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12397,22 +12407,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119849903</v>
+        <v>119849755</v>
       </c>
       <c r="B109" t="n">
-        <v>90562</v>
+        <v>90580</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12449,13 +12459,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>608950</v>
+        <v>608914</v>
       </c>
       <c r="R109" t="n">
-        <v>7062709</v>
+        <v>7062689</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12511,10 +12521,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119851377</v>
+        <v>119852068</v>
       </c>
       <c r="B110" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12551,10 +12561,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>609065</v>
+        <v>609119</v>
       </c>
       <c r="R110" t="n">
-        <v>7062657</v>
+        <v>7062737</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12584,19 +12594,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12611,12 +12611,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
@@ -12626,7 +12626,7 @@
         <v>120091070</v>
       </c>
       <c r="B111" t="n">
-        <v>95775</v>
+        <v>95798</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12742,7 +12742,7 @@
         <v>119849952</v>
       </c>
       <c r="B112" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -6152,7 +6152,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119851306</v>
+        <v>119849966</v>
       </c>
       <c r="B50" t="n">
         <v>97930</v>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6196,10 +6196,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609039</v>
+        <v>608853</v>
       </c>
       <c r="R50" t="n">
-        <v>7062664</v>
+        <v>7062579</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6268,10 +6268,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119851413</v>
+        <v>119851306</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6280,31 +6280,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6313,10 +6312,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609070</v>
+        <v>609039</v>
       </c>
       <c r="R51" t="n">
-        <v>7062653</v>
+        <v>7062664</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6348,7 +6347,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6358,7 +6357,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6385,10 +6384,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119850459</v>
+        <v>119851377</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6401,39 +6400,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>608949</v>
+        <v>609065</v>
       </c>
       <c r="R52" t="n">
-        <v>7062585</v>
+        <v>7062657</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6465,7 +6459,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6475,7 +6469,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6502,10 +6496,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119849966</v>
+        <v>119851413</v>
       </c>
       <c r="B53" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6514,30 +6508,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6546,10 +6541,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>608853</v>
+        <v>609070</v>
       </c>
       <c r="R53" t="n">
-        <v>7062579</v>
+        <v>7062653</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6581,7 +6576,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6591,7 +6586,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6618,10 +6613,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119851377</v>
+        <v>119850459</v>
       </c>
       <c r="B54" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6634,34 +6629,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609065</v>
+        <v>608949</v>
       </c>
       <c r="R54" t="n">
-        <v>7062657</v>
+        <v>7062585</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6730,10 +6730,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119850568</v>
+        <v>119849717</v>
       </c>
       <c r="B55" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6742,25 +6742,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609033</v>
+        <v>608896</v>
       </c>
       <c r="R55" t="n">
-        <v>7062884</v>
+        <v>7062656</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6803,9 +6803,24 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6820,22 +6835,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119849717</v>
+        <v>119850568</v>
       </c>
       <c r="B56" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6844,25 +6859,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6872,10 +6887,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>608896</v>
+        <v>609033</v>
       </c>
       <c r="R56" t="n">
-        <v>7062656</v>
+        <v>7062884</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6905,24 +6920,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6937,22 +6937,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119849708</v>
+        <v>119851361</v>
       </c>
       <c r="B57" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6965,21 +6965,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6989,13 +6989,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>608910</v>
+        <v>609100</v>
       </c>
       <c r="R57" t="n">
-        <v>7062662</v>
+        <v>7062937</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7019,12 +7019,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7051,10 +7051,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119851361</v>
+        <v>119849708</v>
       </c>
       <c r="B58" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7067,21 +7067,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>609100</v>
+        <v>608910</v>
       </c>
       <c r="R58" t="n">
-        <v>7062937</v>
+        <v>7062662</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8853,10 +8853,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119850955</v>
+        <v>119850519</v>
       </c>
       <c r="B75" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8865,25 +8865,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8893,10 +8893,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>609006</v>
+        <v>609012</v>
       </c>
       <c r="R75" t="n">
-        <v>7062681</v>
+        <v>7062828</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8926,19 +8926,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8953,19 +8943,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119851664</v>
+        <v>119850955</v>
       </c>
       <c r="B76" t="n">
         <v>79623</v>
@@ -9005,10 +8995,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>609125</v>
+        <v>609006</v>
       </c>
       <c r="R76" t="n">
-        <v>7062827</v>
+        <v>7062681</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9038,9 +9028,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9055,19 +9055,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119852025</v>
+        <v>119851664</v>
       </c>
       <c r="B77" t="n">
         <v>79623</v>
@@ -9107,10 +9107,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>609136</v>
+        <v>609125</v>
       </c>
       <c r="R77" t="n">
-        <v>7062753</v>
+        <v>7062827</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9169,7 +9169,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119851684</v>
+        <v>119852025</v>
       </c>
       <c r="B78" t="n">
         <v>79623</v>
@@ -9209,13 +9209,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>609149</v>
+        <v>609136</v>
       </c>
       <c r="R78" t="n">
-        <v>7062828</v>
+        <v>7062753</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119851878</v>
+        <v>119851684</v>
       </c>
       <c r="B79" t="n">
         <v>79623</v>
@@ -9311,13 +9311,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>609153</v>
+        <v>609149</v>
       </c>
       <c r="R79" t="n">
-        <v>7062778</v>
+        <v>7062828</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9373,10 +9373,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119851274</v>
+        <v>119851878</v>
       </c>
       <c r="B80" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9389,39 +9389,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>609039</v>
+        <v>609153</v>
       </c>
       <c r="R80" t="n">
-        <v>7062654</v>
+        <v>7062778</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9451,19 +9446,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9478,22 +9463,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119850519</v>
+        <v>119851274</v>
       </c>
       <c r="B81" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9502,38 +9487,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>609012</v>
+        <v>609039</v>
       </c>
       <c r="R81" t="n">
-        <v>7062828</v>
+        <v>7062654</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9563,9 +9553,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9580,12 +9580,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -11049,10 +11049,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119851928</v>
+        <v>119851641</v>
       </c>
       <c r="B96" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11061,25 +11061,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11089,13 +11089,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>609172</v>
+        <v>609109</v>
       </c>
       <c r="R96" t="n">
-        <v>7062778</v>
+        <v>7062833</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11151,7 +11151,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119851641</v>
+        <v>119851428</v>
       </c>
       <c r="B97" t="n">
         <v>79659</v>
@@ -11191,10 +11191,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>609109</v>
+        <v>609133</v>
       </c>
       <c r="R97" t="n">
-        <v>7062833</v>
+        <v>7062851</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -11253,10 +11253,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119851428</v>
+        <v>119850656</v>
       </c>
       <c r="B98" t="n">
-        <v>79659</v>
+        <v>97930</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11265,25 +11265,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11293,13 +11293,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>609133</v>
+        <v>609048</v>
       </c>
       <c r="R98" t="n">
-        <v>7062851</v>
+        <v>7062921</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11355,10 +11355,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119850656</v>
+        <v>119851928</v>
       </c>
       <c r="B99" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11367,25 +11367,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11395,10 +11395,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>609048</v>
+        <v>609172</v>
       </c>
       <c r="R99" t="n">
-        <v>7062921</v>
+        <v>7062778</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -5390,10 +5390,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119850876</v>
+        <v>119850656</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5402,25 +5402,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5430,13 +5430,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>609066</v>
+        <v>609048</v>
       </c>
       <c r="R43" t="n">
-        <v>7062980</v>
+        <v>7062921</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5492,10 +5492,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119851695</v>
+        <v>119851802</v>
       </c>
       <c r="B44" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5508,42 +5508,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>609150</v>
+        <v>609143</v>
       </c>
       <c r="R44" t="n">
-        <v>7062808</v>
+        <v>7062799</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5599,10 +5594,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119850926</v>
+        <v>119851421</v>
       </c>
       <c r="B45" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5615,42 +5610,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>609003</v>
+        <v>609130</v>
       </c>
       <c r="R45" t="n">
-        <v>7062700</v>
+        <v>7062851</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5677,19 +5667,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5704,22 +5684,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119850188</v>
+        <v>119851618</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5728,25 +5708,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5756,10 +5736,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>608997</v>
+        <v>609113</v>
       </c>
       <c r="R46" t="n">
-        <v>7062738</v>
+        <v>7062853</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5818,10 +5798,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119851047</v>
+        <v>119851160</v>
       </c>
       <c r="B47" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5830,30 +5810,31 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>12</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5862,10 +5843,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>609018</v>
+        <v>609023</v>
       </c>
       <c r="R47" t="n">
-        <v>7062666</v>
+        <v>7062674</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5897,7 +5878,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5907,7 +5888,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5934,10 +5915,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119849858</v>
+        <v>119850850</v>
       </c>
       <c r="B48" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5946,42 +5927,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>608877</v>
+        <v>609076</v>
       </c>
       <c r="R48" t="n">
-        <v>7062639</v>
+        <v>7062968</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6011,19 +5988,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6038,22 +6005,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119849721</v>
+        <v>119851361</v>
       </c>
       <c r="B49" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6066,21 +6033,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6090,13 +6057,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>608918</v>
+        <v>609100</v>
       </c>
       <c r="R49" t="n">
-        <v>7062673</v>
+        <v>7062937</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6120,12 +6087,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6152,7 +6119,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119849966</v>
+        <v>119851329</v>
       </c>
       <c r="B50" t="n">
         <v>97930</v>
@@ -6185,21 +6152,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>608853</v>
+        <v>609091</v>
       </c>
       <c r="R50" t="n">
-        <v>7062579</v>
+        <v>7062941</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6226,22 +6189,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:37</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:37</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6256,22 +6209,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119851306</v>
+        <v>119849905</v>
       </c>
       <c r="B51" t="n">
-        <v>97930</v>
+        <v>90600</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6280,42 +6233,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609039</v>
+        <v>608876</v>
       </c>
       <c r="R51" t="n">
-        <v>7062664</v>
+        <v>7062635</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6347,7 +6296,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6357,7 +6306,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6384,10 +6333,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119851377</v>
+        <v>119849717</v>
       </c>
       <c r="B52" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6400,21 +6349,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6424,10 +6373,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>609065</v>
+        <v>608896</v>
       </c>
       <c r="R52" t="n">
-        <v>7062657</v>
+        <v>7062656</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6459,7 +6408,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6469,7 +6418,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6613,10 +6567,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119850459</v>
+        <v>119851732</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6629,39 +6583,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>608949</v>
+        <v>609149</v>
       </c>
       <c r="R54" t="n">
-        <v>7062585</v>
+        <v>7062808</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6691,19 +6640,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6718,19 +6657,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119849717</v>
+        <v>119850926</v>
       </c>
       <c r="B55" t="n">
         <v>57320</v>
@@ -6764,16 +6703,21 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>608896</v>
+        <v>609003</v>
       </c>
       <c r="R55" t="n">
-        <v>7062656</v>
+        <v>7062700</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6805,7 +6749,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6815,12 +6759,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6847,10 +6786,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119850568</v>
+        <v>119849708</v>
       </c>
       <c r="B56" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6859,25 +6798,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6887,10 +6826,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>609033</v>
+        <v>608910</v>
       </c>
       <c r="R56" t="n">
-        <v>7062884</v>
+        <v>7062662</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6949,10 +6888,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119851361</v>
+        <v>119849966</v>
       </c>
       <c r="B57" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6961,41 +6900,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609100</v>
+        <v>608853</v>
       </c>
       <c r="R57" t="n">
-        <v>7062937</v>
+        <v>7062579</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7019,12 +6962,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7039,22 +6992,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119849708</v>
+        <v>119851641</v>
       </c>
       <c r="B58" t="n">
-        <v>90864</v>
+        <v>79659</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7063,25 +7016,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7091,13 +7044,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>608910</v>
+        <v>609109</v>
       </c>
       <c r="R58" t="n">
-        <v>7062662</v>
+        <v>7062833</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7153,10 +7106,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119850562</v>
+        <v>119850720</v>
       </c>
       <c r="B59" t="n">
-        <v>91146</v>
+        <v>97930</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7169,34 +7122,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>608992</v>
+        <v>608957</v>
       </c>
       <c r="R59" t="n">
-        <v>7062626</v>
+        <v>7062678</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7228,7 +7185,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7238,7 +7195,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7265,10 +7222,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119851861</v>
+        <v>119850752</v>
       </c>
       <c r="B60" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7277,25 +7234,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7305,13 +7262,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>609153</v>
+        <v>609068</v>
       </c>
       <c r="R60" t="n">
-        <v>7062783</v>
+        <v>7062927</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7335,12 +7292,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7367,10 +7329,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119850850</v>
+        <v>119851185</v>
       </c>
       <c r="B61" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7379,25 +7341,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7407,13 +7369,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609076</v>
+        <v>609097</v>
       </c>
       <c r="R61" t="n">
-        <v>7062968</v>
+        <v>7062964</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7437,12 +7399,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7469,7 +7431,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119850006</v>
+        <v>119851861</v>
       </c>
       <c r="B62" t="n">
         <v>79623</v>
@@ -7509,10 +7471,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609003</v>
+        <v>609153</v>
       </c>
       <c r="R62" t="n">
-        <v>7062728</v>
+        <v>7062783</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7571,10 +7533,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119850834</v>
+        <v>119852068</v>
       </c>
       <c r="B63" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7587,21 +7549,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7611,13 +7573,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609080</v>
+        <v>609119</v>
       </c>
       <c r="R63" t="n">
-        <v>7062946</v>
+        <v>7062737</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7673,10 +7635,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119850752</v>
+        <v>119851878</v>
       </c>
       <c r="B64" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7685,25 +7647,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7713,10 +7675,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609068</v>
+        <v>609153</v>
       </c>
       <c r="R64" t="n">
-        <v>7062927</v>
+        <v>7062778</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7743,17 +7705,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7780,10 +7737,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119849724</v>
+        <v>119851502</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7792,25 +7749,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7820,13 +7777,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>608908</v>
+        <v>609140</v>
       </c>
       <c r="R65" t="n">
-        <v>7062658</v>
+        <v>7062863</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7853,19 +7810,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7880,22 +7827,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119850782</v>
+        <v>119850562</v>
       </c>
       <c r="B66" t="n">
-        <v>97930</v>
+        <v>91146</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7908,38 +7855,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>608954</v>
+        <v>608992</v>
       </c>
       <c r="R66" t="n">
-        <v>7062685</v>
+        <v>7062626</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7971,7 +7914,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7981,7 +7924,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8008,10 +7951,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119851950</v>
+        <v>119849903</v>
       </c>
       <c r="B67" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8024,21 +7967,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8048,13 +7991,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>609160</v>
+        <v>608950</v>
       </c>
       <c r="R67" t="n">
-        <v>7062762</v>
+        <v>7062709</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8110,10 +8053,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119850220</v>
+        <v>119851973</v>
       </c>
       <c r="B68" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8126,21 +8069,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8150,10 +8093,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>608994</v>
+        <v>609151</v>
       </c>
       <c r="R68" t="n">
-        <v>7062775</v>
+        <v>7062747</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8180,12 +8123,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8212,7 +8155,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119851973</v>
+        <v>119850006</v>
       </c>
       <c r="B69" t="n">
         <v>79623</v>
@@ -8252,13 +8195,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>609151</v>
+        <v>609003</v>
       </c>
       <c r="R69" t="n">
-        <v>7062747</v>
+        <v>7062728</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8314,7 +8257,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119851421</v>
+        <v>119852025</v>
       </c>
       <c r="B70" t="n">
         <v>79623</v>
@@ -8354,13 +8297,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>609130</v>
+        <v>609136</v>
       </c>
       <c r="R70" t="n">
-        <v>7062851</v>
+        <v>7062753</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8416,7 +8359,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119850321</v>
+        <v>119851928</v>
       </c>
       <c r="B71" t="n">
         <v>79623</v>
@@ -8456,13 +8399,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609015</v>
+        <v>609172</v>
       </c>
       <c r="R71" t="n">
-        <v>7062798</v>
+        <v>7062778</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8518,10 +8461,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119851732</v>
+        <v>119851695</v>
       </c>
       <c r="B72" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8534,37 +8477,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>609149</v>
+        <v>609150</v>
       </c>
       <c r="R72" t="n">
         <v>7062808</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8620,10 +8568,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119851160</v>
+        <v>119850568</v>
       </c>
       <c r="B73" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8632,43 +8580,38 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>609023</v>
+        <v>609033</v>
       </c>
       <c r="R73" t="n">
-        <v>7062674</v>
+        <v>7062884</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8698,19 +8641,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8725,19 +8658,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119850096</v>
+        <v>119850436</v>
       </c>
       <c r="B74" t="n">
         <v>97930</v>
@@ -8770,24 +8703,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>608905</v>
+        <v>609002</v>
       </c>
       <c r="R74" t="n">
-        <v>7062586</v>
+        <v>7062810</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8814,19 +8743,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8841,22 +8760,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119850519</v>
+        <v>119849829</v>
       </c>
       <c r="B75" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8865,25 +8784,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8893,10 +8812,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>609012</v>
+        <v>608941</v>
       </c>
       <c r="R75" t="n">
-        <v>7062828</v>
+        <v>7062708</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8955,10 +8874,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119850955</v>
+        <v>119849721</v>
       </c>
       <c r="B76" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8971,21 +8890,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8995,10 +8914,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>609006</v>
+        <v>608918</v>
       </c>
       <c r="R76" t="n">
-        <v>7062681</v>
+        <v>7062673</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9028,19 +8947,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9055,22 +8964,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119851664</v>
+        <v>119850876</v>
       </c>
       <c r="B77" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9083,21 +8992,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9107,13 +9016,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>609125</v>
+        <v>609066</v>
       </c>
       <c r="R77" t="n">
-        <v>7062827</v>
+        <v>7062980</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9169,10 +9078,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119852025</v>
+        <v>119850115</v>
       </c>
       <c r="B78" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9181,25 +9090,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9209,13 +9118,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>609136</v>
+        <v>609002</v>
       </c>
       <c r="R78" t="n">
-        <v>7062753</v>
+        <v>7062743</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9271,10 +9180,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119851684</v>
+        <v>119851251</v>
       </c>
       <c r="B79" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9287,21 +9196,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9311,13 +9220,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>609149</v>
+        <v>609099</v>
       </c>
       <c r="R79" t="n">
-        <v>7062828</v>
+        <v>7062948</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9373,10 +9282,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119851878</v>
+        <v>119849858</v>
       </c>
       <c r="B80" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9385,38 +9294,42 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>609153</v>
+        <v>608877</v>
       </c>
       <c r="R80" t="n">
-        <v>7062778</v>
+        <v>7062639</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9446,9 +9359,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9463,22 +9386,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119851274</v>
+        <v>119850782</v>
       </c>
       <c r="B81" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9487,31 +9410,30 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9520,10 +9442,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>609039</v>
+        <v>608954</v>
       </c>
       <c r="R81" t="n">
-        <v>7062654</v>
+        <v>7062685</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9555,7 +9477,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9565,7 +9487,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9592,10 +9514,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119850411</v>
+        <v>119850220</v>
       </c>
       <c r="B82" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9604,25 +9526,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9632,10 +9554,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>609003</v>
+        <v>608994</v>
       </c>
       <c r="R82" t="n">
-        <v>7062803</v>
+        <v>7062775</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9662,12 +9584,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9694,10 +9616,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119850115</v>
+        <v>119851274</v>
       </c>
       <c r="B83" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9706,41 +9628,46 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>609002</v>
+        <v>609039</v>
       </c>
       <c r="R83" t="n">
-        <v>7062743</v>
+        <v>7062654</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9767,9 +9694,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9784,19 +9721,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119851329</v>
+        <v>119851306</v>
       </c>
       <c r="B84" t="n">
         <v>97930</v>
@@ -9829,17 +9766,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>609091</v>
+        <v>609039</v>
       </c>
       <c r="R84" t="n">
-        <v>7062941</v>
+        <v>7062664</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9866,12 +9807,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9886,22 +9837,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119850436</v>
+        <v>119849630</v>
       </c>
       <c r="B85" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9910,25 +9861,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9938,13 +9889,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>609002</v>
+        <v>608895</v>
       </c>
       <c r="R85" t="n">
-        <v>7062810</v>
+        <v>7062683</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9974,6 +9925,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10000,10 +9956,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119849630</v>
+        <v>119849658</v>
       </c>
       <c r="B86" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10016,37 +9972,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>608895</v>
+        <v>608890</v>
       </c>
       <c r="R86" t="n">
-        <v>7062683</v>
+        <v>7062664</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10073,14 +10034,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, även på tall.</t>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10095,22 +10061,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119849973</v>
+        <v>119850955</v>
       </c>
       <c r="B87" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10119,25 +10085,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10147,13 +10113,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>608986</v>
+        <v>609006</v>
       </c>
       <c r="R87" t="n">
-        <v>7062749</v>
+        <v>7062681</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10180,9 +10146,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>14:42</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10197,22 +10173,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119851251</v>
+        <v>119851684</v>
       </c>
       <c r="B88" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10225,21 +10201,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10249,13 +10225,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>609099</v>
+        <v>609149</v>
       </c>
       <c r="R88" t="n">
-        <v>7062948</v>
+        <v>7062828</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10311,7 +10287,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119851993</v>
+        <v>119850321</v>
       </c>
       <c r="B89" t="n">
         <v>79623</v>
@@ -10351,13 +10327,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>609135</v>
+        <v>609015</v>
       </c>
       <c r="R89" t="n">
-        <v>7062752</v>
+        <v>7062798</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10525,10 +10501,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119849742</v>
+        <v>119850096</v>
       </c>
       <c r="B91" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10537,41 +10513,45 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>608916</v>
+        <v>608905</v>
       </c>
       <c r="R91" t="n">
-        <v>7062680</v>
+        <v>7062586</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10598,9 +10578,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10615,19 +10605,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119849740</v>
+        <v>119851047</v>
       </c>
       <c r="B92" t="n">
         <v>97930</v>
@@ -10662,7 +10652,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -10671,10 +10661,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>608907</v>
+        <v>609018</v>
       </c>
       <c r="R92" t="n">
-        <v>7062655</v>
+        <v>7062666</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10706,7 +10696,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10716,7 +10706,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10743,10 +10733,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119851618</v>
+        <v>119849742</v>
       </c>
       <c r="B93" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10759,21 +10749,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10783,10 +10773,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>609113</v>
+        <v>608916</v>
       </c>
       <c r="R93" t="n">
-        <v>7062853</v>
+        <v>7062680</v>
       </c>
       <c r="S93" t="n">
         <v>15</v>
@@ -10845,10 +10835,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119849971</v>
+        <v>119851428</v>
       </c>
       <c r="B94" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10857,25 +10847,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10885,13 +10875,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>608977</v>
+        <v>609133</v>
       </c>
       <c r="R94" t="n">
-        <v>7062755</v>
+        <v>7062851</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10947,10 +10937,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119849903</v>
+        <v>119851664</v>
       </c>
       <c r="B95" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10963,21 +10953,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10987,10 +10977,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>608950</v>
+        <v>609125</v>
       </c>
       <c r="R95" t="n">
-        <v>7062709</v>
+        <v>7062827</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11049,10 +11039,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119851641</v>
+        <v>119850519</v>
       </c>
       <c r="B96" t="n">
-        <v>79659</v>
+        <v>97930</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11061,25 +11051,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11089,13 +11079,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>609109</v>
+        <v>609012</v>
       </c>
       <c r="R96" t="n">
-        <v>7062833</v>
+        <v>7062828</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11151,10 +11141,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119851428</v>
+        <v>119850411</v>
       </c>
       <c r="B97" t="n">
-        <v>79659</v>
+        <v>97930</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11163,25 +11153,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11191,13 +11181,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>609133</v>
+        <v>609003</v>
       </c>
       <c r="R97" t="n">
-        <v>7062851</v>
+        <v>7062803</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11253,10 +11243,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119850656</v>
+        <v>119849755</v>
       </c>
       <c r="B98" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11265,25 +11255,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11293,13 +11283,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>609048</v>
+        <v>608914</v>
       </c>
       <c r="R98" t="n">
-        <v>7062921</v>
+        <v>7062689</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11355,10 +11345,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119851928</v>
+        <v>119849973</v>
       </c>
       <c r="B99" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11367,25 +11357,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11395,13 +11385,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>609172</v>
+        <v>608986</v>
       </c>
       <c r="R99" t="n">
-        <v>7062778</v>
+        <v>7062749</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11457,10 +11447,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119851235</v>
+        <v>119851993</v>
       </c>
       <c r="B100" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11469,25 +11459,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11497,13 +11487,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>609101</v>
+        <v>609135</v>
       </c>
       <c r="R100" t="n">
-        <v>7062955</v>
+        <v>7062752</v>
       </c>
       <c r="S100" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11559,10 +11549,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119849905</v>
+        <v>119851104</v>
       </c>
       <c r="B101" t="n">
-        <v>90600</v>
+        <v>78542</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11575,21 +11565,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11599,13 +11589,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>608876</v>
+        <v>609085</v>
       </c>
       <c r="R101" t="n">
-        <v>7062635</v>
+        <v>7062996</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11632,19 +11622,14 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>13:30</t>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11659,22 +11644,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119849829</v>
+        <v>119850834</v>
       </c>
       <c r="B102" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11687,21 +11672,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11711,13 +11696,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>608941</v>
+        <v>609080</v>
       </c>
       <c r="R102" t="n">
-        <v>7062708</v>
+        <v>7062946</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11773,7 +11758,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119851104</v>
+        <v>119849724</v>
       </c>
       <c r="B103" t="n">
         <v>78542</v>
@@ -11813,13 +11798,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>609085</v>
+        <v>608908</v>
       </c>
       <c r="R103" t="n">
-        <v>7062996</v>
+        <v>7062658</v>
       </c>
       <c r="S103" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11846,14 +11831,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11868,22 +11858,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119851802</v>
+        <v>119851235</v>
       </c>
       <c r="B104" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11892,25 +11882,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11920,13 +11910,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>609143</v>
+        <v>609101</v>
       </c>
       <c r="R104" t="n">
-        <v>7062799</v>
+        <v>7062955</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11982,7 +11972,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119850720</v>
+        <v>119850188</v>
       </c>
       <c r="B105" t="n">
         <v>97930</v>
@@ -12015,24 +12005,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>608957</v>
+        <v>608997</v>
       </c>
       <c r="R105" t="n">
-        <v>7062678</v>
+        <v>7062738</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12059,19 +12045,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12086,22 +12062,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119849658</v>
+        <v>119849971</v>
       </c>
       <c r="B106" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12114,39 +12090,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>608890</v>
+        <v>608977</v>
       </c>
       <c r="R106" t="n">
-        <v>7062664</v>
+        <v>7062755</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12176,19 +12147,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12203,19 +12164,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119851502</v>
+        <v>119849740</v>
       </c>
       <c r="B107" t="n">
         <v>97930</v>
@@ -12248,20 +12209,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>609140</v>
+        <v>608907</v>
       </c>
       <c r="R107" t="n">
-        <v>7062863</v>
+        <v>7062655</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12288,9 +12253,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12305,22 +12280,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119851185</v>
+        <v>119851377</v>
       </c>
       <c r="B108" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12329,25 +12304,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12357,13 +12332,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>609097</v>
+        <v>609065</v>
       </c>
       <c r="R108" t="n">
-        <v>7062964</v>
+        <v>7062657</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12387,12 +12362,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12407,22 +12392,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119849755</v>
+        <v>119851950</v>
       </c>
       <c r="B109" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12435,21 +12420,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12459,10 +12444,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>608914</v>
+        <v>609160</v>
       </c>
       <c r="R109" t="n">
-        <v>7062689</v>
+        <v>7062762</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -12521,10 +12506,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119852068</v>
+        <v>119850459</v>
       </c>
       <c r="B110" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12537,34 +12522,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>609119</v>
+        <v>608949</v>
       </c>
       <c r="R110" t="n">
-        <v>7062737</v>
+        <v>7062585</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12594,9 +12584,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12611,12 +12611,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -7106,10 +7106,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119850720</v>
+        <v>119851861</v>
       </c>
       <c r="B59" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7118,45 +7118,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>608957</v>
+        <v>609153</v>
       </c>
       <c r="R59" t="n">
-        <v>7062678</v>
+        <v>7062783</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7183,19 +7179,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7210,22 +7196,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119850752</v>
+        <v>119852068</v>
       </c>
       <c r="B60" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7234,25 +7220,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7262,10 +7248,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>609068</v>
+        <v>609119</v>
       </c>
       <c r="R60" t="n">
-        <v>7062927</v>
+        <v>7062737</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7292,17 +7278,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7329,10 +7310,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119851185</v>
+        <v>119851878</v>
       </c>
       <c r="B61" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7341,25 +7322,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7369,13 +7350,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609097</v>
+        <v>609153</v>
       </c>
       <c r="R61" t="n">
-        <v>7062964</v>
+        <v>7062778</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7399,12 +7380,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7431,10 +7412,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119851861</v>
+        <v>119850720</v>
       </c>
       <c r="B62" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7443,41 +7424,45 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609153</v>
+        <v>608957</v>
       </c>
       <c r="R62" t="n">
-        <v>7062783</v>
+        <v>7062678</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7504,9 +7489,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7521,22 +7516,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119852068</v>
+        <v>119850752</v>
       </c>
       <c r="B63" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7545,25 +7540,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7573,10 +7568,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609119</v>
+        <v>609068</v>
       </c>
       <c r="R63" t="n">
-        <v>7062737</v>
+        <v>7062927</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7603,12 +7598,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7635,10 +7635,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119851878</v>
+        <v>119851185</v>
       </c>
       <c r="B64" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7647,25 +7647,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7675,13 +7675,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609153</v>
+        <v>609097</v>
       </c>
       <c r="R64" t="n">
-        <v>7062778</v>
+        <v>7062964</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7705,12 +7705,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8461,10 +8461,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119851695</v>
+        <v>119850568</v>
       </c>
       <c r="B72" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8473,46 +8473,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>609150</v>
+        <v>609033</v>
       </c>
       <c r="R72" t="n">
-        <v>7062808</v>
+        <v>7062884</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8568,7 +8563,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119850568</v>
+        <v>119850436</v>
       </c>
       <c r="B73" t="n">
         <v>97930</v>
@@ -8608,13 +8603,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>609033</v>
+        <v>609002</v>
       </c>
       <c r="R73" t="n">
-        <v>7062884</v>
+        <v>7062810</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8670,10 +8665,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119850436</v>
+        <v>119851695</v>
       </c>
       <c r="B74" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8682,41 +8677,46 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>609002</v>
+        <v>609150</v>
       </c>
       <c r="R74" t="n">
-        <v>7062810</v>
+        <v>7062808</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9514,10 +9514,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119850220</v>
+        <v>119849630</v>
       </c>
       <c r="B82" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9530,21 +9530,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9554,13 +9554,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>608994</v>
+        <v>608895</v>
       </c>
       <c r="R82" t="n">
-        <v>7062775</v>
+        <v>7062683</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9584,12 +9584,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9616,7 +9621,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119851274</v>
+        <v>119849658</v>
       </c>
       <c r="B83" t="n">
         <v>57320</v>
@@ -9661,10 +9666,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>609039</v>
+        <v>608890</v>
       </c>
       <c r="R83" t="n">
-        <v>7062654</v>
+        <v>7062664</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9696,7 +9701,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9706,7 +9711,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9733,10 +9738,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119851306</v>
+        <v>119850955</v>
       </c>
       <c r="B84" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9745,42 +9750,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>609039</v>
+        <v>609006</v>
       </c>
       <c r="R84" t="n">
-        <v>7062664</v>
+        <v>7062681</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9812,7 +9813,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9822,7 +9823,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9849,10 +9850,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119849630</v>
+        <v>119851684</v>
       </c>
       <c r="B85" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9865,21 +9866,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9889,13 +9890,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>608895</v>
+        <v>609149</v>
       </c>
       <c r="R85" t="n">
-        <v>7062683</v>
+        <v>7062828</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9925,11 +9926,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9956,10 +9952,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119849658</v>
+        <v>119850220</v>
       </c>
       <c r="B86" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9972,39 +9968,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>608890</v>
+        <v>608994</v>
       </c>
       <c r="R86" t="n">
-        <v>7062664</v>
+        <v>7062775</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10031,22 +10022,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10061,22 +10042,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119850955</v>
+        <v>119851274</v>
       </c>
       <c r="B87" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10089,34 +10070,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>609006</v>
+        <v>609039</v>
       </c>
       <c r="R87" t="n">
-        <v>7062681</v>
+        <v>7062654</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10148,7 +10134,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10158,7 +10144,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10185,10 +10171,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119851684</v>
+        <v>119851306</v>
       </c>
       <c r="B88" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10197,41 +10183,45 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>609149</v>
+        <v>609039</v>
       </c>
       <c r="R88" t="n">
-        <v>7062828</v>
+        <v>7062664</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10258,9 +10248,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10275,12 +10275,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119849740</v>
+        <v>119851377</v>
       </c>
       <c r="B107" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12188,42 +12188,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>608907</v>
+        <v>609065</v>
       </c>
       <c r="R107" t="n">
-        <v>7062655</v>
+        <v>7062657</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12255,7 +12251,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12265,7 +12261,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12292,7 +12288,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119851377</v>
+        <v>119851950</v>
       </c>
       <c r="B108" t="n">
         <v>79623</v>
@@ -12332,13 +12328,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>609065</v>
+        <v>609160</v>
       </c>
       <c r="R108" t="n">
-        <v>7062657</v>
+        <v>7062762</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12365,19 +12361,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12392,22 +12378,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119851950</v>
+        <v>119850459</v>
       </c>
       <c r="B109" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12420,37 +12406,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>609160</v>
+        <v>608949</v>
       </c>
       <c r="R109" t="n">
-        <v>7062762</v>
+        <v>7062585</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12477,9 +12468,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12494,22 +12495,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119850459</v>
+        <v>119849740</v>
       </c>
       <c r="B110" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12518,31 +12519,30 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12551,10 +12551,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>608949</v>
+        <v>608907</v>
       </c>
       <c r="R110" t="n">
-        <v>7062585</v>
+        <v>7062655</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12586,7 +12586,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12596,7 +12596,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -5390,10 +5390,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119850656</v>
+        <v>119850926</v>
       </c>
       <c r="B43" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5402,38 +5402,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>609048</v>
+        <v>609003</v>
       </c>
       <c r="R43" t="n">
-        <v>7062921</v>
+        <v>7062700</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5463,9 +5468,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5480,19 +5495,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119851802</v>
+        <v>119851878</v>
       </c>
       <c r="B44" t="n">
         <v>79623</v>
@@ -5532,10 +5547,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>609143</v>
+        <v>609153</v>
       </c>
       <c r="R44" t="n">
-        <v>7062799</v>
+        <v>7062778</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5594,7 +5609,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119851421</v>
+        <v>119851928</v>
       </c>
       <c r="B45" t="n">
         <v>79623</v>
@@ -5634,13 +5649,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>609130</v>
+        <v>609172</v>
       </c>
       <c r="R45" t="n">
-        <v>7062851</v>
+        <v>7062778</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5696,10 +5711,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119851618</v>
+        <v>119850656</v>
       </c>
       <c r="B46" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5708,25 +5723,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5736,13 +5751,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>609113</v>
+        <v>609048</v>
       </c>
       <c r="R46" t="n">
-        <v>7062853</v>
+        <v>7062921</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5798,10 +5813,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119851160</v>
+        <v>119850834</v>
       </c>
       <c r="B47" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5814,42 +5829,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>609023</v>
+        <v>609080</v>
       </c>
       <c r="R47" t="n">
-        <v>7062674</v>
+        <v>7062946</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5876,19 +5886,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5903,22 +5903,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119850850</v>
+        <v>119849755</v>
       </c>
       <c r="B48" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5931,21 +5931,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5955,13 +5955,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>609076</v>
+        <v>608914</v>
       </c>
       <c r="R48" t="n">
-        <v>7062968</v>
+        <v>7062689</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6017,10 +6017,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119851361</v>
+        <v>119851235</v>
       </c>
       <c r="B49" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6029,25 +6029,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6057,13 +6057,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609100</v>
+        <v>609101</v>
       </c>
       <c r="R49" t="n">
-        <v>7062937</v>
+        <v>7062955</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6119,10 +6119,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119851329</v>
+        <v>119849973</v>
       </c>
       <c r="B50" t="n">
-        <v>97930</v>
+        <v>79652</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6131,25 +6131,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6159,13 +6159,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>609091</v>
+        <v>608986</v>
       </c>
       <c r="R50" t="n">
-        <v>7062941</v>
+        <v>7062749</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6221,10 +6221,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119849905</v>
+        <v>119850519</v>
       </c>
       <c r="B51" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6233,25 +6233,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6261,10 +6261,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>608876</v>
+        <v>609012</v>
       </c>
       <c r="R51" t="n">
-        <v>7062635</v>
+        <v>7062828</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6294,19 +6294,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6321,22 +6311,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119849717</v>
+        <v>119850411</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6345,25 +6335,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6373,10 +6363,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>608896</v>
+        <v>609003</v>
       </c>
       <c r="R52" t="n">
-        <v>7062656</v>
+        <v>7062803</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6406,24 +6396,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6438,22 +6413,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119851413</v>
+        <v>119851802</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6466,39 +6441,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>609070</v>
+        <v>609143</v>
       </c>
       <c r="R53" t="n">
-        <v>7062653</v>
+        <v>7062799</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6528,19 +6498,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:14</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6555,22 +6515,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119851732</v>
+        <v>119851641</v>
       </c>
       <c r="B54" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6579,25 +6539,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6607,13 +6567,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609149</v>
+        <v>609109</v>
       </c>
       <c r="R54" t="n">
-        <v>7062808</v>
+        <v>7062833</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6669,10 +6629,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119850926</v>
+        <v>119850436</v>
       </c>
       <c r="B55" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6681,46 +6641,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609003</v>
+        <v>609002</v>
       </c>
       <c r="R55" t="n">
-        <v>7062700</v>
+        <v>7062810</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6747,19 +6702,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6774,22 +6719,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119849708</v>
+        <v>119849858</v>
       </c>
       <c r="B56" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6798,38 +6743,42 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>608910</v>
+        <v>608877</v>
       </c>
       <c r="R56" t="n">
-        <v>7062662</v>
+        <v>7062639</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6859,9 +6808,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6876,22 +6835,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119849966</v>
+        <v>119851861</v>
       </c>
       <c r="B57" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6900,45 +6859,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>608853</v>
+        <v>609153</v>
       </c>
       <c r="R57" t="n">
-        <v>7062579</v>
+        <v>7062783</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6965,19 +6920,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6992,22 +6937,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119851641</v>
+        <v>119852068</v>
       </c>
       <c r="B58" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7016,25 +6961,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7044,13 +6989,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>609109</v>
+        <v>609119</v>
       </c>
       <c r="R58" t="n">
-        <v>7062833</v>
+        <v>7062737</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7106,7 +7051,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119851861</v>
+        <v>119851290</v>
       </c>
       <c r="B59" t="n">
         <v>79623</v>
@@ -7146,13 +7091,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>609153</v>
+        <v>609054</v>
       </c>
       <c r="R59" t="n">
-        <v>7062783</v>
+        <v>7062684</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7179,9 +7124,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7196,22 +7151,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119852068</v>
+        <v>119850459</v>
       </c>
       <c r="B60" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7224,34 +7179,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>609119</v>
+        <v>608949</v>
       </c>
       <c r="R60" t="n">
-        <v>7062737</v>
+        <v>7062585</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7281,9 +7241,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7298,22 +7268,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119851878</v>
+        <v>119850562</v>
       </c>
       <c r="B61" t="n">
-        <v>79623</v>
+        <v>91146</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7322,25 +7292,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7350,10 +7320,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>609153</v>
+        <v>608992</v>
       </c>
       <c r="R61" t="n">
-        <v>7062778</v>
+        <v>7062626</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7383,9 +7353,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7400,22 +7380,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119850720</v>
+        <v>119850955</v>
       </c>
       <c r="B62" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7424,42 +7404,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>608957</v>
+        <v>609006</v>
       </c>
       <c r="R62" t="n">
-        <v>7062678</v>
+        <v>7062681</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7491,7 +7467,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7501,7 +7477,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7528,10 +7504,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119850752</v>
+        <v>119851618</v>
       </c>
       <c r="B63" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7540,25 +7516,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7568,13 +7544,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609068</v>
+        <v>609113</v>
       </c>
       <c r="R63" t="n">
-        <v>7062927</v>
+        <v>7062853</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7598,17 +7574,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7635,7 +7606,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119851185</v>
+        <v>119850096</v>
       </c>
       <c r="B64" t="n">
         <v>97930</v>
@@ -7668,20 +7639,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>609097</v>
+        <v>608905</v>
       </c>
       <c r="R64" t="n">
-        <v>7062964</v>
+        <v>7062586</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7705,12 +7680,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7725,19 +7710,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119851502</v>
+        <v>119850720</v>
       </c>
       <c r="B65" t="n">
         <v>97930</v>
@@ -7770,20 +7755,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>609140</v>
+        <v>608957</v>
       </c>
       <c r="R65" t="n">
-        <v>7062863</v>
+        <v>7062678</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7810,9 +7799,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7827,22 +7826,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119850562</v>
+        <v>119849724</v>
       </c>
       <c r="B66" t="n">
-        <v>91146</v>
+        <v>78542</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7851,25 +7850,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7879,10 +7878,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>608992</v>
+        <v>608908</v>
       </c>
       <c r="R66" t="n">
-        <v>7062626</v>
+        <v>7062658</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7914,7 +7913,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7924,7 +7923,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7951,10 +7950,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119849903</v>
+        <v>119849717</v>
       </c>
       <c r="B67" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7967,21 +7966,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7991,10 +7990,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>608950</v>
+        <v>608896</v>
       </c>
       <c r="R67" t="n">
-        <v>7062709</v>
+        <v>7062656</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8024,9 +8023,24 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8041,22 +8055,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119851973</v>
+        <v>119849829</v>
       </c>
       <c r="B68" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8069,21 +8083,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8093,10 +8107,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>609151</v>
+        <v>608941</v>
       </c>
       <c r="R68" t="n">
-        <v>7062747</v>
+        <v>7062708</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8155,10 +8169,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119850006</v>
+        <v>119851329</v>
       </c>
       <c r="B69" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8167,25 +8181,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8195,13 +8209,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>609003</v>
+        <v>609091</v>
       </c>
       <c r="R69" t="n">
-        <v>7062728</v>
+        <v>7062941</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8225,12 +8239,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8257,10 +8271,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119852025</v>
+        <v>119850115</v>
       </c>
       <c r="B70" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8269,25 +8283,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8297,13 +8311,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>609136</v>
+        <v>609002</v>
       </c>
       <c r="R70" t="n">
-        <v>7062753</v>
+        <v>7062743</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8359,10 +8373,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119851928</v>
+        <v>119851428</v>
       </c>
       <c r="B71" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8371,25 +8385,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8399,13 +8413,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609172</v>
+        <v>609133</v>
       </c>
       <c r="R71" t="n">
-        <v>7062778</v>
+        <v>7062851</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8461,10 +8475,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119850568</v>
+        <v>119851274</v>
       </c>
       <c r="B72" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8473,38 +8487,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>609033</v>
+        <v>609039</v>
       </c>
       <c r="R72" t="n">
-        <v>7062884</v>
+        <v>7062654</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8534,9 +8553,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8551,19 +8580,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119850436</v>
+        <v>119851502</v>
       </c>
       <c r="B73" t="n">
         <v>97930</v>
@@ -8603,10 +8632,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>609002</v>
+        <v>609140</v>
       </c>
       <c r="R73" t="n">
-        <v>7062810</v>
+        <v>7062863</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8665,10 +8694,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119851695</v>
+        <v>119850568</v>
       </c>
       <c r="B74" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8677,46 +8706,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>609150</v>
+        <v>609033</v>
       </c>
       <c r="R74" t="n">
-        <v>7062808</v>
+        <v>7062884</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8772,10 +8796,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119849829</v>
+        <v>119849966</v>
       </c>
       <c r="B75" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8784,38 +8808,42 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>608941</v>
+        <v>608853</v>
       </c>
       <c r="R75" t="n">
-        <v>7062708</v>
+        <v>7062579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8845,9 +8873,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8862,22 +8900,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119849721</v>
+        <v>119851993</v>
       </c>
       <c r="B76" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8890,21 +8928,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8914,10 +8952,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>608918</v>
+        <v>609135</v>
       </c>
       <c r="R76" t="n">
-        <v>7062673</v>
+        <v>7062752</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8976,10 +9014,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119850876</v>
+        <v>119851684</v>
       </c>
       <c r="B77" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8992,21 +9030,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9016,13 +9054,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>609066</v>
+        <v>609149</v>
       </c>
       <c r="R77" t="n">
-        <v>7062980</v>
+        <v>7062828</v>
       </c>
       <c r="S77" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9078,10 +9116,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119850115</v>
+        <v>119849903</v>
       </c>
       <c r="B78" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9090,25 +9128,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9118,13 +9156,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>609002</v>
+        <v>608950</v>
       </c>
       <c r="R78" t="n">
-        <v>7062743</v>
+        <v>7062709</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9180,10 +9218,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119851251</v>
+        <v>119849905</v>
       </c>
       <c r="B79" t="n">
-        <v>90580</v>
+        <v>90600</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9196,21 +9234,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9220,10 +9258,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>609099</v>
+        <v>608876</v>
       </c>
       <c r="R79" t="n">
-        <v>7062948</v>
+        <v>7062635</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9253,9 +9291,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9270,19 +9318,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119849858</v>
+        <v>119849740</v>
       </c>
       <c r="B80" t="n">
         <v>97930</v>
@@ -9317,7 +9365,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9326,10 +9374,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>608877</v>
+        <v>608907</v>
       </c>
       <c r="R80" t="n">
-        <v>7062639</v>
+        <v>7062655</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9361,7 +9409,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9371,7 +9419,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9398,10 +9446,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119850782</v>
+        <v>119851413</v>
       </c>
       <c r="B81" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9410,30 +9458,31 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9442,10 +9491,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>608954</v>
+        <v>609070</v>
       </c>
       <c r="R81" t="n">
-        <v>7062685</v>
+        <v>7062653</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9477,7 +9526,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9487,7 +9536,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9514,10 +9563,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119849630</v>
+        <v>119850850</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9530,21 +9579,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9554,13 +9603,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>608895</v>
+        <v>609076</v>
       </c>
       <c r="R82" t="n">
-        <v>7062683</v>
+        <v>7062968</v>
       </c>
       <c r="S82" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9590,11 +9639,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9621,10 +9665,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119849658</v>
+        <v>119851377</v>
       </c>
       <c r="B83" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9637,39 +9681,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>608890</v>
+        <v>609065</v>
       </c>
       <c r="R83" t="n">
-        <v>7062664</v>
+        <v>7062657</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9701,7 +9740,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9711,7 +9750,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9738,10 +9777,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119850955</v>
+        <v>119851251</v>
       </c>
       <c r="B84" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9754,21 +9793,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9778,10 +9817,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>609006</v>
+        <v>609099</v>
       </c>
       <c r="R84" t="n">
-        <v>7062681</v>
+        <v>7062948</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9811,19 +9850,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9838,22 +9867,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119851684</v>
+        <v>119850220</v>
       </c>
       <c r="B85" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9866,21 +9895,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9890,13 +9919,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>609149</v>
+        <v>608994</v>
       </c>
       <c r="R85" t="n">
-        <v>7062828</v>
+        <v>7062775</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9920,12 +9949,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9952,10 +9981,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119850220</v>
+        <v>119851306</v>
       </c>
       <c r="B86" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9964,38 +9993,42 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>608994</v>
+        <v>609039</v>
       </c>
       <c r="R86" t="n">
-        <v>7062775</v>
+        <v>7062664</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10022,12 +10055,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10042,22 +10085,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119851274</v>
+        <v>119850321</v>
       </c>
       <c r="B87" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10070,42 +10113,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>609039</v>
+        <v>609015</v>
       </c>
       <c r="R87" t="n">
-        <v>7062654</v>
+        <v>7062798</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10132,19 +10170,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10159,22 +10187,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119851306</v>
+        <v>119849971</v>
       </c>
       <c r="B88" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10183,42 +10211,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>609039</v>
+        <v>608977</v>
       </c>
       <c r="R88" t="n">
-        <v>7062664</v>
+        <v>7062755</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10248,19 +10272,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10275,22 +10289,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119850321</v>
+        <v>119851185</v>
       </c>
       <c r="B89" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10299,25 +10313,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10327,10 +10341,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>609015</v>
+        <v>609097</v>
       </c>
       <c r="R89" t="n">
-        <v>7062798</v>
+        <v>7062964</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -10357,12 +10371,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10389,10 +10403,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119851290</v>
+        <v>119850876</v>
       </c>
       <c r="B90" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10405,21 +10419,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10429,13 +10443,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>609054</v>
+        <v>609066</v>
       </c>
       <c r="R90" t="n">
-        <v>7062684</v>
+        <v>7062980</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10462,19 +10476,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:01</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:01</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10489,22 +10493,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119850096</v>
+        <v>119851695</v>
       </c>
       <c r="B91" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10513,30 +10517,31 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -10545,13 +10550,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>608905</v>
+        <v>609150</v>
       </c>
       <c r="R91" t="n">
-        <v>7062586</v>
+        <v>7062808</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10578,19 +10583,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>13:47</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>13:47</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10605,22 +10600,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119851047</v>
+        <v>119849708</v>
       </c>
       <c r="B92" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10629,42 +10624,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>609018</v>
+        <v>608910</v>
       </c>
       <c r="R92" t="n">
-        <v>7062666</v>
+        <v>7062662</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10694,19 +10685,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10721,22 +10702,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119849742</v>
+        <v>119851973</v>
       </c>
       <c r="B93" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10749,21 +10730,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10773,13 +10754,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>608916</v>
+        <v>609151</v>
       </c>
       <c r="R93" t="n">
-        <v>7062680</v>
+        <v>7062747</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10835,10 +10816,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119851428</v>
+        <v>119852025</v>
       </c>
       <c r="B94" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10847,25 +10828,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10875,13 +10856,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>609133</v>
+        <v>609136</v>
       </c>
       <c r="R94" t="n">
-        <v>7062851</v>
+        <v>7062753</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10937,10 +10918,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119851664</v>
+        <v>119851047</v>
       </c>
       <c r="B95" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10949,38 +10930,42 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>609125</v>
+        <v>609018</v>
       </c>
       <c r="R95" t="n">
-        <v>7062827</v>
+        <v>7062666</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11010,9 +10995,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11027,19 +11022,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119850519</v>
+        <v>119850752</v>
       </c>
       <c r="B96" t="n">
         <v>97930</v>
@@ -11079,10 +11074,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>609012</v>
+        <v>609068</v>
       </c>
       <c r="R96" t="n">
-        <v>7062828</v>
+        <v>7062927</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11109,12 +11104,17 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11141,7 +11141,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119850411</v>
+        <v>119850188</v>
       </c>
       <c r="B97" t="n">
         <v>97930</v>
@@ -11181,13 +11181,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>609003</v>
+        <v>608997</v>
       </c>
       <c r="R97" t="n">
-        <v>7062803</v>
+        <v>7062738</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11243,10 +11243,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119849755</v>
+        <v>119851421</v>
       </c>
       <c r="B98" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11259,21 +11259,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11283,10 +11283,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>608914</v>
+        <v>609130</v>
       </c>
       <c r="R98" t="n">
-        <v>7062689</v>
+        <v>7062851</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -11345,10 +11345,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119849973</v>
+        <v>119851104</v>
       </c>
       <c r="B99" t="n">
-        <v>79652</v>
+        <v>78542</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11357,25 +11357,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11385,13 +11385,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>608986</v>
+        <v>609085</v>
       </c>
       <c r="R99" t="n">
-        <v>7062749</v>
+        <v>7062996</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11421,6 +11421,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11447,7 +11452,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119851993</v>
+        <v>119851950</v>
       </c>
       <c r="B100" t="n">
         <v>79623</v>
@@ -11487,13 +11492,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>609135</v>
+        <v>609160</v>
       </c>
       <c r="R100" t="n">
-        <v>7062752</v>
+        <v>7062762</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11549,10 +11554,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119851104</v>
+        <v>119851361</v>
       </c>
       <c r="B101" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11565,21 +11570,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11589,13 +11594,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>609085</v>
+        <v>609100</v>
       </c>
       <c r="R101" t="n">
-        <v>7062996</v>
+        <v>7062937</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11619,17 +11624,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11656,10 +11656,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119850834</v>
+        <v>119851732</v>
       </c>
       <c r="B102" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11672,21 +11672,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11696,13 +11696,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>609080</v>
+        <v>609149</v>
       </c>
       <c r="R102" t="n">
-        <v>7062946</v>
+        <v>7062808</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11758,10 +11758,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119849724</v>
+        <v>119851664</v>
       </c>
       <c r="B103" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11774,21 +11774,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11798,10 +11798,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>608908</v>
+        <v>609125</v>
       </c>
       <c r="R103" t="n">
-        <v>7062658</v>
+        <v>7062827</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11831,19 +11831,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11858,22 +11848,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119851235</v>
+        <v>119849658</v>
       </c>
       <c r="B104" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11882,41 +11872,46 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>609101</v>
+        <v>608890</v>
       </c>
       <c r="R104" t="n">
-        <v>7062955</v>
+        <v>7062664</v>
       </c>
       <c r="S104" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11943,9 +11938,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11960,22 +11965,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119850188</v>
+        <v>119850006</v>
       </c>
       <c r="B105" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11984,25 +11989,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12012,10 +12017,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>608997</v>
+        <v>609003</v>
       </c>
       <c r="R105" t="n">
-        <v>7062738</v>
+        <v>7062728</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -12074,10 +12079,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119849971</v>
+        <v>119849742</v>
       </c>
       <c r="B106" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12090,21 +12095,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12114,13 +12119,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>608977</v>
+        <v>608916</v>
       </c>
       <c r="R106" t="n">
-        <v>7062755</v>
+        <v>7062680</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12176,10 +12181,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119851377</v>
+        <v>119849721</v>
       </c>
       <c r="B107" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12192,21 +12197,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12216,10 +12221,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>609065</v>
+        <v>608918</v>
       </c>
       <c r="R107" t="n">
-        <v>7062657</v>
+        <v>7062673</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12249,19 +12254,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12276,22 +12271,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119851950</v>
+        <v>119850782</v>
       </c>
       <c r="B108" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12300,41 +12295,45 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>609160</v>
+        <v>608954</v>
       </c>
       <c r="R108" t="n">
-        <v>7062762</v>
+        <v>7062685</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12361,9 +12360,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12378,19 +12387,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119850459</v>
+        <v>119851160</v>
       </c>
       <c r="B109" t="n">
         <v>57320</v>
@@ -12435,10 +12444,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>608949</v>
+        <v>609023</v>
       </c>
       <c r="R109" t="n">
-        <v>7062585</v>
+        <v>7062674</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12470,7 +12479,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12480,7 +12489,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12507,10 +12516,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119849740</v>
+        <v>119849630</v>
       </c>
       <c r="B110" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12519,45 +12528,41 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>608907</v>
+        <v>608895</v>
       </c>
       <c r="R110" t="n">
-        <v>7062655</v>
+        <v>7062683</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12584,19 +12589,14 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>13:22</t>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12611,12 +12611,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -8067,10 +8067,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119849829</v>
+        <v>119851428</v>
       </c>
       <c r="B68" t="n">
-        <v>90580</v>
+        <v>79659</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8079,25 +8079,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8107,13 +8107,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>608941</v>
+        <v>609133</v>
       </c>
       <c r="R68" t="n">
-        <v>7062708</v>
+        <v>7062851</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8169,10 +8169,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119851329</v>
+        <v>119851274</v>
       </c>
       <c r="B69" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8181,38 +8181,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>609091</v>
+        <v>609039</v>
       </c>
       <c r="R69" t="n">
-        <v>7062941</v>
+        <v>7062654</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8239,12 +8244,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8259,22 +8274,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119850115</v>
+        <v>119849829</v>
       </c>
       <c r="B70" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8283,25 +8298,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8311,13 +8326,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>609002</v>
+        <v>608941</v>
       </c>
       <c r="R70" t="n">
-        <v>7062743</v>
+        <v>7062708</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8373,10 +8388,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119851428</v>
+        <v>119851329</v>
       </c>
       <c r="B71" t="n">
-        <v>79659</v>
+        <v>97930</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8385,25 +8400,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8413,13 +8428,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609133</v>
+        <v>609091</v>
       </c>
       <c r="R71" t="n">
-        <v>7062851</v>
+        <v>7062941</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8443,12 +8458,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8475,10 +8490,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119851274</v>
+        <v>119850115</v>
       </c>
       <c r="B72" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8487,46 +8502,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>609039</v>
+        <v>609002</v>
       </c>
       <c r="R72" t="n">
-        <v>7062654</v>
+        <v>7062743</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8553,19 +8563,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>15:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8580,22 +8580,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119851502</v>
+        <v>119851993</v>
       </c>
       <c r="B73" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8604,25 +8604,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8632,13 +8632,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>609140</v>
+        <v>609135</v>
       </c>
       <c r="R73" t="n">
-        <v>7062863</v>
+        <v>7062752</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119850568</v>
+        <v>119849966</v>
       </c>
       <c r="B74" t="n">
         <v>97930</v>
@@ -8727,17 +8727,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>609033</v>
+        <v>608853</v>
       </c>
       <c r="R74" t="n">
-        <v>7062884</v>
+        <v>7062579</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8767,9 +8771,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8784,19 +8798,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119849966</v>
+        <v>119851502</v>
       </c>
       <c r="B75" t="n">
         <v>97930</v>
@@ -8829,24 +8843,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>608853</v>
+        <v>609140</v>
       </c>
       <c r="R75" t="n">
-        <v>7062579</v>
+        <v>7062863</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8873,19 +8883,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8900,22 +8900,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119851993</v>
+        <v>119850568</v>
       </c>
       <c r="B76" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8924,25 +8924,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8952,10 +8952,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>609135</v>
+        <v>609033</v>
       </c>
       <c r="R76" t="n">
-        <v>7062752</v>
+        <v>7062884</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9330,10 +9330,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119849740</v>
+        <v>119851251</v>
       </c>
       <c r="B80" t="n">
-        <v>97930</v>
+        <v>90580</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9342,42 +9342,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>608907</v>
+        <v>609099</v>
       </c>
       <c r="R80" t="n">
-        <v>7062655</v>
+        <v>7062948</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9407,19 +9403,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>13:22</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>13:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9434,22 +9420,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119851413</v>
+        <v>119850220</v>
       </c>
       <c r="B81" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9462,39 +9448,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>609070</v>
+        <v>608994</v>
       </c>
       <c r="R81" t="n">
-        <v>7062653</v>
+        <v>7062775</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9521,22 +9502,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>15:14</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9551,22 +9522,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119850850</v>
+        <v>119851413</v>
       </c>
       <c r="B82" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9579,34 +9550,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>609076</v>
+        <v>609070</v>
       </c>
       <c r="R82" t="n">
-        <v>7062968</v>
+        <v>7062653</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9636,9 +9612,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9653,19 +9639,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119851377</v>
+        <v>119850850</v>
       </c>
       <c r="B83" t="n">
         <v>79623</v>
@@ -9705,10 +9691,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>609065</v>
+        <v>609076</v>
       </c>
       <c r="R83" t="n">
-        <v>7062657</v>
+        <v>7062968</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9738,19 +9724,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9765,22 +9741,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119851251</v>
+        <v>119851377</v>
       </c>
       <c r="B84" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9793,21 +9769,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9817,10 +9793,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>609099</v>
+        <v>609065</v>
       </c>
       <c r="R84" t="n">
-        <v>7062948</v>
+        <v>7062657</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9850,9 +9826,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9867,22 +9853,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119850220</v>
+        <v>119849740</v>
       </c>
       <c r="B85" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9891,38 +9877,42 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>608994</v>
+        <v>608907</v>
       </c>
       <c r="R85" t="n">
-        <v>7062775</v>
+        <v>7062655</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9949,12 +9939,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9969,22 +9969,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119851306</v>
+        <v>119850321</v>
       </c>
       <c r="B86" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9993,45 +9993,41 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>609039</v>
+        <v>609015</v>
       </c>
       <c r="R86" t="n">
-        <v>7062664</v>
+        <v>7062798</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10058,19 +10054,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10085,22 +10071,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119850321</v>
+        <v>119851306</v>
       </c>
       <c r="B87" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10109,41 +10095,45 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>609015</v>
+        <v>609039</v>
       </c>
       <c r="R87" t="n">
-        <v>7062798</v>
+        <v>7062664</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10170,9 +10160,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10187,22 +10187,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119849971</v>
+        <v>119851185</v>
       </c>
       <c r="B88" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10211,25 +10211,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10239,13 +10239,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>608977</v>
+        <v>609097</v>
       </c>
       <c r="R88" t="n">
-        <v>7062755</v>
+        <v>7062964</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10269,12 +10269,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10301,10 +10301,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119851185</v>
+        <v>119849971</v>
       </c>
       <c r="B89" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10313,25 +10313,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10341,13 +10341,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>609097</v>
+        <v>608977</v>
       </c>
       <c r="R89" t="n">
-        <v>7062964</v>
+        <v>7062755</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10371,12 +10371,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10918,10 +10918,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119851047</v>
+        <v>119851421</v>
       </c>
       <c r="B95" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10930,45 +10930,41 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>609018</v>
+        <v>609130</v>
       </c>
       <c r="R95" t="n">
-        <v>7062666</v>
+        <v>7062851</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10995,19 +10991,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11022,22 +11008,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119850752</v>
+        <v>119851104</v>
       </c>
       <c r="B96" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11046,25 +11032,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11074,13 +11060,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>609068</v>
+        <v>609085</v>
       </c>
       <c r="R96" t="n">
-        <v>7062927</v>
+        <v>7062996</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11104,12 +11090,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -11141,10 +11127,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119850188</v>
+        <v>119851950</v>
       </c>
       <c r="B97" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11153,25 +11139,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11181,10 +11167,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>608997</v>
+        <v>609160</v>
       </c>
       <c r="R97" t="n">
-        <v>7062738</v>
+        <v>7062762</v>
       </c>
       <c r="S97" t="n">
         <v>15</v>
@@ -11243,7 +11229,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119851421</v>
+        <v>119851361</v>
       </c>
       <c r="B98" t="n">
         <v>79623</v>
@@ -11283,10 +11269,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>609130</v>
+        <v>609100</v>
       </c>
       <c r="R98" t="n">
-        <v>7062851</v>
+        <v>7062937</v>
       </c>
       <c r="S98" t="n">
         <v>15</v>
@@ -11313,12 +11299,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11345,10 +11331,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119851104</v>
+        <v>119851047</v>
       </c>
       <c r="B99" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11357,41 +11343,45 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>609085</v>
+        <v>609018</v>
       </c>
       <c r="R99" t="n">
-        <v>7062996</v>
+        <v>7062666</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11418,14 +11408,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11440,22 +11435,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119851950</v>
+        <v>119850752</v>
       </c>
       <c r="B100" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11464,25 +11459,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11492,13 +11487,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>609160</v>
+        <v>609068</v>
       </c>
       <c r="R100" t="n">
-        <v>7062762</v>
+        <v>7062927</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11522,12 +11517,17 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11554,10 +11554,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119851361</v>
+        <v>119850188</v>
       </c>
       <c r="B101" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11566,25 +11566,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11594,10 +11594,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>609100</v>
+        <v>608997</v>
       </c>
       <c r="R101" t="n">
-        <v>7062937</v>
+        <v>7062738</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11624,12 +11624,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD101" t="b">

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -5390,10 +5390,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119850926</v>
+        <v>119851290</v>
       </c>
       <c r="B43" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5406,39 +5406,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>609003</v>
+        <v>609054</v>
       </c>
       <c r="R43" t="n">
-        <v>7062700</v>
+        <v>7062684</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5470,7 +5465,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5480,7 +5475,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5507,10 +5502,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119851878</v>
+        <v>119851329</v>
       </c>
       <c r="B44" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5519,25 +5514,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5547,10 +5542,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>609153</v>
+        <v>609091</v>
       </c>
       <c r="R44" t="n">
-        <v>7062778</v>
+        <v>7062941</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5577,12 +5572,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5609,10 +5604,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119851928</v>
+        <v>119851235</v>
       </c>
       <c r="B45" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5621,25 +5616,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5649,13 +5644,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>609172</v>
+        <v>609101</v>
       </c>
       <c r="R45" t="n">
-        <v>7062778</v>
+        <v>7062955</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5711,10 +5706,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119850656</v>
+        <v>119849905</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>90600</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5723,25 +5718,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5751,10 +5746,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>609048</v>
+        <v>608876</v>
       </c>
       <c r="R46" t="n">
-        <v>7062921</v>
+        <v>7062635</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5784,9 +5779,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5801,22 +5806,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119850834</v>
+        <v>119851973</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5829,21 +5834,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5853,13 +5858,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>609080</v>
+        <v>609151</v>
       </c>
       <c r="R47" t="n">
-        <v>7062946</v>
+        <v>7062747</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5915,10 +5920,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119849755</v>
+        <v>119852068</v>
       </c>
       <c r="B48" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5931,21 +5936,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5955,13 +5960,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>608914</v>
+        <v>609119</v>
       </c>
       <c r="R48" t="n">
-        <v>7062689</v>
+        <v>7062737</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6017,10 +6022,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119851235</v>
+        <v>119851695</v>
       </c>
       <c r="B49" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6029,41 +6034,46 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>609101</v>
+        <v>609150</v>
       </c>
       <c r="R49" t="n">
-        <v>7062955</v>
+        <v>7062808</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6119,10 +6129,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119849973</v>
+        <v>119850568</v>
       </c>
       <c r="B50" t="n">
-        <v>79652</v>
+        <v>97930</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6131,25 +6141,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6159,13 +6169,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>608986</v>
+        <v>609033</v>
       </c>
       <c r="R50" t="n">
-        <v>7062749</v>
+        <v>7062884</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6221,7 +6231,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119850519</v>
+        <v>119850115</v>
       </c>
       <c r="B51" t="n">
         <v>97930</v>
@@ -6261,13 +6271,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>609012</v>
+        <v>609002</v>
       </c>
       <c r="R51" t="n">
-        <v>7062828</v>
+        <v>7062743</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6323,10 +6333,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119850411</v>
+        <v>119850834</v>
       </c>
       <c r="B52" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6335,25 +6345,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6363,13 +6373,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>609003</v>
+        <v>609080</v>
       </c>
       <c r="R52" t="n">
-        <v>7062803</v>
+        <v>7062946</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6425,10 +6435,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119851802</v>
+        <v>119850876</v>
       </c>
       <c r="B53" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6441,21 +6451,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6465,13 +6475,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>609143</v>
+        <v>609066</v>
       </c>
       <c r="R53" t="n">
-        <v>7062799</v>
+        <v>7062980</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6527,10 +6537,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119851641</v>
+        <v>119851421</v>
       </c>
       <c r="B54" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6539,25 +6549,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6567,10 +6577,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>609109</v>
+        <v>609130</v>
       </c>
       <c r="R54" t="n">
-        <v>7062833</v>
+        <v>7062851</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6629,10 +6639,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119850436</v>
+        <v>119851928</v>
       </c>
       <c r="B55" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6641,25 +6651,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6669,13 +6679,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>609002</v>
+        <v>609172</v>
       </c>
       <c r="R55" t="n">
-        <v>7062810</v>
+        <v>7062778</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6731,10 +6741,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119849858</v>
+        <v>119849630</v>
       </c>
       <c r="B56" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6743,45 +6753,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>608877</v>
+        <v>608895</v>
       </c>
       <c r="R56" t="n">
-        <v>7062639</v>
+        <v>7062683</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6808,19 +6814,14 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:27</t>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6835,22 +6836,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119851861</v>
+        <v>119849721</v>
       </c>
       <c r="B57" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6863,21 +6864,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6887,13 +6888,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>609153</v>
+        <v>608918</v>
       </c>
       <c r="R57" t="n">
-        <v>7062783</v>
+        <v>7062673</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6949,10 +6950,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119852068</v>
+        <v>119850926</v>
       </c>
       <c r="B58" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6965,34 +6966,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>609119</v>
+        <v>609003</v>
       </c>
       <c r="R58" t="n">
-        <v>7062737</v>
+        <v>7062700</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7022,9 +7028,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7039,19 +7055,19 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119851290</v>
+        <v>119850955</v>
       </c>
       <c r="B59" t="n">
         <v>79623</v>
@@ -7091,10 +7107,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>609054</v>
+        <v>609006</v>
       </c>
       <c r="R59" t="n">
-        <v>7062684</v>
+        <v>7062681</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7126,7 +7142,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7136,7 +7152,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7163,10 +7179,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119850459</v>
+        <v>119851377</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7179,39 +7195,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>608949</v>
+        <v>609065</v>
       </c>
       <c r="R60" t="n">
-        <v>7062585</v>
+        <v>7062657</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7243,7 +7254,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7253,7 +7264,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7280,10 +7291,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119850562</v>
+        <v>119850459</v>
       </c>
       <c r="B61" t="n">
-        <v>91146</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7292,38 +7303,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>608992</v>
+        <v>608949</v>
       </c>
       <c r="R61" t="n">
-        <v>7062626</v>
+        <v>7062585</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7355,7 +7371,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7365,7 +7381,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7392,10 +7408,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119850955</v>
+        <v>119850188</v>
       </c>
       <c r="B62" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7404,25 +7420,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7432,13 +7448,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>609006</v>
+        <v>608997</v>
       </c>
       <c r="R62" t="n">
-        <v>7062681</v>
+        <v>7062738</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7465,19 +7481,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>14:42</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7492,22 +7498,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119851618</v>
+        <v>119850411</v>
       </c>
       <c r="B63" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7516,25 +7522,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7544,13 +7550,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>609113</v>
+        <v>609003</v>
       </c>
       <c r="R63" t="n">
-        <v>7062853</v>
+        <v>7062803</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7606,7 +7612,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119850096</v>
+        <v>119849858</v>
       </c>
       <c r="B64" t="n">
         <v>97930</v>
@@ -7650,10 +7656,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>608905</v>
+        <v>608877</v>
       </c>
       <c r="R64" t="n">
-        <v>7062586</v>
+        <v>7062639</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7685,7 +7691,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7695,7 +7701,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7722,10 +7728,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119850720</v>
+        <v>119850321</v>
       </c>
       <c r="B65" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7734,45 +7740,41 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>608957</v>
+        <v>609015</v>
       </c>
       <c r="R65" t="n">
-        <v>7062678</v>
+        <v>7062798</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7799,19 +7801,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>14:23</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7826,22 +7818,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119849724</v>
+        <v>119850220</v>
       </c>
       <c r="B66" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7854,21 +7846,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7878,10 +7870,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>608908</v>
+        <v>608994</v>
       </c>
       <c r="R66" t="n">
-        <v>7062658</v>
+        <v>7062775</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7908,22 +7900,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7938,22 +7920,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119849717</v>
+        <v>119849755</v>
       </c>
       <c r="B67" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7966,21 +7948,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7990,13 +7972,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>608896</v>
+        <v>608914</v>
       </c>
       <c r="R67" t="n">
-        <v>7062656</v>
+        <v>7062689</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8023,24 +8005,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8055,22 +8022,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119851428</v>
+        <v>119849971</v>
       </c>
       <c r="B68" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8079,25 +8046,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8107,13 +8074,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>609133</v>
+        <v>608977</v>
       </c>
       <c r="R68" t="n">
-        <v>7062851</v>
+        <v>7062755</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8169,7 +8136,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119851274</v>
+        <v>119849658</v>
       </c>
       <c r="B69" t="n">
         <v>57320</v>
@@ -8214,10 +8181,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>609039</v>
+        <v>608890</v>
       </c>
       <c r="R69" t="n">
-        <v>7062654</v>
+        <v>7062664</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8249,7 +8216,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8259,7 +8226,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8286,10 +8253,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119849829</v>
+        <v>119850850</v>
       </c>
       <c r="B70" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8302,21 +8269,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8326,10 +8293,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>608941</v>
+        <v>609076</v>
       </c>
       <c r="R70" t="n">
-        <v>7062708</v>
+        <v>7062968</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8388,10 +8355,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119851329</v>
+        <v>119851732</v>
       </c>
       <c r="B71" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8400,25 +8367,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8428,10 +8395,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>609091</v>
+        <v>609149</v>
       </c>
       <c r="R71" t="n">
-        <v>7062941</v>
+        <v>7062808</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8458,12 +8425,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8490,10 +8457,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119850115</v>
+        <v>119851802</v>
       </c>
       <c r="B72" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8502,25 +8469,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8530,13 +8497,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>609002</v>
+        <v>609143</v>
       </c>
       <c r="R72" t="n">
-        <v>7062743</v>
+        <v>7062799</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8592,7 +8559,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119851993</v>
+        <v>119851878</v>
       </c>
       <c r="B73" t="n">
         <v>79623</v>
@@ -8632,10 +8599,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>609135</v>
+        <v>609153</v>
       </c>
       <c r="R73" t="n">
-        <v>7062752</v>
+        <v>7062778</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8694,7 +8661,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119849966</v>
+        <v>119850096</v>
       </c>
       <c r="B74" t="n">
         <v>97930</v>
@@ -8729,7 +8696,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8738,10 +8705,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>608853</v>
+        <v>608905</v>
       </c>
       <c r="R74" t="n">
-        <v>7062579</v>
+        <v>7062586</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8773,7 +8740,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8783,7 +8750,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8810,7 +8777,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119851502</v>
+        <v>119850519</v>
       </c>
       <c r="B75" t="n">
         <v>97930</v>
@@ -8850,13 +8817,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>609140</v>
+        <v>609012</v>
       </c>
       <c r="R75" t="n">
-        <v>7062863</v>
+        <v>7062828</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8912,7 +8879,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119850568</v>
+        <v>119851502</v>
       </c>
       <c r="B76" t="n">
         <v>97930</v>
@@ -8952,13 +8919,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>609033</v>
+        <v>609140</v>
       </c>
       <c r="R76" t="n">
-        <v>7062884</v>
+        <v>7062863</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9014,10 +8981,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119851684</v>
+        <v>119851047</v>
       </c>
       <c r="B77" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9026,41 +8993,45 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>609149</v>
+        <v>609018</v>
       </c>
       <c r="R77" t="n">
-        <v>7062828</v>
+        <v>7062666</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9087,9 +9058,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9104,19 +9085,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119849903</v>
+        <v>119849829</v>
       </c>
       <c r="B78" t="n">
         <v>90580</v>
@@ -9156,10 +9137,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>608950</v>
+        <v>608941</v>
       </c>
       <c r="R78" t="n">
-        <v>7062709</v>
+        <v>7062708</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9218,10 +9199,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119849905</v>
+        <v>119851861</v>
       </c>
       <c r="B79" t="n">
-        <v>90600</v>
+        <v>79623</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9234,21 +9215,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9258,13 +9239,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>608876</v>
+        <v>609153</v>
       </c>
       <c r="R79" t="n">
-        <v>7062635</v>
+        <v>7062783</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9291,19 +9272,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9318,22 +9289,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119851251</v>
+        <v>119851361</v>
       </c>
       <c r="B80" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9346,21 +9317,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9370,13 +9341,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>609099</v>
+        <v>609100</v>
       </c>
       <c r="R80" t="n">
-        <v>7062948</v>
+        <v>7062937</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9400,12 +9371,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9432,10 +9403,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119850220</v>
+        <v>119849740</v>
       </c>
       <c r="B81" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9444,38 +9415,42 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>608994</v>
+        <v>608907</v>
       </c>
       <c r="R81" t="n">
-        <v>7062775</v>
+        <v>7062655</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9502,12 +9477,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9522,22 +9507,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119851413</v>
+        <v>119849724</v>
       </c>
       <c r="B82" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9550,39 +9535,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>609070</v>
+        <v>608908</v>
       </c>
       <c r="R82" t="n">
-        <v>7062653</v>
+        <v>7062658</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9614,7 +9594,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9624,7 +9604,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9651,10 +9631,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119850850</v>
+        <v>119851251</v>
       </c>
       <c r="B83" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9667,21 +9647,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9691,10 +9671,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>609076</v>
+        <v>609099</v>
       </c>
       <c r="R83" t="n">
-        <v>7062968</v>
+        <v>7062948</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9753,7 +9733,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119851377</v>
+        <v>119850006</v>
       </c>
       <c r="B84" t="n">
         <v>79623</v>
@@ -9793,13 +9773,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>609065</v>
+        <v>609003</v>
       </c>
       <c r="R84" t="n">
-        <v>7062657</v>
+        <v>7062728</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9826,19 +9806,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>15:08</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>15:08</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9853,22 +9823,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119849740</v>
+        <v>119851160</v>
       </c>
       <c r="B85" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9877,30 +9847,31 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9909,10 +9880,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>608907</v>
+        <v>609023</v>
       </c>
       <c r="R85" t="n">
-        <v>7062655</v>
+        <v>7062674</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9944,7 +9915,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9954,7 +9925,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9981,10 +9952,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119850321</v>
+        <v>119850720</v>
       </c>
       <c r="B86" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9993,41 +9964,45 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>609015</v>
+        <v>608957</v>
       </c>
       <c r="R86" t="n">
-        <v>7062798</v>
+        <v>7062678</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10054,9 +10029,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10071,22 +10056,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119851306</v>
+        <v>119851950</v>
       </c>
       <c r="B87" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10095,45 +10080,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>609039</v>
+        <v>609160</v>
       </c>
       <c r="R87" t="n">
-        <v>7062664</v>
+        <v>7062762</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10160,19 +10141,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10187,22 +10158,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119851185</v>
+        <v>119851618</v>
       </c>
       <c r="B88" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10211,25 +10182,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10239,10 +10210,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>609097</v>
+        <v>609113</v>
       </c>
       <c r="R88" t="n">
-        <v>7062964</v>
+        <v>7062853</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -10269,12 +10240,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10301,10 +10272,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119849971</v>
+        <v>119849742</v>
       </c>
       <c r="B89" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10317,21 +10288,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10341,13 +10312,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>608977</v>
+        <v>608916</v>
       </c>
       <c r="R89" t="n">
-        <v>7062755</v>
+        <v>7062680</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10403,10 +10374,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119850876</v>
+        <v>119849717</v>
       </c>
       <c r="B90" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10419,21 +10390,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10443,13 +10414,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>609066</v>
+        <v>608896</v>
       </c>
       <c r="R90" t="n">
-        <v>7062980</v>
+        <v>7062656</v>
       </c>
       <c r="S90" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10476,9 +10447,24 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10493,22 +10479,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119851695</v>
+        <v>119851428</v>
       </c>
       <c r="B91" t="n">
-        <v>57473</v>
+        <v>79659</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10517,46 +10503,41 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>609150</v>
+        <v>609133</v>
       </c>
       <c r="R91" t="n">
-        <v>7062808</v>
+        <v>7062851</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10612,10 +10593,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119849708</v>
+        <v>119851684</v>
       </c>
       <c r="B92" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10628,21 +10609,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10652,13 +10633,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>608910</v>
+        <v>609149</v>
       </c>
       <c r="R92" t="n">
-        <v>7062662</v>
+        <v>7062828</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10714,10 +10695,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119851973</v>
+        <v>119851413</v>
       </c>
       <c r="B93" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10730,34 +10711,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>609151</v>
+        <v>609070</v>
       </c>
       <c r="R93" t="n">
-        <v>7062747</v>
+        <v>7062653</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10787,9 +10773,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10804,22 +10800,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119852025</v>
+        <v>119850436</v>
       </c>
       <c r="B94" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10828,25 +10824,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10856,13 +10852,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>609136</v>
+        <v>609002</v>
       </c>
       <c r="R94" t="n">
-        <v>7062753</v>
+        <v>7062810</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10918,10 +10914,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119851421</v>
+        <v>119849708</v>
       </c>
       <c r="B95" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10934,21 +10930,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10958,13 +10954,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>609130</v>
+        <v>608910</v>
       </c>
       <c r="R95" t="n">
-        <v>7062851</v>
+        <v>7062662</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11020,10 +11016,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119851104</v>
+        <v>119850562</v>
       </c>
       <c r="B96" t="n">
-        <v>78542</v>
+        <v>91146</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11032,25 +11028,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>760</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11060,13 +11056,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>609085</v>
+        <v>608992</v>
       </c>
       <c r="R96" t="n">
-        <v>7062996</v>
+        <v>7062626</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11093,14 +11089,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11115,22 +11116,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119851950</v>
+        <v>119851104</v>
       </c>
       <c r="B97" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11143,21 +11144,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11167,13 +11168,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>609160</v>
+        <v>609085</v>
       </c>
       <c r="R97" t="n">
-        <v>7062762</v>
+        <v>7062996</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11203,6 +11204,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11229,10 +11235,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119851361</v>
+        <v>119850782</v>
       </c>
       <c r="B98" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11241,41 +11247,45 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>609100</v>
+        <v>608954</v>
       </c>
       <c r="R98" t="n">
-        <v>7062937</v>
+        <v>7062685</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11299,12 +11309,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11319,19 +11339,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119851047</v>
+        <v>119850656</v>
       </c>
       <c r="B99" t="n">
         <v>97930</v>
@@ -11364,21 +11384,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>609018</v>
+        <v>609048</v>
       </c>
       <c r="R99" t="n">
-        <v>7062666</v>
+        <v>7062921</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11408,19 +11424,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:45</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11435,19 +11441,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119850752</v>
+        <v>119849966</v>
       </c>
       <c r="B100" t="n">
         <v>97930</v>
@@ -11480,17 +11486,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>609068</v>
+        <v>608853</v>
       </c>
       <c r="R100" t="n">
-        <v>7062927</v>
+        <v>7062579</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11517,17 +11527,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11542,22 +11557,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119850188</v>
+        <v>119849973</v>
       </c>
       <c r="B101" t="n">
-        <v>97930</v>
+        <v>79652</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11566,25 +11581,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11594,10 +11609,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>608997</v>
+        <v>608986</v>
       </c>
       <c r="R101" t="n">
-        <v>7062738</v>
+        <v>7062749</v>
       </c>
       <c r="S101" t="n">
         <v>15</v>
@@ -11656,10 +11671,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119851732</v>
+        <v>119851641</v>
       </c>
       <c r="B102" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11668,25 +11683,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11696,13 +11711,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>609149</v>
+        <v>609109</v>
       </c>
       <c r="R102" t="n">
-        <v>7062808</v>
+        <v>7062833</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11758,10 +11773,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119851664</v>
+        <v>119851306</v>
       </c>
       <c r="B103" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11770,38 +11785,42 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>609125</v>
+        <v>609039</v>
       </c>
       <c r="R103" t="n">
-        <v>7062827</v>
+        <v>7062664</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11831,9 +11850,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11848,22 +11877,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119849658</v>
+        <v>119851185</v>
       </c>
       <c r="B104" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11872,46 +11901,41 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>608890</v>
+        <v>609097</v>
       </c>
       <c r="R104" t="n">
-        <v>7062664</v>
+        <v>7062964</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11935,22 +11959,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11965,22 +11979,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119850006</v>
+        <v>119850752</v>
       </c>
       <c r="B105" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11989,25 +12003,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12017,13 +12031,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>609003</v>
+        <v>609068</v>
       </c>
       <c r="R105" t="n">
-        <v>7062728</v>
+        <v>7062927</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -12047,12 +12061,17 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12079,10 +12098,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119849742</v>
+        <v>119849903</v>
       </c>
       <c r="B106" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12095,21 +12114,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12119,13 +12138,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>608916</v>
+        <v>608950</v>
       </c>
       <c r="R106" t="n">
-        <v>7062680</v>
+        <v>7062709</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12181,10 +12200,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119849721</v>
+        <v>119851274</v>
       </c>
       <c r="B107" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12197,34 +12216,39 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>608918</v>
+        <v>609039</v>
       </c>
       <c r="R107" t="n">
-        <v>7062673</v>
+        <v>7062654</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12254,9 +12278,19 @@
           <t>2024-09-19</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12271,22 +12305,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119850782</v>
+        <v>119851993</v>
       </c>
       <c r="B108" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12295,42 +12329,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>608954</v>
+        <v>609135</v>
       </c>
       <c r="R108" t="n">
-        <v>7062685</v>
+        <v>7062752</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12360,19 +12390,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>14:27</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>14:27</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12387,22 +12407,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119851160</v>
+        <v>119851664</v>
       </c>
       <c r="B109" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12415,39 +12435,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>609023</v>
+        <v>609125</v>
       </c>
       <c r="R109" t="n">
-        <v>7062674</v>
+        <v>7062827</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12477,19 +12492,9 @@
           <t>2024-09-19</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12504,22 +12509,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119849630</v>
+        <v>119852025</v>
       </c>
       <c r="B110" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12532,21 +12537,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12556,13 +12561,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>608895</v>
+        <v>609136</v>
       </c>
       <c r="R110" t="n">
-        <v>7062683</v>
+        <v>7062753</v>
       </c>
       <c r="S110" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12592,11 +12597,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Riklig förekomst, även på tall.</t>
         </is>
       </c>
       <c r="AD110" t="b">

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -12848,7 +12848,7 @@
         <v>122742576</v>
       </c>
       <c r="B113" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12951,10 +12951,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122746839</v>
+        <v>122742575</v>
       </c>
       <c r="B114" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12987,14 +12987,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lill-Sännan N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>609241</v>
+        <v>609261</v>
       </c>
       <c r="R114" t="n">
-        <v>7062789</v>
+        <v>7062892</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13057,10 +13057,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122742575</v>
+        <v>122746839</v>
       </c>
       <c r="B115" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13093,14 +13093,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Lill-Sännan N, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>609261</v>
+        <v>609241</v>
       </c>
       <c r="R115" t="n">
-        <v>7062892</v>
+        <v>7062789</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13166,7 +13166,7 @@
         <v>122742574</v>
       </c>
       <c r="B116" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -12845,7 +12845,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122742576</v>
+        <v>122746839</v>
       </c>
       <c r="B113" t="n">
         <v>98355</v>
@@ -12881,14 +12881,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Lill-Sännan N, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>609298</v>
+        <v>609241</v>
       </c>
       <c r="R113" t="n">
-        <v>7062892</v>
+        <v>7062789</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13057,7 +13057,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122746839</v>
+        <v>122742576</v>
       </c>
       <c r="B115" t="n">
         <v>98355</v>
@@ -13093,14 +13093,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Lill-Sännan N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>609241</v>
+        <v>609298</v>
       </c>
       <c r="R115" t="n">
-        <v>7062789</v>
+        <v>7062892</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -12845,10 +12845,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122746839</v>
+        <v>122742576</v>
       </c>
       <c r="B113" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12881,14 +12881,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lill-Sännan N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>609241</v>
+        <v>609298</v>
       </c>
       <c r="R113" t="n">
-        <v>7062789</v>
+        <v>7062892</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12954,7 +12954,7 @@
         <v>122742575</v>
       </c>
       <c r="B114" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13057,10 +13057,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122742576</v>
+        <v>122746839</v>
       </c>
       <c r="B115" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13093,14 +13093,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Lill-Sännan N, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>609298</v>
+        <v>609241</v>
       </c>
       <c r="R115" t="n">
-        <v>7062892</v>
+        <v>7062789</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13166,7 +13166,7 @@
         <v>122742574</v>
       </c>
       <c r="B116" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -12845,7 +12845,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122742576</v>
+        <v>122742575</v>
       </c>
       <c r="B113" t="n">
         <v>98357</v>
@@ -12885,7 +12885,7 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>609298</v>
+        <v>609261</v>
       </c>
       <c r="R113" t="n">
         <v>7062892</v>
@@ -12951,7 +12951,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122742575</v>
+        <v>122742576</v>
       </c>
       <c r="B114" t="n">
         <v>98357</v>
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>609261</v>
+        <v>609298</v>
       </c>
       <c r="R114" t="n">
         <v>7062892</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -12845,10 +12845,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122742575</v>
+        <v>122742574</v>
       </c>
       <c r="B113" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12885,10 +12885,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>609261</v>
+        <v>609226</v>
       </c>
       <c r="R113" t="n">
-        <v>7062892</v>
+        <v>7062868</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12951,10 +12951,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122742576</v>
+        <v>122746839</v>
       </c>
       <c r="B114" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12987,14 +12987,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Lill-Sännan N, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>609298</v>
+        <v>609241</v>
       </c>
       <c r="R114" t="n">
-        <v>7062892</v>
+        <v>7062789</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13057,10 +13057,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122746839</v>
+        <v>122742576</v>
       </c>
       <c r="B115" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13093,14 +13093,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Lill-Sännan N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>609241</v>
+        <v>609298</v>
       </c>
       <c r="R115" t="n">
-        <v>7062789</v>
+        <v>7062892</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13163,10 +13163,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122742574</v>
+        <v>122742575</v>
       </c>
       <c r="B116" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13203,10 +13203,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>609226</v>
+        <v>609261</v>
       </c>
       <c r="R116" t="n">
-        <v>7062868</v>
+        <v>7062892</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -12951,7 +12951,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122746839</v>
+        <v>122742576</v>
       </c>
       <c r="B114" t="n">
         <v>98365</v>
@@ -12987,14 +12987,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lill-Sännan N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>609241</v>
+        <v>609298</v>
       </c>
       <c r="R114" t="n">
-        <v>7062789</v>
+        <v>7062892</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13057,7 +13057,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122742576</v>
+        <v>122746839</v>
       </c>
       <c r="B115" t="n">
         <v>98365</v>
@@ -13093,14 +13093,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Lill-Sännan N, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>609298</v>
+        <v>609241</v>
       </c>
       <c r="R115" t="n">
-        <v>7062892</v>
+        <v>7062789</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -12845,7 +12845,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122742574</v>
+        <v>122746839</v>
       </c>
       <c r="B113" t="n">
         <v>98365</v>
@@ -12881,14 +12881,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Lill-Sännan N, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>609226</v>
+        <v>609241</v>
       </c>
       <c r="R113" t="n">
-        <v>7062868</v>
+        <v>7062789</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12951,7 +12951,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122742576</v>
+        <v>122742575</v>
       </c>
       <c r="B114" t="n">
         <v>98365</v>
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>609298</v>
+        <v>609261</v>
       </c>
       <c r="R114" t="n">
         <v>7062892</v>
@@ -13057,7 +13057,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122746839</v>
+        <v>122742576</v>
       </c>
       <c r="B115" t="n">
         <v>98365</v>
@@ -13093,14 +13093,14 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Lill-Sännan N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>609241</v>
+        <v>609298</v>
       </c>
       <c r="R115" t="n">
-        <v>7062789</v>
+        <v>7062892</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13163,7 +13163,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122742575</v>
+        <v>122742574</v>
       </c>
       <c r="B116" t="n">
         <v>98365</v>
@@ -13203,10 +13203,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>609261</v>
+        <v>609226</v>
       </c>
       <c r="R116" t="n">
-        <v>7062892</v>
+        <v>7062868</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -12845,7 +12845,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122746839</v>
+        <v>122742575</v>
       </c>
       <c r="B113" t="n">
         <v>98365</v>
@@ -12881,14 +12881,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Lill-Sännan N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>609241</v>
+        <v>609261</v>
       </c>
       <c r="R113" t="n">
-        <v>7062789</v>
+        <v>7062892</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12951,7 +12951,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122742575</v>
+        <v>122742576</v>
       </c>
       <c r="B114" t="n">
         <v>98365</v>
@@ -12991,7 +12991,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>609261</v>
+        <v>609298</v>
       </c>
       <c r="R114" t="n">
         <v>7062892</v>
@@ -13057,7 +13057,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122742576</v>
+        <v>122742574</v>
       </c>
       <c r="B115" t="n">
         <v>98365</v>
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>609298</v>
+        <v>609226</v>
       </c>
       <c r="R115" t="n">
-        <v>7062892</v>
+        <v>7062868</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13163,7 +13163,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122742574</v>
+        <v>122746839</v>
       </c>
       <c r="B116" t="n">
         <v>98365</v>
@@ -13199,14 +13199,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Lill-Sännan N, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>609226</v>
+        <v>609241</v>
       </c>
       <c r="R116" t="n">
-        <v>7062868</v>
+        <v>7062789</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -12845,7 +12845,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122742575</v>
+        <v>122742574</v>
       </c>
       <c r="B113" t="n">
         <v>98365</v>
@@ -12885,10 +12885,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>609261</v>
+        <v>609226</v>
       </c>
       <c r="R113" t="n">
-        <v>7062892</v>
+        <v>7062868</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13057,7 +13057,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122742574</v>
+        <v>122742575</v>
       </c>
       <c r="B115" t="n">
         <v>98365</v>
@@ -13097,10 +13097,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>609226</v>
+        <v>609261</v>
       </c>
       <c r="R115" t="n">
-        <v>7062868</v>
+        <v>7062892</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -12848,7 +12848,7 @@
         <v>122742574</v>
       </c>
       <c r="B113" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12951,10 +12951,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122742576</v>
+        <v>122746839</v>
       </c>
       <c r="B114" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12987,14 +12987,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Lill-Sännan N, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>609298</v>
+        <v>609241</v>
       </c>
       <c r="R114" t="n">
-        <v>7062892</v>
+        <v>7062789</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13057,10 +13057,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>122742575</v>
+        <v>122742576</v>
       </c>
       <c r="B115" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>609261</v>
+        <v>609298</v>
       </c>
       <c r="R115" t="n">
         <v>7062892</v>
@@ -13163,10 +13163,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>122746839</v>
+        <v>122742575</v>
       </c>
       <c r="B116" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13199,14 +13199,14 @@
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Lill-Sännan N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>609241</v>
+        <v>609261</v>
       </c>
       <c r="R116" t="n">
-        <v>7062789</v>
+        <v>7062892</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -12845,10 +12845,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122742574</v>
+        <v>122746839</v>
       </c>
       <c r="B113" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12881,14 +12881,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Sanddals- SV, Ång</t>
+          <t>Lill-Sännan N, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>609226</v>
+        <v>609241</v>
       </c>
       <c r="R113" t="n">
-        <v>7062868</v>
+        <v>7062789</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12940,7 +12940,7 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Helene Andersson, Kristofer Wester</t>
+          <t>Kristofer Wester, Helene Andersson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
@@ -12951,10 +12951,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122746839</v>
+        <v>122742574</v>
       </c>
       <c r="B114" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12987,14 +12987,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lill-Sännan N, Ång</t>
+          <t>Sanddals- SV, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>609241</v>
+        <v>609226</v>
       </c>
       <c r="R114" t="n">
-        <v>7062789</v>
+        <v>7062868</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13060,7 +13060,7 @@
         <v>122742576</v>
       </c>
       <c r="B115" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>122742575</v>
       </c>
       <c r="B116" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AY140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13267,6 +13267,2480 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>125271462</v>
+      </c>
+      <c r="B117" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>609053</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7062842</v>
+      </c>
+      <c r="S117" t="n">
+        <v>15</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>125271489</v>
+      </c>
+      <c r="B118" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>609056</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7062848</v>
+      </c>
+      <c r="S118" t="n">
+        <v>15</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>125269977</v>
+      </c>
+      <c r="B119" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>609090</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7063013</v>
+      </c>
+      <c r="S119" t="n">
+        <v>15</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>125270136</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79927</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>609102</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7062917</v>
+      </c>
+      <c r="S120" t="n">
+        <v>15</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>125269804</v>
+      </c>
+      <c r="B121" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>609090</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7063026</v>
+      </c>
+      <c r="S121" t="n">
+        <v>15</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>125269907</v>
+      </c>
+      <c r="B122" t="n">
+        <v>91361</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>609091</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7063024</v>
+      </c>
+      <c r="S122" t="n">
+        <v>15</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>125271565</v>
+      </c>
+      <c r="B123" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>609059</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7062880</v>
+      </c>
+      <c r="S123" t="n">
+        <v>15</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>125270406</v>
+      </c>
+      <c r="B124" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>609114</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7062709</v>
+      </c>
+      <c r="S124" t="n">
+        <v>15</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>125270531</v>
+      </c>
+      <c r="B125" t="n">
+        <v>91673</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>898</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Blackticka</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Steccherinum collabens</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>609079</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7062685</v>
+      </c>
+      <c r="S125" t="n">
+        <v>15</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125269871</v>
+      </c>
+      <c r="B126" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>609090</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7063026</v>
+      </c>
+      <c r="S126" t="n">
+        <v>15</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>125270505</v>
+      </c>
+      <c r="B127" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>609082</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7062688</v>
+      </c>
+      <c r="S127" t="n">
+        <v>15</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>125273101</v>
+      </c>
+      <c r="B128" t="n">
+        <v>96985</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>609053</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7063023</v>
+      </c>
+      <c r="S128" t="n">
+        <v>15</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>125271349</v>
+      </c>
+      <c r="B129" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>609012</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7062832</v>
+      </c>
+      <c r="S129" t="n">
+        <v>15</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>125271814</v>
+      </c>
+      <c r="B130" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>609083</v>
+      </c>
+      <c r="R130" t="n">
+        <v>7062960</v>
+      </c>
+      <c r="S130" t="n">
+        <v>15</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>125269793</v>
+      </c>
+      <c r="B131" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>609090</v>
+      </c>
+      <c r="R131" t="n">
+        <v>7063026</v>
+      </c>
+      <c r="S131" t="n">
+        <v>15</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>125269981</v>
+      </c>
+      <c r="B132" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>609081</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7063021</v>
+      </c>
+      <c r="S132" t="n">
+        <v>15</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>125271430</v>
+      </c>
+      <c r="B133" t="n">
+        <v>91012</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>609049</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7062834</v>
+      </c>
+      <c r="S133" t="n">
+        <v>15</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>125271754</v>
+      </c>
+      <c r="B134" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>609075</v>
+      </c>
+      <c r="R134" t="n">
+        <v>7062923</v>
+      </c>
+      <c r="S134" t="n">
+        <v>15</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>125271717</v>
+      </c>
+      <c r="B135" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>609076</v>
+      </c>
+      <c r="R135" t="n">
+        <v>7062922</v>
+      </c>
+      <c r="S135" t="n">
+        <v>15</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>125271702</v>
+      </c>
+      <c r="B136" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>609074</v>
+      </c>
+      <c r="R136" t="n">
+        <v>7062921</v>
+      </c>
+      <c r="S136" t="n">
+        <v>15</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>125271636</v>
+      </c>
+      <c r="B137" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>609058</v>
+      </c>
+      <c r="R137" t="n">
+        <v>7062880</v>
+      </c>
+      <c r="S137" t="n">
+        <v>15</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>125271733</v>
+      </c>
+      <c r="B138" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>609075</v>
+      </c>
+      <c r="R138" t="n">
+        <v>7062923</v>
+      </c>
+      <c r="S138" t="n">
+        <v>15</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>125270100</v>
+      </c>
+      <c r="B139" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>609102</v>
+      </c>
+      <c r="R139" t="n">
+        <v>7062918</v>
+      </c>
+      <c r="S139" t="n">
+        <v>15</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>125271533</v>
+      </c>
+      <c r="B140" t="n">
+        <v>90977</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>609058</v>
+      </c>
+      <c r="R140" t="n">
+        <v>7062860</v>
+      </c>
+      <c r="S140" t="n">
+        <v>15</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY140"/>
+  <dimension ref="A1:AY142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13269,10 +13269,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125271462</v>
+        <v>125270505</v>
       </c>
       <c r="B117" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13281,42 +13281,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>609053</v>
+        <v>609082</v>
       </c>
       <c r="R117" t="n">
-        <v>7062842</v>
+        <v>7062688</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13375,10 +13371,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125271489</v>
+        <v>125271717</v>
       </c>
       <c r="B118" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13387,38 +13383,42 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>609056</v>
+        <v>609076</v>
       </c>
       <c r="R118" t="n">
-        <v>7062848</v>
+        <v>7062922</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13477,10 +13477,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125269977</v>
+        <v>125269804</v>
       </c>
       <c r="B119" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13489,25 +13489,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13520,7 +13520,7 @@
         <v>609090</v>
       </c>
       <c r="R119" t="n">
-        <v>7063013</v>
+        <v>7063026</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13579,10 +13579,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125270136</v>
+        <v>125270531</v>
       </c>
       <c r="B120" t="n">
-        <v>79927</v>
+        <v>91673</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13591,25 +13591,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6464</v>
+        <v>898</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13619,10 +13619,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>609102</v>
+        <v>609079</v>
       </c>
       <c r="R120" t="n">
-        <v>7062917</v>
+        <v>7062685</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13681,10 +13681,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125269804</v>
+        <v>125271533</v>
       </c>
       <c r="B121" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13693,25 +13693,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13721,10 +13721,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>609090</v>
+        <v>609058</v>
       </c>
       <c r="R121" t="n">
-        <v>7063026</v>
+        <v>7062860</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13783,10 +13783,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125269907</v>
+        <v>125271430</v>
       </c>
       <c r="B122" t="n">
-        <v>91361</v>
+        <v>91012</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13795,25 +13795,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13823,10 +13823,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>609091</v>
+        <v>609049</v>
       </c>
       <c r="R122" t="n">
-        <v>7063024</v>
+        <v>7062834</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13885,10 +13885,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125271565</v>
+        <v>125270406</v>
       </c>
       <c r="B123" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13897,25 +13897,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13925,10 +13925,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>609059</v>
+        <v>609114</v>
       </c>
       <c r="R123" t="n">
-        <v>7062880</v>
+        <v>7062709</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13987,10 +13987,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125270406</v>
+        <v>125271754</v>
       </c>
       <c r="B124" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13999,38 +13999,42 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>609114</v>
+        <v>609075</v>
       </c>
       <c r="R124" t="n">
-        <v>7062709</v>
+        <v>7062923</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -14089,10 +14093,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125270531</v>
+        <v>125271733</v>
       </c>
       <c r="B125" t="n">
-        <v>91673</v>
+        <v>79920</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14101,25 +14105,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>898</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14129,10 +14133,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>609079</v>
+        <v>609075</v>
       </c>
       <c r="R125" t="n">
-        <v>7062685</v>
+        <v>7062923</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -14191,10 +14195,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125269871</v>
+        <v>125271489</v>
       </c>
       <c r="B126" t="n">
-        <v>91012</v>
+        <v>90977</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14203,25 +14207,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14231,10 +14235,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>609090</v>
+        <v>609056</v>
       </c>
       <c r="R126" t="n">
-        <v>7063026</v>
+        <v>7062848</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14293,10 +14297,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125270505</v>
+        <v>125271814</v>
       </c>
       <c r="B127" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14309,21 +14313,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14333,10 +14337,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>609082</v>
+        <v>609083</v>
       </c>
       <c r="R127" t="n">
-        <v>7062688</v>
+        <v>7062960</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -14497,10 +14501,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125271349</v>
+        <v>125271565</v>
       </c>
       <c r="B129" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14509,43 +14513,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>609012</v>
+        <v>609059</v>
       </c>
       <c r="R129" t="n">
-        <v>7062832</v>
+        <v>7062880</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -14578,11 +14577,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14609,10 +14603,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125271814</v>
+        <v>125270136</v>
       </c>
       <c r="B130" t="n">
-        <v>78810</v>
+        <v>79927</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14621,25 +14615,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14649,10 +14643,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>609083</v>
+        <v>609102</v>
       </c>
       <c r="R130" t="n">
-        <v>7062960</v>
+        <v>7062917</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14813,10 +14807,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125269981</v>
+        <v>125271349</v>
       </c>
       <c r="B132" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14829,34 +14823,39 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>609081</v>
+        <v>609012</v>
       </c>
       <c r="R132" t="n">
-        <v>7063021</v>
+        <v>7062832</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14889,6 +14888,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14915,10 +14919,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125271430</v>
+        <v>125271702</v>
       </c>
       <c r="B133" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14927,38 +14931,42 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>609049</v>
+        <v>609074</v>
       </c>
       <c r="R133" t="n">
-        <v>7062834</v>
+        <v>7062921</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15017,7 +15025,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125271754</v>
+        <v>125271462</v>
       </c>
       <c r="B134" t="n">
         <v>98101</v>
@@ -15061,10 +15069,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>609075</v>
+        <v>609053</v>
       </c>
       <c r="R134" t="n">
-        <v>7062923</v>
+        <v>7062842</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15123,10 +15131,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125271717</v>
+        <v>125270100</v>
       </c>
       <c r="B135" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15135,42 +15143,38 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>609076</v>
+        <v>609102</v>
       </c>
       <c r="R135" t="n">
-        <v>7062922</v>
+        <v>7062918</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15229,10 +15233,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125271702</v>
+        <v>125271636</v>
       </c>
       <c r="B136" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15241,42 +15245,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>609074</v>
+        <v>609058</v>
       </c>
       <c r="R136" t="n">
-        <v>7062921</v>
+        <v>7062880</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15335,10 +15335,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125271636</v>
+        <v>125269981</v>
       </c>
       <c r="B137" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15351,21 +15351,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>609058</v>
+        <v>609081</v>
       </c>
       <c r="R137" t="n">
-        <v>7062880</v>
+        <v>7063021</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15437,10 +15437,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125271733</v>
+        <v>125269871</v>
       </c>
       <c r="B138" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15449,25 +15449,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15477,10 +15477,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>609075</v>
+        <v>609090</v>
       </c>
       <c r="R138" t="n">
-        <v>7062923</v>
+        <v>7063026</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15539,10 +15539,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125270100</v>
+        <v>125269977</v>
       </c>
       <c r="B139" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15551,25 +15551,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15579,10 +15579,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>609102</v>
+        <v>609090</v>
       </c>
       <c r="R139" t="n">
-        <v>7062918</v>
+        <v>7063013</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15641,10 +15641,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125271533</v>
+        <v>125307928</v>
       </c>
       <c r="B140" t="n">
-        <v>90977</v>
+        <v>79920</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15657,37 +15657,40 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Skalberget, Skalberget, Ång</t>
+          <t>Kläppsjöhällan, Ång</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>609058</v>
+        <v>609121</v>
       </c>
       <c r="R140" t="n">
-        <v>7062860</v>
+        <v>7062933</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15725,6 +15728,7 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15740,6 +15744,227 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>125307925</v>
+      </c>
+      <c r="B141" t="n">
+        <v>57513</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Kläppsjöhällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>609034</v>
+      </c>
+      <c r="R141" t="n">
+        <v>7062660</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>125307927</v>
+      </c>
+      <c r="B142" t="n">
+        <v>79891</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Kläppsjöhällan, Ång</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>609121</v>
+      </c>
+      <c r="R142" t="n">
+        <v>7062933</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY142"/>
+  <dimension ref="A1:AY143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13269,10 +13269,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125270505</v>
+        <v>125271754</v>
       </c>
       <c r="B117" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13281,38 +13281,42 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>609082</v>
+        <v>609075</v>
       </c>
       <c r="R117" t="n">
-        <v>7062688</v>
+        <v>7062923</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13371,10 +13375,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125271717</v>
+        <v>125269977</v>
       </c>
       <c r="B118" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13383,42 +13387,38 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>609076</v>
+        <v>609090</v>
       </c>
       <c r="R118" t="n">
-        <v>7062922</v>
+        <v>7063013</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13477,10 +13477,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125269804</v>
+        <v>125269981</v>
       </c>
       <c r="B119" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13493,21 +13493,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13517,10 +13517,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>609090</v>
+        <v>609081</v>
       </c>
       <c r="R119" t="n">
-        <v>7063026</v>
+        <v>7063021</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13579,10 +13579,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125270531</v>
+        <v>125269871</v>
       </c>
       <c r="B120" t="n">
-        <v>91673</v>
+        <v>91012</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13591,25 +13591,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13619,10 +13619,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>609079</v>
+        <v>609090</v>
       </c>
       <c r="R120" t="n">
-        <v>7062685</v>
+        <v>7063026</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13681,10 +13681,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125271533</v>
+        <v>125271349</v>
       </c>
       <c r="B121" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13693,38 +13693,43 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>609058</v>
+        <v>609012</v>
       </c>
       <c r="R121" t="n">
-        <v>7062860</v>
+        <v>7062832</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13757,6 +13762,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13783,10 +13793,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125271430</v>
+        <v>125270100</v>
       </c>
       <c r="B122" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13799,21 +13809,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13823,10 +13833,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>609049</v>
+        <v>609102</v>
       </c>
       <c r="R122" t="n">
-        <v>7062834</v>
+        <v>7062918</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13885,7 +13895,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125270406</v>
+        <v>125269793</v>
       </c>
       <c r="B123" t="n">
         <v>79891</v>
@@ -13925,10 +13935,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>609114</v>
+        <v>609090</v>
       </c>
       <c r="R123" t="n">
-        <v>7062709</v>
+        <v>7063026</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13987,10 +13997,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125271754</v>
+        <v>125270531</v>
       </c>
       <c r="B124" t="n">
-        <v>98101</v>
+        <v>91673</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14003,38 +14013,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>609075</v>
+        <v>609079</v>
       </c>
       <c r="R124" t="n">
-        <v>7062923</v>
+        <v>7062685</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -14093,10 +14099,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125271733</v>
+        <v>125271636</v>
       </c>
       <c r="B125" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14105,25 +14111,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14133,10 +14139,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>609075</v>
+        <v>609058</v>
       </c>
       <c r="R125" t="n">
-        <v>7062923</v>
+        <v>7062880</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -14195,10 +14201,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125271489</v>
+        <v>125271430</v>
       </c>
       <c r="B126" t="n">
-        <v>90977</v>
+        <v>91012</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14207,25 +14213,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14235,10 +14241,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>609056</v>
+        <v>609049</v>
       </c>
       <c r="R126" t="n">
-        <v>7062848</v>
+        <v>7062834</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14399,10 +14405,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125273101</v>
+        <v>125271489</v>
       </c>
       <c r="B128" t="n">
-        <v>96985</v>
+        <v>90977</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14415,21 +14421,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14439,10 +14445,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>609053</v>
+        <v>609056</v>
       </c>
       <c r="R128" t="n">
-        <v>7063023</v>
+        <v>7062848</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -14603,10 +14609,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125270136</v>
+        <v>125271533</v>
       </c>
       <c r="B130" t="n">
-        <v>79927</v>
+        <v>90977</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14619,21 +14625,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14643,10 +14649,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>609102</v>
+        <v>609058</v>
       </c>
       <c r="R130" t="n">
-        <v>7062917</v>
+        <v>7062860</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14705,10 +14711,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125269793</v>
+        <v>125270505</v>
       </c>
       <c r="B131" t="n">
-        <v>79891</v>
+        <v>91012</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14721,21 +14727,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14745,10 +14751,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>609090</v>
+        <v>609082</v>
       </c>
       <c r="R131" t="n">
-        <v>7063026</v>
+        <v>7062688</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14807,10 +14813,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125271349</v>
+        <v>125270136</v>
       </c>
       <c r="B132" t="n">
-        <v>57513</v>
+        <v>79927</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14819,43 +14825,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>609012</v>
+        <v>609102</v>
       </c>
       <c r="R132" t="n">
-        <v>7062832</v>
+        <v>7062917</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14888,11 +14889,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14919,10 +14915,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125271702</v>
+        <v>125269804</v>
       </c>
       <c r="B133" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14931,42 +14927,38 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>609074</v>
+        <v>609090</v>
       </c>
       <c r="R133" t="n">
-        <v>7062921</v>
+        <v>7063026</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15025,10 +15017,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125271462</v>
+        <v>125271733</v>
       </c>
       <c r="B134" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15037,42 +15029,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>609053</v>
+        <v>609075</v>
       </c>
       <c r="R134" t="n">
-        <v>7062842</v>
+        <v>7062923</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15131,10 +15119,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125270100</v>
+        <v>125271702</v>
       </c>
       <c r="B135" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15143,38 +15131,42 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>609102</v>
+        <v>609074</v>
       </c>
       <c r="R135" t="n">
-        <v>7062918</v>
+        <v>7062921</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15233,10 +15225,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125271636</v>
+        <v>125270406</v>
       </c>
       <c r="B136" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15249,21 +15241,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15273,10 +15265,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>609058</v>
+        <v>609114</v>
       </c>
       <c r="R136" t="n">
-        <v>7062880</v>
+        <v>7062709</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15335,10 +15327,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125269981</v>
+        <v>125271717</v>
       </c>
       <c r="B137" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15347,38 +15339,42 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>609081</v>
+        <v>609076</v>
       </c>
       <c r="R137" t="n">
-        <v>7063021</v>
+        <v>7062922</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15437,10 +15433,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125269871</v>
+        <v>125271462</v>
       </c>
       <c r="B138" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15449,38 +15445,42 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>609090</v>
+        <v>609053</v>
       </c>
       <c r="R138" t="n">
-        <v>7063026</v>
+        <v>7062842</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15539,10 +15539,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125269977</v>
+        <v>125273101</v>
       </c>
       <c r="B139" t="n">
-        <v>79920</v>
+        <v>96985</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15555,21 +15555,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15579,10 +15579,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>609090</v>
+        <v>609053</v>
       </c>
       <c r="R139" t="n">
-        <v>7063013</v>
+        <v>7063023</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15966,6 +15966,108 @@
       </c>
       <c r="AY142" t="inlineStr"/>
     </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>125269907</v>
+      </c>
+      <c r="B143" t="n">
+        <v>91361</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>609091</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7063024</v>
+      </c>
+      <c r="S143" t="n">
+        <v>15</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -13269,10 +13269,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125271754</v>
+        <v>125270531</v>
       </c>
       <c r="B117" t="n">
-        <v>98101</v>
+        <v>91673</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13285,38 +13285,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>609075</v>
+        <v>609079</v>
       </c>
       <c r="R117" t="n">
-        <v>7062923</v>
+        <v>7062685</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13375,10 +13371,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125269977</v>
+        <v>125269804</v>
       </c>
       <c r="B118" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13387,25 +13383,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13418,7 +13414,7 @@
         <v>609090</v>
       </c>
       <c r="R118" t="n">
-        <v>7063013</v>
+        <v>7063026</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13477,10 +13473,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125269981</v>
+        <v>125270136</v>
       </c>
       <c r="B119" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13489,25 +13485,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13517,10 +13513,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>609081</v>
+        <v>609102</v>
       </c>
       <c r="R119" t="n">
-        <v>7063021</v>
+        <v>7062917</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13579,10 +13575,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125269871</v>
+        <v>125271462</v>
       </c>
       <c r="B120" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13591,38 +13587,42 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>609090</v>
+        <v>609053</v>
       </c>
       <c r="R120" t="n">
-        <v>7063026</v>
+        <v>7062842</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13681,10 +13681,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125271349</v>
+        <v>125269793</v>
       </c>
       <c r="B121" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13697,39 +13697,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>609012</v>
+        <v>609090</v>
       </c>
       <c r="R121" t="n">
-        <v>7062832</v>
+        <v>7063026</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13762,11 +13757,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13793,10 +13783,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125270100</v>
+        <v>125271636</v>
       </c>
       <c r="B122" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13809,21 +13799,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13833,10 +13823,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>609102</v>
+        <v>609058</v>
       </c>
       <c r="R122" t="n">
-        <v>7062918</v>
+        <v>7062880</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13895,10 +13885,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125269793</v>
+        <v>125271489</v>
       </c>
       <c r="B123" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13907,25 +13897,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13935,10 +13925,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>609090</v>
+        <v>609056</v>
       </c>
       <c r="R123" t="n">
-        <v>7063026</v>
+        <v>7062848</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13997,10 +13987,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125270531</v>
+        <v>125269871</v>
       </c>
       <c r="B124" t="n">
-        <v>91673</v>
+        <v>91012</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14009,25 +13999,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14037,10 +14027,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>609079</v>
+        <v>609090</v>
       </c>
       <c r="R124" t="n">
-        <v>7062685</v>
+        <v>7063026</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -14099,10 +14089,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125271636</v>
+        <v>125269977</v>
       </c>
       <c r="B125" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14111,25 +14101,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14139,10 +14129,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>609058</v>
+        <v>609090</v>
       </c>
       <c r="R125" t="n">
-        <v>7062880</v>
+        <v>7063013</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -14201,10 +14191,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125271430</v>
+        <v>125271733</v>
       </c>
       <c r="B126" t="n">
-        <v>91012</v>
+        <v>79920</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14213,25 +14203,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14241,10 +14231,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>609049</v>
+        <v>609075</v>
       </c>
       <c r="R126" t="n">
-        <v>7062834</v>
+        <v>7062923</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14303,10 +14293,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125271814</v>
+        <v>125271533</v>
       </c>
       <c r="B127" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14315,25 +14305,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14343,10 +14333,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>609083</v>
+        <v>609058</v>
       </c>
       <c r="R127" t="n">
-        <v>7062960</v>
+        <v>7062860</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -14405,10 +14395,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125271489</v>
+        <v>125271754</v>
       </c>
       <c r="B128" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14417,38 +14407,42 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>609056</v>
+        <v>609075</v>
       </c>
       <c r="R128" t="n">
-        <v>7062848</v>
+        <v>7062923</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -14507,10 +14501,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125271565</v>
+        <v>125271430</v>
       </c>
       <c r="B129" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14519,25 +14513,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14547,10 +14541,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>609059</v>
+        <v>609049</v>
       </c>
       <c r="R129" t="n">
-        <v>7062880</v>
+        <v>7062834</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -14609,10 +14603,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125271533</v>
+        <v>125269981</v>
       </c>
       <c r="B130" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14621,25 +14615,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14649,10 +14643,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>609058</v>
+        <v>609081</v>
       </c>
       <c r="R130" t="n">
-        <v>7062860</v>
+        <v>7063021</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14711,10 +14705,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125270505</v>
+        <v>125271717</v>
       </c>
       <c r="B131" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14723,38 +14717,42 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>609082</v>
+        <v>609076</v>
       </c>
       <c r="R131" t="n">
-        <v>7062688</v>
+        <v>7062922</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14813,10 +14811,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125270136</v>
+        <v>125270406</v>
       </c>
       <c r="B132" t="n">
-        <v>79927</v>
+        <v>79891</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14825,25 +14823,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14853,10 +14851,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>609102</v>
+        <v>609114</v>
       </c>
       <c r="R132" t="n">
-        <v>7062917</v>
+        <v>7062709</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14915,7 +14913,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125269804</v>
+        <v>125271814</v>
       </c>
       <c r="B133" t="n">
         <v>78810</v>
@@ -14955,10 +14953,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>609090</v>
+        <v>609083</v>
       </c>
       <c r="R133" t="n">
-        <v>7063026</v>
+        <v>7062960</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15017,10 +15015,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125271733</v>
+        <v>125270100</v>
       </c>
       <c r="B134" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15029,25 +15027,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15057,10 +15055,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>609075</v>
+        <v>609102</v>
       </c>
       <c r="R134" t="n">
-        <v>7062923</v>
+        <v>7062918</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15225,10 +15223,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125270406</v>
+        <v>125271349</v>
       </c>
       <c r="B136" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15241,34 +15239,39 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>609114</v>
+        <v>609012</v>
       </c>
       <c r="R136" t="n">
-        <v>7062709</v>
+        <v>7062832</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15301,6 +15304,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15327,10 +15335,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125271717</v>
+        <v>125271565</v>
       </c>
       <c r="B137" t="n">
-        <v>98101</v>
+        <v>79920</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15339,42 +15347,38 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>609076</v>
+        <v>609059</v>
       </c>
       <c r="R137" t="n">
-        <v>7062922</v>
+        <v>7062880</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15433,10 +15437,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125271462</v>
+        <v>125273101</v>
       </c>
       <c r="B138" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15445,32 +15449,28 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
@@ -15480,7 +15480,7 @@
         <v>609053</v>
       </c>
       <c r="R138" t="n">
-        <v>7062842</v>
+        <v>7063023</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15539,10 +15539,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125273101</v>
+        <v>125270505</v>
       </c>
       <c r="B139" t="n">
-        <v>96985</v>
+        <v>91012</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15551,25 +15551,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>221941</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15579,10 +15579,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>609053</v>
+        <v>609082</v>
       </c>
       <c r="R139" t="n">
-        <v>7063023</v>
+        <v>7062688</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15747,10 +15747,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125307925</v>
+        <v>125307927</v>
       </c>
       <c r="B141" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15763,31 +15763,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15795,10 +15790,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>609034</v>
+        <v>609121</v>
       </c>
       <c r="R141" t="n">
-        <v>7062660</v>
+        <v>7062933</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15833,17 +15828,13 @@
           <t>2025-05-20</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15862,10 +15853,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125307927</v>
+        <v>125307925</v>
       </c>
       <c r="B142" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15878,26 +15869,31 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -15905,10 +15901,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>609121</v>
+        <v>609034</v>
       </c>
       <c r="R142" t="n">
-        <v>7062933</v>
+        <v>7062660</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15943,13 +15939,17 @@
           <t>2025-05-20</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -15117,10 +15117,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125271702</v>
+        <v>125271349</v>
       </c>
       <c r="B135" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15129,30 +15129,31 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -15161,10 +15162,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>609074</v>
+        <v>609012</v>
       </c>
       <c r="R135" t="n">
-        <v>7062921</v>
+        <v>7062832</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15197,6 +15198,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15223,10 +15229,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125271349</v>
+        <v>125271565</v>
       </c>
       <c r="B136" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15235,43 +15241,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>609012</v>
+        <v>609059</v>
       </c>
       <c r="R136" t="n">
-        <v>7062832</v>
+        <v>7062880</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15304,11 +15305,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15335,10 +15331,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125271565</v>
+        <v>125271702</v>
       </c>
       <c r="B137" t="n">
-        <v>79920</v>
+        <v>98101</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15347,38 +15343,42 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>609059</v>
+        <v>609074</v>
       </c>
       <c r="R137" t="n">
-        <v>7062880</v>
+        <v>7062921</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -13269,10 +13269,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125270531</v>
+        <v>125269871</v>
       </c>
       <c r="B117" t="n">
-        <v>91673</v>
+        <v>91012</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13281,25 +13281,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>609079</v>
+        <v>609090</v>
       </c>
       <c r="R117" t="n">
-        <v>7062685</v>
+        <v>7063026</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13371,10 +13371,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125269804</v>
+        <v>125270100</v>
       </c>
       <c r="B118" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13387,21 +13387,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>609090</v>
+        <v>609102</v>
       </c>
       <c r="R118" t="n">
-        <v>7063026</v>
+        <v>7062918</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13473,10 +13473,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125270136</v>
+        <v>125271565</v>
       </c>
       <c r="B119" t="n">
-        <v>79927</v>
+        <v>79920</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13489,21 +13489,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13513,10 +13513,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>609102</v>
+        <v>609059</v>
       </c>
       <c r="R119" t="n">
-        <v>7062917</v>
+        <v>7062880</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13575,7 +13575,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125271462</v>
+        <v>125271754</v>
       </c>
       <c r="B120" t="n">
         <v>98101</v>
@@ -13619,10 +13619,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>609053</v>
+        <v>609075</v>
       </c>
       <c r="R120" t="n">
-        <v>7062842</v>
+        <v>7062923</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13681,10 +13681,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125269793</v>
+        <v>125269977</v>
       </c>
       <c r="B121" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13693,25 +13693,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13724,7 +13724,7 @@
         <v>609090</v>
       </c>
       <c r="R121" t="n">
-        <v>7063026</v>
+        <v>7063013</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13783,10 +13783,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125271636</v>
+        <v>125270505</v>
       </c>
       <c r="B122" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13799,21 +13799,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13823,10 +13823,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>609058</v>
+        <v>609082</v>
       </c>
       <c r="R122" t="n">
-        <v>7062880</v>
+        <v>7062688</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13885,10 +13885,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125271489</v>
+        <v>125270531</v>
       </c>
       <c r="B123" t="n">
-        <v>90977</v>
+        <v>91673</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13897,25 +13897,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5447</v>
+        <v>898</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13925,10 +13925,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>609056</v>
+        <v>609079</v>
       </c>
       <c r="R123" t="n">
-        <v>7062848</v>
+        <v>7062685</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13987,7 +13987,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125269871</v>
+        <v>125271430</v>
       </c>
       <c r="B124" t="n">
         <v>91012</v>
@@ -14027,10 +14027,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>609090</v>
+        <v>609049</v>
       </c>
       <c r="R124" t="n">
-        <v>7063026</v>
+        <v>7062834</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -14089,10 +14089,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125269977</v>
+        <v>125271489</v>
       </c>
       <c r="B125" t="n">
-        <v>79920</v>
+        <v>90977</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14105,21 +14105,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14129,10 +14129,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>609090</v>
+        <v>609056</v>
       </c>
       <c r="R125" t="n">
-        <v>7063013</v>
+        <v>7062848</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -14191,10 +14191,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125271733</v>
+        <v>125270406</v>
       </c>
       <c r="B126" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14203,25 +14203,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14231,10 +14231,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>609075</v>
+        <v>609114</v>
       </c>
       <c r="R126" t="n">
-        <v>7062923</v>
+        <v>7062709</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14293,10 +14293,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125271533</v>
+        <v>125271717</v>
       </c>
       <c r="B127" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14305,38 +14305,42 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>609058</v>
+        <v>609076</v>
       </c>
       <c r="R127" t="n">
-        <v>7062860</v>
+        <v>7062922</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -14395,7 +14399,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125271754</v>
+        <v>125271462</v>
       </c>
       <c r="B128" t="n">
         <v>98101</v>
@@ -14439,10 +14443,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>609075</v>
+        <v>609053</v>
       </c>
       <c r="R128" t="n">
-        <v>7062923</v>
+        <v>7062842</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -14501,10 +14505,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125271430</v>
+        <v>125271349</v>
       </c>
       <c r="B129" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14517,34 +14521,39 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>609049</v>
+        <v>609012</v>
       </c>
       <c r="R129" t="n">
-        <v>7062834</v>
+        <v>7062832</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -14577,6 +14586,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14603,10 +14617,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125269981</v>
+        <v>125271814</v>
       </c>
       <c r="B130" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14619,21 +14633,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14643,10 +14657,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>609081</v>
+        <v>609083</v>
       </c>
       <c r="R130" t="n">
-        <v>7063021</v>
+        <v>7062960</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14705,10 +14719,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125271717</v>
+        <v>125271533</v>
       </c>
       <c r="B131" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14717,42 +14731,38 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>609076</v>
+        <v>609058</v>
       </c>
       <c r="R131" t="n">
-        <v>7062922</v>
+        <v>7062860</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14811,10 +14821,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125270406</v>
+        <v>125270136</v>
       </c>
       <c r="B132" t="n">
-        <v>79891</v>
+        <v>79927</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14823,25 +14833,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14851,10 +14861,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>609114</v>
+        <v>609102</v>
       </c>
       <c r="R132" t="n">
-        <v>7062709</v>
+        <v>7062917</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14913,10 +14923,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125271814</v>
+        <v>125273101</v>
       </c>
       <c r="B133" t="n">
-        <v>78810</v>
+        <v>96985</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14925,25 +14935,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14953,10 +14963,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>609083</v>
+        <v>609053</v>
       </c>
       <c r="R133" t="n">
-        <v>7062960</v>
+        <v>7063023</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15015,10 +15025,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125270100</v>
+        <v>125271636</v>
       </c>
       <c r="B134" t="n">
-        <v>79891</v>
+        <v>78810</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15031,21 +15041,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15055,10 +15065,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>609102</v>
+        <v>609058</v>
       </c>
       <c r="R134" t="n">
-        <v>7062918</v>
+        <v>7062880</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15117,10 +15127,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125271349</v>
+        <v>125269804</v>
       </c>
       <c r="B135" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15133,39 +15143,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>609012</v>
+        <v>609090</v>
       </c>
       <c r="R135" t="n">
-        <v>7062832</v>
+        <v>7063026</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15198,11 +15203,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15229,10 +15229,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125271565</v>
+        <v>125269981</v>
       </c>
       <c r="B136" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15241,25 +15241,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15269,10 +15269,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>609059</v>
+        <v>609081</v>
       </c>
       <c r="R136" t="n">
-        <v>7062880</v>
+        <v>7063021</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15437,10 +15437,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125273101</v>
+        <v>125271733</v>
       </c>
       <c r="B138" t="n">
-        <v>96985</v>
+        <v>79920</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15453,21 +15453,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15477,10 +15477,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>609053</v>
+        <v>609075</v>
       </c>
       <c r="R138" t="n">
-        <v>7063023</v>
+        <v>7062923</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15539,10 +15539,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125270505</v>
+        <v>125269793</v>
       </c>
       <c r="B139" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15555,21 +15555,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15579,10 +15579,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>609082</v>
+        <v>609090</v>
       </c>
       <c r="R139" t="n">
-        <v>7062688</v>
+        <v>7063026</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15641,10 +15641,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125307928</v>
+        <v>125307927</v>
       </c>
       <c r="B140" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15653,25 +15653,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15747,10 +15747,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125307927</v>
+        <v>125307928</v>
       </c>
       <c r="B141" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15759,25 +15759,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -13269,10 +13269,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125269871</v>
+        <v>125270100</v>
       </c>
       <c r="B117" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13285,21 +13285,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>609090</v>
+        <v>609102</v>
       </c>
       <c r="R117" t="n">
-        <v>7063026</v>
+        <v>7062918</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13371,10 +13371,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125270100</v>
+        <v>125271565</v>
       </c>
       <c r="B118" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13383,25 +13383,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>609102</v>
+        <v>609059</v>
       </c>
       <c r="R118" t="n">
-        <v>7062918</v>
+        <v>7062880</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13473,10 +13473,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125271565</v>
+        <v>125269871</v>
       </c>
       <c r="B119" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13485,25 +13485,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13513,10 +13513,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>609059</v>
+        <v>609090</v>
       </c>
       <c r="R119" t="n">
-        <v>7062880</v>
+        <v>7063026</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -14191,10 +14191,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125270406</v>
+        <v>125271717</v>
       </c>
       <c r="B126" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14203,38 +14203,42 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>609114</v>
+        <v>609076</v>
       </c>
       <c r="R126" t="n">
-        <v>7062709</v>
+        <v>7062922</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14293,7 +14297,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125271717</v>
+        <v>125271462</v>
       </c>
       <c r="B127" t="n">
         <v>98101</v>
@@ -14328,7 +14332,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -14337,10 +14341,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>609076</v>
+        <v>609053</v>
       </c>
       <c r="R127" t="n">
-        <v>7062922</v>
+        <v>7062842</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -14399,10 +14403,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125271462</v>
+        <v>125270406</v>
       </c>
       <c r="B128" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14411,42 +14415,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>609053</v>
+        <v>609114</v>
       </c>
       <c r="R128" t="n">
-        <v>7062842</v>
+        <v>7062709</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -13269,10 +13269,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125270100</v>
+        <v>125269977</v>
       </c>
       <c r="B117" t="n">
-        <v>79891</v>
+        <v>79920</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13281,25 +13281,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>609102</v>
+        <v>609090</v>
       </c>
       <c r="R117" t="n">
-        <v>7062918</v>
+        <v>7063013</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13371,10 +13371,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125271565</v>
+        <v>125269871</v>
       </c>
       <c r="B118" t="n">
-        <v>79920</v>
+        <v>91012</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13383,25 +13383,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>609059</v>
+        <v>609090</v>
       </c>
       <c r="R118" t="n">
-        <v>7062880</v>
+        <v>7063026</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13473,10 +13473,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125269871</v>
+        <v>125271636</v>
       </c>
       <c r="B119" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13489,21 +13489,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13513,10 +13513,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>609090</v>
+        <v>609058</v>
       </c>
       <c r="R119" t="n">
-        <v>7063026</v>
+        <v>7062880</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13575,10 +13575,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125271754</v>
+        <v>125273101</v>
       </c>
       <c r="B120" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13587,42 +13587,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>609075</v>
+        <v>609053</v>
       </c>
       <c r="R120" t="n">
-        <v>7062923</v>
+        <v>7063023</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13681,10 +13677,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125269977</v>
+        <v>125269981</v>
       </c>
       <c r="B121" t="n">
-        <v>79920</v>
+        <v>79891</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13693,25 +13689,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13721,10 +13717,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>609090</v>
+        <v>609081</v>
       </c>
       <c r="R121" t="n">
-        <v>7063013</v>
+        <v>7063021</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13783,10 +13779,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125270505</v>
+        <v>125270531</v>
       </c>
       <c r="B122" t="n">
-        <v>91012</v>
+        <v>91673</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13795,25 +13791,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13823,10 +13819,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>609082</v>
+        <v>609079</v>
       </c>
       <c r="R122" t="n">
-        <v>7062688</v>
+        <v>7062685</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13885,10 +13881,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125270531</v>
+        <v>125271814</v>
       </c>
       <c r="B123" t="n">
-        <v>91673</v>
+        <v>78810</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13897,25 +13893,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13925,10 +13921,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>609079</v>
+        <v>609083</v>
       </c>
       <c r="R123" t="n">
-        <v>7062685</v>
+        <v>7062960</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13987,10 +13983,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125271430</v>
+        <v>125271717</v>
       </c>
       <c r="B124" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13999,38 +13995,42 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>609049</v>
+        <v>609076</v>
       </c>
       <c r="R124" t="n">
-        <v>7062834</v>
+        <v>7062922</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -14089,10 +14089,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125271489</v>
+        <v>125271462</v>
       </c>
       <c r="B125" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14101,38 +14101,42 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>609056</v>
+        <v>609053</v>
       </c>
       <c r="R125" t="n">
-        <v>7062848</v>
+        <v>7062842</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -14191,10 +14195,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125271717</v>
+        <v>125271349</v>
       </c>
       <c r="B126" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14203,30 +14207,31 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P126" t="inlineStr">
@@ -14235,10 +14240,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>609076</v>
+        <v>609012</v>
       </c>
       <c r="R126" t="n">
-        <v>7062922</v>
+        <v>7062832</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14271,6 +14276,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14297,10 +14307,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125271462</v>
+        <v>125271533</v>
       </c>
       <c r="B127" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14309,42 +14319,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>609053</v>
+        <v>609058</v>
       </c>
       <c r="R127" t="n">
-        <v>7062842</v>
+        <v>7062860</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -14403,10 +14409,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125270406</v>
+        <v>125271754</v>
       </c>
       <c r="B128" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14415,38 +14421,42 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>609114</v>
+        <v>609075</v>
       </c>
       <c r="R128" t="n">
-        <v>7062709</v>
+        <v>7062923</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -14505,10 +14515,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125271349</v>
+        <v>125271430</v>
       </c>
       <c r="B129" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14521,39 +14531,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>609012</v>
+        <v>609049</v>
       </c>
       <c r="R129" t="n">
-        <v>7062832</v>
+        <v>7062834</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -14586,11 +14591,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14617,10 +14617,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125271814</v>
+        <v>125270100</v>
       </c>
       <c r="B130" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14633,21 +14633,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14657,10 +14657,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>609083</v>
+        <v>609102</v>
       </c>
       <c r="R130" t="n">
-        <v>7062960</v>
+        <v>7062918</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14719,10 +14719,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125271533</v>
+        <v>125270406</v>
       </c>
       <c r="B131" t="n">
-        <v>90977</v>
+        <v>79891</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14731,25 +14731,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14759,10 +14759,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>609058</v>
+        <v>609114</v>
       </c>
       <c r="R131" t="n">
-        <v>7062860</v>
+        <v>7062709</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14821,10 +14821,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125270136</v>
+        <v>125270505</v>
       </c>
       <c r="B132" t="n">
-        <v>79927</v>
+        <v>91012</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14833,25 +14833,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14861,10 +14861,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>609102</v>
+        <v>609082</v>
       </c>
       <c r="R132" t="n">
-        <v>7062917</v>
+        <v>7062688</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14923,10 +14923,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125273101</v>
+        <v>125271565</v>
       </c>
       <c r="B133" t="n">
-        <v>96985</v>
+        <v>79920</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14939,21 +14939,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14963,10 +14963,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>609053</v>
+        <v>609059</v>
       </c>
       <c r="R133" t="n">
-        <v>7063023</v>
+        <v>7062880</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15025,10 +15025,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125271636</v>
+        <v>125271733</v>
       </c>
       <c r="B134" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15037,25 +15037,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15065,10 +15065,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>609058</v>
+        <v>609075</v>
       </c>
       <c r="R134" t="n">
-        <v>7062880</v>
+        <v>7062923</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15127,10 +15127,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125269804</v>
+        <v>125269793</v>
       </c>
       <c r="B135" t="n">
-        <v>78810</v>
+        <v>79891</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15143,21 +15143,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15229,10 +15229,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125269981</v>
+        <v>125271702</v>
       </c>
       <c r="B136" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15241,38 +15241,42 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>609081</v>
+        <v>609074</v>
       </c>
       <c r="R136" t="n">
-        <v>7063021</v>
+        <v>7062921</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15331,10 +15335,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125271702</v>
+        <v>125270136</v>
       </c>
       <c r="B137" t="n">
-        <v>98101</v>
+        <v>79927</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15343,42 +15347,38 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>609074</v>
+        <v>609102</v>
       </c>
       <c r="R137" t="n">
-        <v>7062921</v>
+        <v>7062917</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15437,10 +15437,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125271733</v>
+        <v>125269804</v>
       </c>
       <c r="B138" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15449,25 +15449,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15477,10 +15477,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>609075</v>
+        <v>609090</v>
       </c>
       <c r="R138" t="n">
-        <v>7062923</v>
+        <v>7063026</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15539,10 +15539,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125269793</v>
+        <v>125271489</v>
       </c>
       <c r="B139" t="n">
-        <v>79891</v>
+        <v>90977</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15551,25 +15551,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15579,10 +15579,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>609090</v>
+        <v>609056</v>
       </c>
       <c r="R139" t="n">
-        <v>7063026</v>
+        <v>7062848</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15747,10 +15747,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125307928</v>
+        <v>125307925</v>
       </c>
       <c r="B141" t="n">
-        <v>79920</v>
+        <v>57513</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15759,30 +15759,35 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15790,10 +15795,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>609121</v>
+        <v>609034</v>
       </c>
       <c r="R141" t="n">
-        <v>7062933</v>
+        <v>7062660</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15828,13 +15833,17 @@
           <t>2025-05-20</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15853,10 +15862,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125307925</v>
+        <v>125307928</v>
       </c>
       <c r="B142" t="n">
-        <v>57513</v>
+        <v>79920</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15865,35 +15874,30 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
@@ -15901,10 +15905,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>609034</v>
+        <v>609121</v>
       </c>
       <c r="R142" t="n">
-        <v>7062660</v>
+        <v>7062933</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15939,17 +15943,13 @@
           <t>2025-05-20</t>
         </is>
       </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD142" t="b">
         <v>0</v>
       </c>
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -13269,10 +13269,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125269977</v>
+        <v>125270406</v>
       </c>
       <c r="B117" t="n">
-        <v>79920</v>
+        <v>80028</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13281,25 +13281,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>609090</v>
+        <v>609114</v>
       </c>
       <c r="R117" t="n">
-        <v>7063013</v>
+        <v>7062709</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13371,10 +13371,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125269871</v>
+        <v>125271814</v>
       </c>
       <c r="B118" t="n">
-        <v>91012</v>
+        <v>78947</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13387,21 +13387,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>609090</v>
+        <v>609083</v>
       </c>
       <c r="R118" t="n">
-        <v>7063026</v>
+        <v>7062960</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13473,10 +13473,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125271636</v>
+        <v>125271489</v>
       </c>
       <c r="B119" t="n">
-        <v>78810</v>
+        <v>91131</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13485,25 +13485,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13513,10 +13513,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>609058</v>
+        <v>609056</v>
       </c>
       <c r="R119" t="n">
-        <v>7062880</v>
+        <v>7062848</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13575,10 +13575,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125273101</v>
+        <v>125271349</v>
       </c>
       <c r="B120" t="n">
-        <v>96985</v>
+        <v>57635</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13587,38 +13587,43 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>609053</v>
+        <v>609012</v>
       </c>
       <c r="R120" t="n">
-        <v>7063023</v>
+        <v>7062832</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13651,6 +13656,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13677,10 +13687,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125269981</v>
+        <v>125269793</v>
       </c>
       <c r="B121" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13717,10 +13727,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>609081</v>
+        <v>609090</v>
       </c>
       <c r="R121" t="n">
-        <v>7063021</v>
+        <v>7063026</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13779,10 +13789,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125270531</v>
+        <v>125271636</v>
       </c>
       <c r="B122" t="n">
-        <v>91673</v>
+        <v>78947</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13791,25 +13801,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13819,10 +13829,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>609079</v>
+        <v>609058</v>
       </c>
       <c r="R122" t="n">
-        <v>7062685</v>
+        <v>7062880</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13881,10 +13891,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125271814</v>
+        <v>125269871</v>
       </c>
       <c r="B123" t="n">
-        <v>78810</v>
+        <v>91166</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13897,21 +13907,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13921,10 +13931,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>609083</v>
+        <v>609090</v>
       </c>
       <c r="R123" t="n">
-        <v>7062960</v>
+        <v>7063026</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13983,10 +13993,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125271717</v>
+        <v>125269977</v>
       </c>
       <c r="B124" t="n">
-        <v>98101</v>
+        <v>80057</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13995,42 +14005,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>609076</v>
+        <v>609090</v>
       </c>
       <c r="R124" t="n">
-        <v>7062922</v>
+        <v>7063013</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -14089,10 +14095,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125271462</v>
+        <v>125270531</v>
       </c>
       <c r="B125" t="n">
-        <v>98101</v>
+        <v>91833</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14105,38 +14111,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>609053</v>
+        <v>609079</v>
       </c>
       <c r="R125" t="n">
-        <v>7062842</v>
+        <v>7062685</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -14195,10 +14197,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125271349</v>
+        <v>125270505</v>
       </c>
       <c r="B126" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14211,39 +14213,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>609012</v>
+        <v>609082</v>
       </c>
       <c r="R126" t="n">
-        <v>7062832</v>
+        <v>7062688</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14276,11 +14273,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14310,7 +14302,7 @@
         <v>125271533</v>
       </c>
       <c r="B127" t="n">
-        <v>90977</v>
+        <v>91131</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14409,10 +14401,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125271754</v>
+        <v>125273101</v>
       </c>
       <c r="B128" t="n">
-        <v>98101</v>
+        <v>97153</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14421,42 +14413,38 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>609075</v>
+        <v>609053</v>
       </c>
       <c r="R128" t="n">
-        <v>7062923</v>
+        <v>7063023</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -14515,10 +14503,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125271430</v>
+        <v>125271717</v>
       </c>
       <c r="B129" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14527,38 +14515,42 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>609049</v>
+        <v>609076</v>
       </c>
       <c r="R129" t="n">
-        <v>7062834</v>
+        <v>7062922</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -14617,10 +14609,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125270100</v>
+        <v>125271702</v>
       </c>
       <c r="B130" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14629,38 +14621,42 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>609102</v>
+        <v>609074</v>
       </c>
       <c r="R130" t="n">
-        <v>7062918</v>
+        <v>7062921</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14719,10 +14715,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125270406</v>
+        <v>125270100</v>
       </c>
       <c r="B131" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14759,10 +14755,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>609114</v>
+        <v>609102</v>
       </c>
       <c r="R131" t="n">
-        <v>7062709</v>
+        <v>7062918</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14821,10 +14817,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125270505</v>
+        <v>125269981</v>
       </c>
       <c r="B132" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14837,21 +14833,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14861,10 +14857,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>609082</v>
+        <v>609081</v>
       </c>
       <c r="R132" t="n">
-        <v>7062688</v>
+        <v>7063021</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14923,10 +14919,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125271565</v>
+        <v>125271430</v>
       </c>
       <c r="B133" t="n">
-        <v>79920</v>
+        <v>91166</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14935,25 +14931,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14963,10 +14959,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>609059</v>
+        <v>609049</v>
       </c>
       <c r="R133" t="n">
-        <v>7062880</v>
+        <v>7062834</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -15025,10 +15021,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125271733</v>
+        <v>125271754</v>
       </c>
       <c r="B134" t="n">
-        <v>79920</v>
+        <v>98269</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15037,28 +15033,32 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
@@ -15127,10 +15127,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125269793</v>
+        <v>125271733</v>
       </c>
       <c r="B135" t="n">
-        <v>79891</v>
+        <v>80057</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15139,25 +15139,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15167,10 +15167,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>609090</v>
+        <v>609075</v>
       </c>
       <c r="R135" t="n">
-        <v>7063026</v>
+        <v>7062923</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15229,10 +15229,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125271702</v>
+        <v>125271565</v>
       </c>
       <c r="B136" t="n">
-        <v>98101</v>
+        <v>80057</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15241,42 +15241,38 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>609074</v>
+        <v>609059</v>
       </c>
       <c r="R136" t="n">
-        <v>7062921</v>
+        <v>7062880</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15338,7 +15334,7 @@
         <v>125270136</v>
       </c>
       <c r="B137" t="n">
-        <v>79927</v>
+        <v>80064</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15440,7 +15436,7 @@
         <v>125269804</v>
       </c>
       <c r="B138" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15539,10 +15535,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125271489</v>
+        <v>125271462</v>
       </c>
       <c r="B139" t="n">
-        <v>90977</v>
+        <v>98269</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15551,38 +15547,42 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>609056</v>
+        <v>609053</v>
       </c>
       <c r="R139" t="n">
-        <v>7062848</v>
+        <v>7062842</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15641,10 +15641,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125307927</v>
+        <v>125307925</v>
       </c>
       <c r="B140" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15657,26 +15657,31 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
-      <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
@@ -15684,10 +15689,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>609121</v>
+        <v>609034</v>
       </c>
       <c r="R140" t="n">
-        <v>7062933</v>
+        <v>7062660</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15722,13 +15727,17 @@
           <t>2025-05-20</t>
         </is>
       </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD140" t="b">
         <v>0</v>
       </c>
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
@@ -15747,10 +15756,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125307925</v>
+        <v>125307928</v>
       </c>
       <c r="B141" t="n">
-        <v>57513</v>
+        <v>80057</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15759,35 +15768,30 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
@@ -15795,10 +15799,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>609034</v>
+        <v>609121</v>
       </c>
       <c r="R141" t="n">
-        <v>7062660</v>
+        <v>7062933</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15833,17 +15837,13 @@
           <t>2025-05-20</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD141" t="b">
         <v>0</v>
       </c>
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -15862,10 +15862,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125307928</v>
+        <v>125307927</v>
       </c>
       <c r="B142" t="n">
-        <v>79920</v>
+        <v>80028</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15874,25 +15874,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15971,7 +15971,7 @@
         <v>125269907</v>
       </c>
       <c r="B143" t="n">
-        <v>91361</v>
+        <v>91521</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -13993,10 +13993,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125269977</v>
+        <v>125270531</v>
       </c>
       <c r="B124" t="n">
-        <v>80057</v>
+        <v>91833</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14005,25 +14005,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14033,10 +14033,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>609090</v>
+        <v>609079</v>
       </c>
       <c r="R124" t="n">
-        <v>7063013</v>
+        <v>7062685</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -14095,10 +14095,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125270531</v>
+        <v>125270505</v>
       </c>
       <c r="B125" t="n">
-        <v>91833</v>
+        <v>91166</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14107,25 +14107,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14135,10 +14135,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>609079</v>
+        <v>609082</v>
       </c>
       <c r="R125" t="n">
-        <v>7062685</v>
+        <v>7062688</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -14197,10 +14197,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125270505</v>
+        <v>125269977</v>
       </c>
       <c r="B126" t="n">
-        <v>91166</v>
+        <v>80057</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14209,25 +14209,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14237,10 +14237,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>609082</v>
+        <v>609090</v>
       </c>
       <c r="R126" t="n">
-        <v>7062688</v>
+        <v>7063013</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -13269,10 +13269,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125270406</v>
+        <v>125271814</v>
       </c>
       <c r="B117" t="n">
-        <v>80028</v>
+        <v>78947</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13285,21 +13285,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13309,10 +13309,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>609114</v>
+        <v>609083</v>
       </c>
       <c r="R117" t="n">
-        <v>7062709</v>
+        <v>7062960</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13371,10 +13371,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125271814</v>
+        <v>125271533</v>
       </c>
       <c r="B118" t="n">
-        <v>78947</v>
+        <v>91131</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13383,25 +13383,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13411,10 +13411,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>609083</v>
+        <v>609058</v>
       </c>
       <c r="R118" t="n">
-        <v>7062960</v>
+        <v>7062860</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13473,10 +13473,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125271489</v>
+        <v>125269804</v>
       </c>
       <c r="B119" t="n">
-        <v>91131</v>
+        <v>78947</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13485,25 +13485,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13513,10 +13513,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>609056</v>
+        <v>609090</v>
       </c>
       <c r="R119" t="n">
-        <v>7062848</v>
+        <v>7063026</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13575,10 +13575,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125271349</v>
+        <v>125270100</v>
       </c>
       <c r="B120" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13591,39 +13591,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>609012</v>
+        <v>609102</v>
       </c>
       <c r="R120" t="n">
-        <v>7062832</v>
+        <v>7062918</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13656,11 +13651,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13687,10 +13677,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125269793</v>
+        <v>125273101</v>
       </c>
       <c r="B121" t="n">
-        <v>80028</v>
+        <v>97153</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13699,25 +13689,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13727,10 +13717,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>609090</v>
+        <v>609053</v>
       </c>
       <c r="R121" t="n">
-        <v>7063026</v>
+        <v>7063023</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13789,10 +13779,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125271636</v>
+        <v>125269793</v>
       </c>
       <c r="B122" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13805,21 +13795,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13829,10 +13819,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>609058</v>
+        <v>609090</v>
       </c>
       <c r="R122" t="n">
-        <v>7062880</v>
+        <v>7063026</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13891,7 +13881,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125269871</v>
+        <v>125271430</v>
       </c>
       <c r="B123" t="n">
         <v>91166</v>
@@ -13931,10 +13921,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>609090</v>
+        <v>609049</v>
       </c>
       <c r="R123" t="n">
-        <v>7063026</v>
+        <v>7062834</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13993,10 +13983,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125270531</v>
+        <v>125271717</v>
       </c>
       <c r="B124" t="n">
-        <v>91833</v>
+        <v>98269</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14009,34 +13999,38 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>609079</v>
+        <v>609076</v>
       </c>
       <c r="R124" t="n">
-        <v>7062685</v>
+        <v>7062922</v>
       </c>
       <c r="S124" t="n">
         <v>15</v>
@@ -14095,10 +14089,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125270505</v>
+        <v>125271733</v>
       </c>
       <c r="B125" t="n">
-        <v>91166</v>
+        <v>80057</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14107,25 +14101,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14135,10 +14129,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>609082</v>
+        <v>609075</v>
       </c>
       <c r="R125" t="n">
-        <v>7062688</v>
+        <v>7062923</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -14197,10 +14191,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125269977</v>
+        <v>125270531</v>
       </c>
       <c r="B126" t="n">
-        <v>80057</v>
+        <v>91833</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14209,25 +14203,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>898</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14237,10 +14231,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>609090</v>
+        <v>609079</v>
       </c>
       <c r="R126" t="n">
-        <v>7063013</v>
+        <v>7062685</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14299,10 +14293,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125271533</v>
+        <v>125271636</v>
       </c>
       <c r="B127" t="n">
-        <v>91131</v>
+        <v>78947</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14311,25 +14305,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14342,7 +14336,7 @@
         <v>609058</v>
       </c>
       <c r="R127" t="n">
-        <v>7062860</v>
+        <v>7062880</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -14401,10 +14395,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125273101</v>
+        <v>125271565</v>
       </c>
       <c r="B128" t="n">
-        <v>97153</v>
+        <v>80057</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14417,21 +14411,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14441,10 +14435,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>609053</v>
+        <v>609059</v>
       </c>
       <c r="R128" t="n">
-        <v>7063023</v>
+        <v>7062880</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -14503,10 +14497,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125271717</v>
+        <v>125270136</v>
       </c>
       <c r="B129" t="n">
-        <v>98269</v>
+        <v>80064</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14515,42 +14509,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>6464</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>609076</v>
+        <v>609102</v>
       </c>
       <c r="R129" t="n">
-        <v>7062922</v>
+        <v>7062917</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -14609,10 +14599,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125271702</v>
+        <v>125270406</v>
       </c>
       <c r="B130" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -14621,42 +14611,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>609074</v>
+        <v>609114</v>
       </c>
       <c r="R130" t="n">
-        <v>7062921</v>
+        <v>7062709</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14715,10 +14701,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125270100</v>
+        <v>125270505</v>
       </c>
       <c r="B131" t="n">
-        <v>80028</v>
+        <v>91166</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14731,21 +14717,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14755,10 +14741,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>609102</v>
+        <v>609082</v>
       </c>
       <c r="R131" t="n">
-        <v>7062918</v>
+        <v>7062688</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14817,10 +14803,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125269981</v>
+        <v>125271462</v>
       </c>
       <c r="B132" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14829,38 +14815,42 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>609081</v>
+        <v>609053</v>
       </c>
       <c r="R132" t="n">
-        <v>7063021</v>
+        <v>7062842</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14919,10 +14909,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125271430</v>
+        <v>125271349</v>
       </c>
       <c r="B133" t="n">
-        <v>91166</v>
+        <v>57635</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14935,34 +14925,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>609049</v>
+        <v>609012</v>
       </c>
       <c r="R133" t="n">
-        <v>7062834</v>
+        <v>7062832</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14995,6 +14990,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15021,7 +15021,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125271754</v>
+        <v>125271702</v>
       </c>
       <c r="B134" t="n">
         <v>98269</v>
@@ -15056,7 +15056,7 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -15065,10 +15065,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>609075</v>
+        <v>609074</v>
       </c>
       <c r="R134" t="n">
-        <v>7062923</v>
+        <v>7062921</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15127,7 +15127,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125271733</v>
+        <v>125269977</v>
       </c>
       <c r="B135" t="n">
         <v>80057</v>
@@ -15167,10 +15167,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>609075</v>
+        <v>609090</v>
       </c>
       <c r="R135" t="n">
-        <v>7062923</v>
+        <v>7063013</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15229,10 +15229,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125271565</v>
+        <v>125269981</v>
       </c>
       <c r="B136" t="n">
-        <v>80057</v>
+        <v>80028</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15241,25 +15241,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15269,10 +15269,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>609059</v>
+        <v>609081</v>
       </c>
       <c r="R136" t="n">
-        <v>7062880</v>
+        <v>7063021</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15331,10 +15331,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125270136</v>
+        <v>125271489</v>
       </c>
       <c r="B137" t="n">
-        <v>80064</v>
+        <v>91131</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -15347,21 +15347,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6464</v>
+        <v>5447</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15371,10 +15371,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>609102</v>
+        <v>609056</v>
       </c>
       <c r="R137" t="n">
-        <v>7062917</v>
+        <v>7062848</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15433,10 +15433,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>125269804</v>
+        <v>125271754</v>
       </c>
       <c r="B138" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -15445,38 +15445,42 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>609090</v>
+        <v>609075</v>
       </c>
       <c r="R138" t="n">
-        <v>7063026</v>
+        <v>7062923</v>
       </c>
       <c r="S138" t="n">
         <v>15</v>
@@ -15535,10 +15539,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125271462</v>
+        <v>125269871</v>
       </c>
       <c r="B139" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -15547,42 +15551,38 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>609053</v>
+        <v>609090</v>
       </c>
       <c r="R139" t="n">
-        <v>7062842</v>
+        <v>7063026</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15756,10 +15756,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125307928</v>
+        <v>125307927</v>
       </c>
       <c r="B141" t="n">
-        <v>80057</v>
+        <v>80028</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15768,25 +15768,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15862,10 +15862,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125307927</v>
+        <v>125307928</v>
       </c>
       <c r="B142" t="n">
-        <v>80028</v>
+        <v>80057</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15874,25 +15874,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -13575,10 +13575,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125270100</v>
+        <v>125273101</v>
       </c>
       <c r="B120" t="n">
-        <v>80028</v>
+        <v>97153</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13587,25 +13587,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13615,10 +13615,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>609102</v>
+        <v>609053</v>
       </c>
       <c r="R120" t="n">
-        <v>7062918</v>
+        <v>7063023</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13677,10 +13677,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125273101</v>
+        <v>125270100</v>
       </c>
       <c r="B121" t="n">
-        <v>97153</v>
+        <v>80028</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13689,25 +13689,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13717,10 +13717,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>609053</v>
+        <v>609102</v>
       </c>
       <c r="R121" t="n">
-        <v>7063023</v>
+        <v>7062918</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY143"/>
+  <dimension ref="A1:AY144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13269,15 +13269,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125271814</v>
+        <v>125270100</v>
       </c>
       <c r="B117" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13285,21 +13280,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13309,10 +13304,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>609083</v>
+        <v>609102</v>
       </c>
       <c r="R117" t="n">
-        <v>7062960</v>
+        <v>7062918</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13371,50 +13366,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125271533</v>
+        <v>125271349</v>
       </c>
       <c r="B118" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>609058</v>
+        <v>609012</v>
       </c>
       <c r="R118" t="n">
-        <v>7062860</v>
+        <v>7062832</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13447,6 +13442,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13473,37 +13473,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125269804</v>
+        <v>125270531</v>
       </c>
       <c r="B119" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13513,10 +13508,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>609090</v>
+        <v>609079</v>
       </c>
       <c r="R119" t="n">
-        <v>7063026</v>
+        <v>7062685</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13575,15 +13570,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125273101</v>
+        <v>125271489</v>
       </c>
       <c r="B120" t="n">
-        <v>97153</v>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13591,21 +13581,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13615,10 +13605,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>609053</v>
+        <v>609056</v>
       </c>
       <c r="R120" t="n">
-        <v>7063023</v>
+        <v>7062848</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13677,15 +13667,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125270100</v>
+        <v>125269804</v>
       </c>
       <c r="B121" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13693,21 +13678,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13717,10 +13702,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>609102</v>
+        <v>609090</v>
       </c>
       <c r="R121" t="n">
-        <v>7062918</v>
+        <v>7063026</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13779,37 +13764,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125269793</v>
+        <v>125271733</v>
       </c>
       <c r="B122" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13819,10 +13799,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>609090</v>
+        <v>609075</v>
       </c>
       <c r="R122" t="n">
-        <v>7063026</v>
+        <v>7062923</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13881,15 +13861,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125271430</v>
+        <v>125269871</v>
       </c>
       <c r="B123" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13921,10 +13896,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>609049</v>
+        <v>609090</v>
       </c>
       <c r="R123" t="n">
-        <v>7062834</v>
+        <v>7063026</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13986,12 +13961,7 @@
         <v>125271717</v>
       </c>
       <c r="B124" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14089,37 +14059,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125271733</v>
+        <v>125269793</v>
       </c>
       <c r="B125" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14129,10 +14094,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>609075</v>
+        <v>609090</v>
       </c>
       <c r="R125" t="n">
-        <v>7062923</v>
+        <v>7063026</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -14191,37 +14156,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125270531</v>
+        <v>125271565</v>
       </c>
       <c r="B126" t="n">
-        <v>91833</v>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>898</v>
+        <v>6462</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14231,10 +14191,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>609079</v>
+        <v>609059</v>
       </c>
       <c r="R126" t="n">
-        <v>7062685</v>
+        <v>7062880</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14293,37 +14253,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125271636</v>
+        <v>125271533</v>
       </c>
       <c r="B127" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14336,7 +14291,7 @@
         <v>609058</v>
       </c>
       <c r="R127" t="n">
-        <v>7062880</v>
+        <v>7062860</v>
       </c>
       <c r="S127" t="n">
         <v>15</v>
@@ -14395,50 +14350,49 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125271565</v>
+        <v>125271462</v>
       </c>
       <c r="B128" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>609059</v>
+        <v>609053</v>
       </c>
       <c r="R128" t="n">
-        <v>7062880</v>
+        <v>7062842</v>
       </c>
       <c r="S128" t="n">
         <v>15</v>
@@ -14497,37 +14451,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125270136</v>
+        <v>125269981</v>
       </c>
       <c r="B129" t="n">
-        <v>80064</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14537,10 +14486,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>609102</v>
+        <v>609081</v>
       </c>
       <c r="R129" t="n">
-        <v>7062917</v>
+        <v>7063021</v>
       </c>
       <c r="S129" t="n">
         <v>15</v>
@@ -14599,15 +14548,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125270406</v>
+        <v>125271636</v>
       </c>
       <c r="B130" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14615,21 +14559,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14639,10 +14583,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>609114</v>
+        <v>609058</v>
       </c>
       <c r="R130" t="n">
-        <v>7062709</v>
+        <v>7062880</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14701,37 +14645,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125270505</v>
+        <v>125273101</v>
       </c>
       <c r="B131" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97208</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14741,10 +14680,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>609082</v>
+        <v>609053</v>
       </c>
       <c r="R131" t="n">
-        <v>7062688</v>
+        <v>7063023</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>
@@ -14803,54 +14742,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>125271462</v>
+        <v>125270505</v>
       </c>
       <c r="B132" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>609053</v>
+        <v>609082</v>
       </c>
       <c r="R132" t="n">
-        <v>7062842</v>
+        <v>7062688</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -14909,43 +14839,37 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>125271349</v>
+        <v>125271702</v>
       </c>
       <c r="B133" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -14954,10 +14878,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>609012</v>
+        <v>609074</v>
       </c>
       <c r="R133" t="n">
-        <v>7062832</v>
+        <v>7062921</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14990,11 +14914,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15021,54 +14940,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>125271702</v>
+        <v>125271430</v>
       </c>
       <c r="B134" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>609074</v>
+        <v>609049</v>
       </c>
       <c r="R134" t="n">
-        <v>7062921</v>
+        <v>7062834</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -15127,37 +15037,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>125269977</v>
+        <v>125271814</v>
       </c>
       <c r="B135" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15167,10 +15072,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>609090</v>
+        <v>609083</v>
       </c>
       <c r="R135" t="n">
-        <v>7063013</v>
+        <v>7062960</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -15229,37 +15134,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>125269981</v>
+        <v>125270136</v>
       </c>
       <c r="B136" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80106</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15269,10 +15169,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>609081</v>
+        <v>609102</v>
       </c>
       <c r="R136" t="n">
-        <v>7063021</v>
+        <v>7062917</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -15331,15 +15231,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>125271489</v>
+        <v>125269977</v>
       </c>
       <c r="B137" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15347,21 +15242,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15371,10 +15266,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>609056</v>
+        <v>609090</v>
       </c>
       <c r="R137" t="n">
-        <v>7062848</v>
+        <v>7063013</v>
       </c>
       <c r="S137" t="n">
         <v>15</v>
@@ -15436,12 +15331,7 @@
         <v>125271754</v>
       </c>
       <c r="B138" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15539,15 +15429,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>125269871</v>
+        <v>125270406</v>
       </c>
       <c r="B139" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15555,21 +15440,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15579,10 +15464,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>609090</v>
+        <v>609114</v>
       </c>
       <c r="R139" t="n">
-        <v>7063026</v>
+        <v>7062709</v>
       </c>
       <c r="S139" t="n">
         <v>15</v>
@@ -15644,12 +15529,7 @@
         <v>125307925</v>
       </c>
       <c r="B140" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15759,12 +15639,7 @@
         <v>125307927</v>
       </c>
       <c r="B141" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15865,12 +15740,7 @@
         <v>125307928</v>
       </c>
       <c r="B142" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15971,12 +15841,7 @@
         <v>125269907</v>
       </c>
       <c r="B143" t="n">
-        <v>91521</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91575</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16067,6 +15932,108 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>125780954</v>
+      </c>
+      <c r="B144" t="n">
+        <v>96577</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>53</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Kyrkstigen brant, Ång</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>609024</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7062586</v>
+      </c>
+      <c r="S144" t="n">
+        <v>25</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-06-07</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Martin Bergström</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Martin Bergström</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -13476,7 +13476,7 @@
         <v>125270531</v>
       </c>
       <c r="B119" t="n">
-        <v>91887</v>
+        <v>91894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>125271489</v>
       </c>
       <c r="B120" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13764,32 +13764,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125271733</v>
+        <v>125269871</v>
       </c>
       <c r="B122" t="n">
-        <v>80099</v>
+        <v>91227</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13799,10 +13799,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>609075</v>
+        <v>609090</v>
       </c>
       <c r="R122" t="n">
-        <v>7062923</v>
+        <v>7063026</v>
       </c>
       <c r="S122" t="n">
         <v>15</v>
@@ -13861,32 +13861,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125269871</v>
+        <v>125271733</v>
       </c>
       <c r="B123" t="n">
-        <v>91220</v>
+        <v>80099</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13896,10 +13896,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>609090</v>
+        <v>609075</v>
       </c>
       <c r="R123" t="n">
-        <v>7063026</v>
+        <v>7062923</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13961,7 +13961,7 @@
         <v>125271717</v>
       </c>
       <c r="B124" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14059,32 +14059,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125269793</v>
+        <v>125271565</v>
       </c>
       <c r="B125" t="n">
-        <v>80070</v>
+        <v>80099</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14094,10 +14094,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>609090</v>
+        <v>609059</v>
       </c>
       <c r="R125" t="n">
-        <v>7063026</v>
+        <v>7062880</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -14156,32 +14156,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125271565</v>
+        <v>125269793</v>
       </c>
       <c r="B126" t="n">
-        <v>80099</v>
+        <v>80070</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14191,10 +14191,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>609059</v>
+        <v>609090</v>
       </c>
       <c r="R126" t="n">
-        <v>7062880</v>
+        <v>7063026</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14256,7 +14256,7 @@
         <v>125271533</v>
       </c>
       <c r="B127" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>125271462</v>
       </c>
       <c r="B128" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>125273101</v>
       </c>
       <c r="B131" t="n">
-        <v>97208</v>
+        <v>97215</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>125270505</v>
       </c>
       <c r="B132" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>125271702</v>
       </c>
       <c r="B133" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>125271430</v>
       </c>
       <c r="B134" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>125271754</v>
       </c>
       <c r="B138" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>125269907</v>
       </c>
       <c r="B143" t="n">
-        <v>91575</v>
+        <v>91582</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>125780954</v>
       </c>
       <c r="B144" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -14548,32 +14548,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>125271636</v>
+        <v>125273101</v>
       </c>
       <c r="B130" t="n">
-        <v>78967</v>
+        <v>97215</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14583,10 +14583,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>609058</v>
+        <v>609053</v>
       </c>
       <c r="R130" t="n">
-        <v>7062880</v>
+        <v>7063023</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -14645,32 +14645,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>125273101</v>
+        <v>125271636</v>
       </c>
       <c r="B131" t="n">
-        <v>97215</v>
+        <v>78967</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14680,10 +14680,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>609053</v>
+        <v>609058</v>
       </c>
       <c r="R131" t="n">
-        <v>7063023</v>
+        <v>7062880</v>
       </c>
       <c r="S131" t="n">
         <v>15</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -13269,10 +13269,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125270100</v>
+        <v>125271349</v>
       </c>
       <c r="B117" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13280,34 +13280,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>609102</v>
+        <v>609012</v>
       </c>
       <c r="R117" t="n">
-        <v>7062918</v>
+        <v>7062832</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13340,6 +13345,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13366,10 +13376,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125271349</v>
+        <v>125270100</v>
       </c>
       <c r="B118" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13377,39 +13387,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>609012</v>
+        <v>609102</v>
       </c>
       <c r="R118" t="n">
-        <v>7062832</v>
+        <v>7062918</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13442,11 +13447,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14059,32 +14059,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125271565</v>
+        <v>125269793</v>
       </c>
       <c r="B125" t="n">
-        <v>80099</v>
+        <v>80070</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14094,10 +14094,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>609059</v>
+        <v>609090</v>
       </c>
       <c r="R125" t="n">
-        <v>7062880</v>
+        <v>7063026</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -14156,32 +14156,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125269793</v>
+        <v>125271565</v>
       </c>
       <c r="B126" t="n">
-        <v>80070</v>
+        <v>80099</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14191,10 +14191,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>609090</v>
+        <v>609059</v>
       </c>
       <c r="R126" t="n">
-        <v>7063026</v>
+        <v>7062880</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -13269,10 +13269,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125271349</v>
+        <v>125270100</v>
       </c>
       <c r="B117" t="n">
-        <v>57651</v>
+        <v>80071</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13280,39 +13280,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>609012</v>
+        <v>609102</v>
       </c>
       <c r="R117" t="n">
-        <v>7062832</v>
+        <v>7062918</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13345,11 +13340,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-05-20</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13376,10 +13366,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125270100</v>
+        <v>125271349</v>
       </c>
       <c r="B118" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13387,34 +13377,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>609102</v>
+        <v>609012</v>
       </c>
       <c r="R118" t="n">
-        <v>7062918</v>
+        <v>7062832</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13447,6 +13442,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, tall</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13473,32 +13473,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125270531</v>
+        <v>125271489</v>
       </c>
       <c r="B119" t="n">
-        <v>91894</v>
+        <v>91193</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>898</v>
+        <v>5447</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13508,10 +13508,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>609079</v>
+        <v>609056</v>
       </c>
       <c r="R119" t="n">
-        <v>7062685</v>
+        <v>7062848</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13570,32 +13570,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125271489</v>
+        <v>125270531</v>
       </c>
       <c r="B120" t="n">
-        <v>91192</v>
+        <v>91898</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5447</v>
+        <v>898</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13605,10 +13605,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>609056</v>
+        <v>609079</v>
       </c>
       <c r="R120" t="n">
-        <v>7062848</v>
+        <v>7062685</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13670,7 +13670,7 @@
         <v>125269804</v>
       </c>
       <c r="B121" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>125269871</v>
       </c>
       <c r="B122" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13864,7 +13864,7 @@
         <v>125271733</v>
       </c>
       <c r="B123" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>125271717</v>
       </c>
       <c r="B124" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14059,32 +14059,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125269793</v>
+        <v>125271565</v>
       </c>
       <c r="B125" t="n">
-        <v>80070</v>
+        <v>80100</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14094,10 +14094,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>609090</v>
+        <v>609059</v>
       </c>
       <c r="R125" t="n">
-        <v>7063026</v>
+        <v>7062880</v>
       </c>
       <c r="S125" t="n">
         <v>15</v>
@@ -14156,32 +14156,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125271565</v>
+        <v>125269793</v>
       </c>
       <c r="B126" t="n">
-        <v>80099</v>
+        <v>80071</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14191,10 +14191,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>609059</v>
+        <v>609090</v>
       </c>
       <c r="R126" t="n">
-        <v>7062880</v>
+        <v>7063026</v>
       </c>
       <c r="S126" t="n">
         <v>15</v>
@@ -14256,7 +14256,7 @@
         <v>125271533</v>
       </c>
       <c r="B127" t="n">
-        <v>91192</v>
+        <v>91193</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>125271462</v>
       </c>
       <c r="B128" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14454,7 +14454,7 @@
         <v>125269981</v>
       </c>
       <c r="B129" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>125273101</v>
       </c>
       <c r="B130" t="n">
-        <v>97215</v>
+        <v>97218</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>125271636</v>
       </c>
       <c r="B131" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14745,7 +14745,7 @@
         <v>125270505</v>
       </c>
       <c r="B132" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>125271702</v>
       </c>
       <c r="B133" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>125271430</v>
       </c>
       <c r="B134" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15040,7 +15040,7 @@
         <v>125271814</v>
       </c>
       <c r="B135" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>125270136</v>
       </c>
       <c r="B136" t="n">
-        <v>80106</v>
+        <v>80107</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         <v>125269977</v>
       </c>
       <c r="B137" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>125271754</v>
       </c>
       <c r="B138" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>125270406</v>
       </c>
       <c r="B139" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>125307927</v>
       </c>
       <c r="B141" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>125307928</v>
       </c>
       <c r="B142" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>125269907</v>
       </c>
       <c r="B143" t="n">
-        <v>91582</v>
+        <v>91586</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>125780954</v>
       </c>
       <c r="B144" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -15841,7 +15841,7 @@
         <v>125269907</v>
       </c>
       <c r="B143" t="n">
-        <v>91586</v>
+        <v>91590</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>125780954</v>
       </c>
       <c r="B144" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -15938,7 +15938,7 @@
         <v>125780954</v>
       </c>
       <c r="B144" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -15938,7 +15938,7 @@
         <v>125780954</v>
       </c>
       <c r="B144" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -15938,7 +15938,7 @@
         <v>125780954</v>
       </c>
       <c r="B144" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -15938,7 +15938,7 @@
         <v>125780954</v>
       </c>
       <c r="B144" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -15938,7 +15938,7 @@
         <v>125780954</v>
       </c>
       <c r="B144" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -15938,7 +15938,7 @@
         <v>125780954</v>
       </c>
       <c r="B144" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -16148,10 +16148,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133685893</v>
+        <v>133686288</v>
       </c>
       <c r="B146" t="n">
-        <v>91981</v>
+        <v>79359</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16159,21 +16159,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16183,13 +16183,13 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>609095</v>
+        <v>609005</v>
       </c>
       <c r="R146" t="n">
-        <v>7062609</v>
+        <v>7062580</v>
       </c>
       <c r="S146" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16228,7 +16228,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16243,12 +16243,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -16366,10 +16366,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133686288</v>
+        <v>133685893</v>
       </c>
       <c r="B148" t="n">
-        <v>79359</v>
+        <v>91981</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16377,21 +16377,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16401,13 +16401,13 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>609005</v>
+        <v>609095</v>
       </c>
       <c r="R148" t="n">
-        <v>7062580</v>
+        <v>7062609</v>
       </c>
       <c r="S148" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16461,44 +16461,44 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133688622</v>
+        <v>133686560</v>
       </c>
       <c r="B149" t="n">
-        <v>80474</v>
+        <v>99203</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16508,10 +16508,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>609084</v>
+        <v>608900</v>
       </c>
       <c r="R149" t="n">
-        <v>7062747</v>
+        <v>7062591</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16543,7 +16543,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16553,7 +16553,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16580,32 +16580,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133686560</v>
+        <v>133688622</v>
       </c>
       <c r="B150" t="n">
-        <v>99203</v>
+        <v>80474</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16615,10 +16615,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>608900</v>
+        <v>609084</v>
       </c>
       <c r="R150" t="n">
-        <v>7062591</v>
+        <v>7062747</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16901,10 +16901,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133688474</v>
+        <v>133685643</v>
       </c>
       <c r="B153" t="n">
-        <v>80474</v>
+        <v>80475</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16912,21 +16912,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16936,13 +16936,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>609072</v>
+        <v>609088</v>
       </c>
       <c r="R153" t="n">
-        <v>7062733</v>
+        <v>7062612</v>
       </c>
       <c r="S153" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16996,12 +16996,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -17250,10 +17250,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133687183</v>
+        <v>133688474</v>
       </c>
       <c r="B156" t="n">
-        <v>57975</v>
+        <v>80474</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17261,39 +17261,34 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>608838</v>
+        <v>609072</v>
       </c>
       <c r="R156" t="n">
-        <v>7062590</v>
+        <v>7062733</v>
       </c>
       <c r="S156" t="n">
         <v>20</v>
@@ -17325,7 +17320,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17335,12 +17330,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>15:50</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17367,10 +17357,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133685643</v>
+        <v>133687183</v>
       </c>
       <c r="B157" t="n">
-        <v>80475</v>
+        <v>57975</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17378,37 +17368,42 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>609088</v>
+        <v>608838</v>
       </c>
       <c r="R157" t="n">
-        <v>7062612</v>
+        <v>7062590</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17437,7 +17432,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17447,7 +17442,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17462,22 +17462,22 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133686911</v>
+        <v>133688330</v>
       </c>
       <c r="B158" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17485,21 +17485,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17509,13 +17509,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>608888</v>
+        <v>609049</v>
       </c>
       <c r="R158" t="n">
-        <v>7062565</v>
+        <v>7062716</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17554,7 +17554,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17569,22 +17569,22 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133684699</v>
+        <v>133686911</v>
       </c>
       <c r="B159" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17592,39 +17592,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>609029</v>
+        <v>608888</v>
       </c>
       <c r="R159" t="n">
-        <v>7062581</v>
+        <v>7062565</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17656,7 +17651,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17666,12 +17661,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17805,10 +17795,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>133688330</v>
+        <v>133684699</v>
       </c>
       <c r="B161" t="n">
-        <v>80474</v>
+        <v>57975</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -17816,37 +17806,42 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>609049</v>
+        <v>609029</v>
       </c>
       <c r="R161" t="n">
-        <v>7062716</v>
+        <v>7062581</v>
       </c>
       <c r="S161" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -17875,7 +17870,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -17885,7 +17880,12 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17900,12 +17900,12 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
@@ -18810,57 +18810,48 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133686482</v>
+        <v>133686107</v>
       </c>
       <c r="B170" t="n">
-        <v>99181</v>
+        <v>91960</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J170" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>608963</v>
+        <v>609073</v>
       </c>
       <c r="R170" t="n">
-        <v>7062549</v>
+        <v>7062583</v>
       </c>
       <c r="S170" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18889,7 +18880,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18899,7 +18890,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18914,50 +18905,49 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133689109</v>
+        <v>133687436</v>
       </c>
       <c r="B171" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">
@@ -18966,13 +18956,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>609115</v>
+        <v>608938</v>
       </c>
       <c r="R171" t="n">
-        <v>7062870</v>
+        <v>7062637</v>
       </c>
       <c r="S171" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -19001,7 +18991,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19011,12 +19001,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19031,60 +19016,69 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133686107</v>
+        <v>133686482</v>
       </c>
       <c r="B172" t="n">
-        <v>91960</v>
+        <v>99181</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>609073</v>
+        <v>608963</v>
       </c>
       <c r="R172" t="n">
-        <v>7062583</v>
+        <v>7062549</v>
       </c>
       <c r="S172" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19113,7 +19107,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19123,7 +19117,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19138,49 +19132,50 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133687436</v>
+        <v>133689109</v>
       </c>
       <c r="B173" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19189,13 +19184,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>608938</v>
+        <v>609115</v>
       </c>
       <c r="R173" t="n">
-        <v>7062637</v>
+        <v>7062870</v>
       </c>
       <c r="S173" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19224,7 +19219,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19234,7 +19229,12 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19249,12 +19249,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -19377,48 +19377,57 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133687934</v>
+        <v>133686590</v>
       </c>
       <c r="B175" t="n">
-        <v>99203</v>
+        <v>99181</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>608995</v>
+        <v>608939</v>
       </c>
       <c r="R175" t="n">
-        <v>7062669</v>
+        <v>7062553</v>
       </c>
       <c r="S175" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -19447,7 +19456,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19457,7 +19466,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19472,12 +19481,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
@@ -19591,57 +19600,48 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133686590</v>
+        <v>133687934</v>
       </c>
       <c r="B177" t="n">
-        <v>99181</v>
+        <v>99203</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>608939</v>
+        <v>608995</v>
       </c>
       <c r="R177" t="n">
-        <v>7062553</v>
+        <v>7062669</v>
       </c>
       <c r="S177" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19680,7 +19680,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19695,12 +19695,12 @@
       <c r="AT177" t="inlineStr"/>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
@@ -19926,38 +19926,42 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>133686474</v>
+        <v>133686675</v>
       </c>
       <c r="B180" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P180" t="inlineStr">
@@ -19966,10 +19970,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>608965</v>
+        <v>608929</v>
       </c>
       <c r="R180" t="n">
-        <v>7062552</v>
+        <v>7062560</v>
       </c>
       <c r="S180" t="n">
         <v>20</v>
@@ -20001,7 +20005,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20011,12 +20015,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20043,42 +20042,38 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>133686675</v>
+        <v>133686474</v>
       </c>
       <c r="B181" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P181" t="inlineStr">
@@ -20087,10 +20082,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>608929</v>
+        <v>608965</v>
       </c>
       <c r="R181" t="n">
-        <v>7062560</v>
+        <v>7062552</v>
       </c>
       <c r="S181" t="n">
         <v>20</v>
@@ -20122,7 +20117,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20132,7 +20127,12 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20159,45 +20159,54 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133686056</v>
+        <v>133686122</v>
       </c>
       <c r="B182" t="n">
-        <v>80474</v>
+        <v>99181</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>609094</v>
+        <v>609086</v>
       </c>
       <c r="R182" t="n">
-        <v>7062584</v>
+        <v>7062577</v>
       </c>
       <c r="S182" t="n">
         <v>20</v>
@@ -20229,7 +20238,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20239,7 +20248,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20266,10 +20275,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133684732</v>
+        <v>133686056</v>
       </c>
       <c r="B183" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20277,21 +20286,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20301,10 +20310,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>609054</v>
+        <v>609094</v>
       </c>
       <c r="R183" t="n">
-        <v>7062595</v>
+        <v>7062584</v>
       </c>
       <c r="S183" t="n">
         <v>20</v>
@@ -20336,7 +20345,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20346,7 +20355,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20373,54 +20382,45 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133686122</v>
+        <v>133684732</v>
       </c>
       <c r="B184" t="n">
-        <v>99181</v>
+        <v>79359</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>609086</v>
+        <v>609054</v>
       </c>
       <c r="R184" t="n">
-        <v>7062577</v>
+        <v>7062595</v>
       </c>
       <c r="S184" t="n">
         <v>20</v>
@@ -20452,7 +20452,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20489,10 +20489,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133684578</v>
+        <v>133685656</v>
       </c>
       <c r="B185" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20500,21 +20500,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20524,10 +20524,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>609027</v>
+        <v>609081</v>
       </c>
       <c r="R185" t="n">
-        <v>7062584</v>
+        <v>7062637</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20596,7 +20596,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133685656</v>
+        <v>133688563</v>
       </c>
       <c r="B186" t="n">
         <v>80474</v>
@@ -20631,13 +20631,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>609081</v>
+        <v>609080</v>
       </c>
       <c r="R186" t="n">
-        <v>7062637</v>
+        <v>7062720</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20691,22 +20691,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133688563</v>
+        <v>133684578</v>
       </c>
       <c r="B187" t="n">
-        <v>80474</v>
+        <v>79359</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20714,21 +20714,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20738,13 +20738,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>609080</v>
+        <v>609027</v>
       </c>
       <c r="R187" t="n">
-        <v>7062720</v>
+        <v>7062584</v>
       </c>
       <c r="S187" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20783,7 +20783,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20798,12 +20798,12 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -21135,38 +21135,37 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133685279</v>
+        <v>133688603</v>
       </c>
       <c r="B191" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -21175,13 +21174,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>609050</v>
+        <v>609082</v>
       </c>
       <c r="R191" t="n">
-        <v>7062603</v>
+        <v>7062749</v>
       </c>
       <c r="S191" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21210,7 +21209,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21220,12 +21219,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21240,49 +21234,50 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133688603</v>
+        <v>133685279</v>
       </c>
       <c r="B192" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -21291,13 +21286,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>609082</v>
+        <v>609050</v>
       </c>
       <c r="R192" t="n">
-        <v>7062749</v>
+        <v>7062603</v>
       </c>
       <c r="S192" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21326,7 +21321,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21336,7 +21331,12 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21351,12 +21351,12 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
@@ -21582,45 +21582,49 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133688336</v>
+        <v>133687570</v>
       </c>
       <c r="B195" t="n">
-        <v>79359</v>
+        <v>99181</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>609051</v>
+        <v>608957</v>
       </c>
       <c r="R195" t="n">
-        <v>7062718</v>
+        <v>7062629</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21652,7 +21656,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21662,7 +21666,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21689,49 +21693,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133687570</v>
+        <v>133688336</v>
       </c>
       <c r="B196" t="n">
-        <v>99181</v>
+        <v>79359</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>608957</v>
+        <v>609051</v>
       </c>
       <c r="R196" t="n">
-        <v>7062629</v>
+        <v>7062718</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21763,7 +21763,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21773,7 +21773,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD196" t="b">

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -16151,7 +16151,7 @@
         <v>133686288</v>
       </c>
       <c r="B146" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>133684740</v>
       </c>
       <c r="B147" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>133685893</v>
       </c>
       <c r="B148" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16473,32 +16473,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133686560</v>
+        <v>133688622</v>
       </c>
       <c r="B149" t="n">
-        <v>99203</v>
+        <v>80481</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16508,10 +16508,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>608900</v>
+        <v>609084</v>
       </c>
       <c r="R149" t="n">
-        <v>7062591</v>
+        <v>7062747</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16543,7 +16543,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16553,7 +16553,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16580,32 +16580,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133688622</v>
+        <v>133686560</v>
       </c>
       <c r="B150" t="n">
-        <v>80474</v>
+        <v>99210</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6458</v>
+        <v>221952</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16615,10 +16615,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>609084</v>
+        <v>608900</v>
       </c>
       <c r="R150" t="n">
-        <v>7062747</v>
+        <v>7062591</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16660,7 +16660,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16690,7 +16690,7 @@
         <v>133684556</v>
       </c>
       <c r="B151" t="n">
-        <v>91960</v>
+        <v>91967</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>133685620</v>
       </c>
       <c r="B152" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16901,10 +16901,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133685643</v>
+        <v>133688474</v>
       </c>
       <c r="B153" t="n">
-        <v>80475</v>
+        <v>80481</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16912,21 +16912,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16936,13 +16936,13 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>609088</v>
+        <v>609072</v>
       </c>
       <c r="R153" t="n">
-        <v>7062612</v>
+        <v>7062733</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16996,12 +16996,12 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
@@ -17137,7 +17137,7 @@
         <v>133684689</v>
       </c>
       <c r="B155" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17250,10 +17250,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133688474</v>
+        <v>133685643</v>
       </c>
       <c r="B156" t="n">
-        <v>80474</v>
+        <v>80482</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17261,21 +17261,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17285,13 +17285,13 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>609072</v>
+        <v>609088</v>
       </c>
       <c r="R156" t="n">
-        <v>7062733</v>
+        <v>7062612</v>
       </c>
       <c r="S156" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17345,12 +17345,12 @@
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
@@ -17474,10 +17474,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133688330</v>
+        <v>133688381</v>
       </c>
       <c r="B158" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17509,10 +17509,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>609049</v>
+        <v>609045</v>
       </c>
       <c r="R158" t="n">
-        <v>7062716</v>
+        <v>7062726</v>
       </c>
       <c r="S158" t="n">
         <v>20</v>
@@ -17544,7 +17544,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17554,7 +17554,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17581,10 +17581,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>133686911</v>
+        <v>133688330</v>
       </c>
       <c r="B159" t="n">
-        <v>79359</v>
+        <v>80481</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17592,21 +17592,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17616,13 +17616,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>608888</v>
+        <v>609049</v>
       </c>
       <c r="R159" t="n">
-        <v>7062565</v>
+        <v>7062716</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17676,22 +17676,22 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>133688381</v>
+        <v>133686911</v>
       </c>
       <c r="B160" t="n">
-        <v>80474</v>
+        <v>79366</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -17699,21 +17699,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17723,13 +17723,13 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>609045</v>
+        <v>608888</v>
       </c>
       <c r="R160" t="n">
-        <v>7062726</v>
+        <v>7062565</v>
       </c>
       <c r="S160" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -17768,7 +17768,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17783,12 +17783,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
@@ -17912,57 +17912,48 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>133687759</v>
+        <v>133687756</v>
       </c>
       <c r="B162" t="n">
-        <v>99181</v>
+        <v>99210</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>221952</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>608986</v>
+        <v>609002</v>
       </c>
       <c r="R162" t="n">
-        <v>7062613</v>
+        <v>7062636</v>
       </c>
       <c r="S162" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18016,57 +18007,66 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>133688254</v>
+        <v>133687759</v>
       </c>
       <c r="B163" t="n">
-        <v>80474</v>
+        <v>99188</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>609028</v>
+        <v>608986</v>
       </c>
       <c r="R163" t="n">
-        <v>7062685</v>
+        <v>7062613</v>
       </c>
       <c r="S163" t="n">
         <v>20</v>
@@ -18098,7 +18098,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18252,32 +18252,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133687756</v>
+        <v>133688254</v>
       </c>
       <c r="B165" t="n">
-        <v>99203</v>
+        <v>80481</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18287,13 +18287,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>609002</v>
+        <v>609028</v>
       </c>
       <c r="R165" t="n">
-        <v>7062636</v>
+        <v>7062685</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18347,12 +18347,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
@@ -18362,7 +18362,7 @@
         <v>133686301</v>
       </c>
       <c r="B166" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18473,7 +18473,7 @@
         <v>133684282</v>
       </c>
       <c r="B167" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18586,10 +18586,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133687243</v>
+        <v>133685133</v>
       </c>
       <c r="B168" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18597,34 +18597,39 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>608871</v>
+        <v>609059</v>
       </c>
       <c r="R168" t="n">
-        <v>7062630</v>
+        <v>7062616</v>
       </c>
       <c r="S168" t="n">
         <v>20</v>
@@ -18656,7 +18661,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18666,7 +18671,12 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18693,10 +18703,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133685133</v>
+        <v>133687243</v>
       </c>
       <c r="B169" t="n">
-        <v>57975</v>
+        <v>79366</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -18704,39 +18714,34 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>609059</v>
+        <v>608871</v>
       </c>
       <c r="R169" t="n">
-        <v>7062616</v>
+        <v>7062630</v>
       </c>
       <c r="S169" t="n">
         <v>20</v>
@@ -18768,7 +18773,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18778,12 +18783,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18810,10 +18810,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133686107</v>
+        <v>133689109</v>
       </c>
       <c r="B170" t="n">
-        <v>91960</v>
+        <v>57975</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18821,37 +18821,42 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>609073</v>
+        <v>609115</v>
       </c>
       <c r="R170" t="n">
-        <v>7062583</v>
+        <v>7062870</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -18880,7 +18885,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18890,7 +18895,12 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18905,22 +18915,22 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133687436</v>
+        <v>133686482</v>
       </c>
       <c r="B171" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18950,19 +18960,24 @@
           <t>10</t>
         </is>
       </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>608938</v>
+        <v>608963</v>
       </c>
       <c r="R171" t="n">
-        <v>7062637</v>
+        <v>7062549</v>
       </c>
       <c r="S171" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -18991,7 +19006,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19001,7 +19016,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19016,69 +19031,60 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133686482</v>
+        <v>133686107</v>
       </c>
       <c r="B172" t="n">
-        <v>99181</v>
+        <v>91967</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>608963</v>
+        <v>609073</v>
       </c>
       <c r="R172" t="n">
-        <v>7062549</v>
+        <v>7062583</v>
       </c>
       <c r="S172" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19107,7 +19113,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19117,7 +19123,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19132,50 +19138,49 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133689109</v>
+        <v>133687436</v>
       </c>
       <c r="B173" t="n">
-        <v>57975</v>
+        <v>99188</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -19184,13 +19189,13 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>609115</v>
+        <v>608938</v>
       </c>
       <c r="R173" t="n">
-        <v>7062870</v>
+        <v>7062637</v>
       </c>
       <c r="S173" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -19219,7 +19224,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19229,12 +19234,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>17:03</t>
-        </is>
-      </c>
-      <c r="AC173" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19249,12 +19249,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -19264,7 +19264,7 @@
         <v>133688188</v>
       </c>
       <c r="B174" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>133686590</v>
       </c>
       <c r="B175" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19496,7 +19496,7 @@
         <v>133687890</v>
       </c>
       <c r="B176" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>133687934</v>
       </c>
       <c r="B177" t="n">
-        <v>99203</v>
+        <v>99210</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>133688184</v>
       </c>
       <c r="B178" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>133686675</v>
       </c>
       <c r="B180" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20159,54 +20159,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133686122</v>
+        <v>133686056</v>
       </c>
       <c r="B182" t="n">
-        <v>99181</v>
+        <v>80481</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>609086</v>
+        <v>609094</v>
       </c>
       <c r="R182" t="n">
-        <v>7062577</v>
+        <v>7062584</v>
       </c>
       <c r="S182" t="n">
         <v>20</v>
@@ -20238,7 +20229,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20248,7 +20239,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20275,45 +20266,54 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133686056</v>
+        <v>133686122</v>
       </c>
       <c r="B183" t="n">
-        <v>80474</v>
+        <v>99188</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>609094</v>
+        <v>609086</v>
       </c>
       <c r="R183" t="n">
-        <v>7062584</v>
+        <v>7062577</v>
       </c>
       <c r="S183" t="n">
         <v>20</v>
@@ -20345,7 +20345,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20355,7 +20355,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20385,7 +20385,7 @@
         <v>133684732</v>
       </c>
       <c r="B184" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20489,10 +20489,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133685656</v>
+        <v>133684578</v>
       </c>
       <c r="B185" t="n">
-        <v>80474</v>
+        <v>79366</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20500,21 +20500,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20524,10 +20524,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>609081</v>
+        <v>609027</v>
       </c>
       <c r="R185" t="n">
-        <v>7062637</v>
+        <v>7062584</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20559,7 +20559,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20569,7 +20569,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20596,10 +20596,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133688563</v>
+        <v>133685656</v>
       </c>
       <c r="B186" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20631,13 +20631,13 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>609080</v>
+        <v>609081</v>
       </c>
       <c r="R186" t="n">
-        <v>7062720</v>
+        <v>7062637</v>
       </c>
       <c r="S186" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20676,7 +20676,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20691,22 +20691,22 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133684578</v>
+        <v>133688563</v>
       </c>
       <c r="B187" t="n">
-        <v>79359</v>
+        <v>80481</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20714,21 +20714,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20738,13 +20738,13 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>609027</v>
+        <v>609080</v>
       </c>
       <c r="R187" t="n">
-        <v>7062584</v>
+        <v>7062720</v>
       </c>
       <c r="S187" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20773,7 +20773,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20783,7 +20783,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20798,12 +20798,12 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
@@ -20813,7 +20813,7 @@
         <v>133688914</v>
       </c>
       <c r="B188" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>133688242</v>
       </c>
       <c r="B189" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21027,7 +21027,7 @@
         <v>133686596</v>
       </c>
       <c r="B190" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21135,37 +21135,38 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133688603</v>
+        <v>133685279</v>
       </c>
       <c r="B191" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -21174,13 +21175,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>609082</v>
+        <v>609050</v>
       </c>
       <c r="R191" t="n">
-        <v>7062749</v>
+        <v>7062603</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -21209,7 +21210,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21219,7 +21220,12 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21234,50 +21240,49 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133685279</v>
+        <v>133688603</v>
       </c>
       <c r="B192" t="n">
-        <v>57975</v>
+        <v>99188</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -21286,13 +21291,13 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>609050</v>
+        <v>609082</v>
       </c>
       <c r="R192" t="n">
-        <v>7062603</v>
+        <v>7062749</v>
       </c>
       <c r="S192" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -21321,7 +21326,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21331,12 +21336,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21351,12 +21351,12 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
@@ -21478,7 +21478,7 @@
         <v>133688785</v>
       </c>
       <c r="B194" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>133687570</v>
       </c>
       <c r="B195" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>133688336</v>
       </c>
       <c r="B196" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY219"/>
+  <dimension ref="A1:AY220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20403,48 +20403,48 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133686560</v>
+        <v>134530697</v>
       </c>
       <c r="B188" t="n">
-        <v>99217</v>
+        <v>99195</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Skalberget, Skalberget, Ång</t>
+          <t>Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>608900</v>
+        <v>609206</v>
       </c>
       <c r="R188" t="n">
-        <v>7062591</v>
+        <v>7062811</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20468,22 +20468,22 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20498,19 +20498,19 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Martin Bergström</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Martin Bergström</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133687756</v>
+        <v>133686560</v>
       </c>
       <c r="B189" t="n">
         <v>99217</v>
@@ -20545,10 +20545,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>609002</v>
+        <v>608900</v>
       </c>
       <c r="R189" t="n">
-        <v>7062636</v>
+        <v>7062591</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20580,7 +20580,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20590,7 +20590,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20617,7 +20617,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133687890</v>
+        <v>133687756</v>
       </c>
       <c r="B190" t="n">
         <v>99217</v>
@@ -20652,13 +20652,13 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>608992</v>
+        <v>609002</v>
       </c>
       <c r="R190" t="n">
-        <v>7062645</v>
+        <v>7062636</v>
       </c>
       <c r="S190" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -20697,7 +20697,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20712,19 +20712,19 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133687934</v>
+        <v>133687890</v>
       </c>
       <c r="B191" t="n">
         <v>99217</v>
@@ -20759,13 +20759,13 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>608995</v>
+        <v>608992</v>
       </c>
       <c r="R191" t="n">
-        <v>7062669</v>
+        <v>7062645</v>
       </c>
       <c r="S191" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -20794,7 +20794,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -20819,57 +20819,57 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>55947651</v>
+        <v>133687934</v>
       </c>
       <c r="B192" t="n">
-        <v>91909</v>
+        <v>99217</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="P192" t="inlineStr">
         <is>
-          <t>Skalberget, Ång</t>
+          <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>609383</v>
+        <v>608995</v>
       </c>
       <c r="R192" t="n">
-        <v>7063108</v>
+        <v>7062669</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20896,12 +20896,22 @@
       </c>
       <c r="Y192" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>2015-06-23</t>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="AB192" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -20916,23 +20926,19 @@
       <c r="AT192" t="inlineStr"/>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>Mikael Gudrunsson</t>
-        </is>
-      </c>
-      <c r="AY192" t="inlineStr">
-        <is>
-          <t>Naturvärdesinventering Y-län</t>
-        </is>
-      </c>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>55947655</v>
+        <v>55947651</v>
       </c>
       <c r="B193" t="n">
         <v>91909</v>
@@ -20967,10 +20973,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>609176</v>
+        <v>609383</v>
       </c>
       <c r="R193" t="n">
-        <v>7062998</v>
+        <v>7063108</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21033,7 +21039,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>125269871</v>
+        <v>55947655</v>
       </c>
       <c r="B194" t="n">
         <v>91909</v>
@@ -21064,17 +21070,17 @@
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Skalberget, Skalberget, Ång</t>
+          <t>Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>609090</v>
+        <v>609176</v>
       </c>
       <c r="R194" t="n">
-        <v>7063026</v>
+        <v>7062998</v>
       </c>
       <c r="S194" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -21098,12 +21104,12 @@
       </c>
       <c r="Y194" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2015-06-23</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2015-06-23</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21118,19 +21124,23 @@
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mikael Gudrunsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY194" t="inlineStr"/>
+          <t>Mikael Gudrunsson</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>125272232</v>
+        <v>125269871</v>
       </c>
       <c r="B195" t="n">
         <v>91909</v>
@@ -21165,10 +21175,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>609191</v>
+        <v>609090</v>
       </c>
       <c r="R195" t="n">
-        <v>7062977</v>
+        <v>7063026</v>
       </c>
       <c r="S195" t="n">
         <v>15</v>
@@ -21227,7 +21237,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>125272971</v>
+        <v>125272232</v>
       </c>
       <c r="B196" t="n">
         <v>91909</v>
@@ -21262,10 +21272,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>609030</v>
+        <v>609191</v>
       </c>
       <c r="R196" t="n">
-        <v>7062982</v>
+        <v>7062977</v>
       </c>
       <c r="S196" t="n">
         <v>15</v>
@@ -21324,32 +21334,32 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>125269907</v>
+        <v>125272971</v>
       </c>
       <c r="B197" t="n">
-        <v>92281</v>
+        <v>91909</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21359,10 +21369,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>609091</v>
+        <v>609030</v>
       </c>
       <c r="R197" t="n">
-        <v>7063024</v>
+        <v>7062982</v>
       </c>
       <c r="S197" t="n">
         <v>15</v>
@@ -21421,32 +21431,32 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>125272687</v>
+        <v>125269907</v>
       </c>
       <c r="B198" t="n">
-        <v>92632</v>
+        <v>92281</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>3298</v>
+        <v>2062</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21456,10 +21466,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>609150</v>
+        <v>609091</v>
       </c>
       <c r="R198" t="n">
-        <v>7062995</v>
+        <v>7063024</v>
       </c>
       <c r="S198" t="n">
         <v>15</v>
@@ -21518,7 +21528,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>125272751</v>
+        <v>125272687</v>
       </c>
       <c r="B199" t="n">
         <v>92632</v>
@@ -21553,10 +21563,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>609151</v>
+        <v>609150</v>
       </c>
       <c r="R199" t="n">
-        <v>7062994</v>
+        <v>7062995</v>
       </c>
       <c r="S199" t="n">
         <v>15</v>
@@ -21615,32 +21625,32 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119850876</v>
+        <v>125272751</v>
       </c>
       <c r="B200" t="n">
-        <v>79327</v>
+        <v>92632</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -21650,13 +21660,13 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>609066</v>
+        <v>609151</v>
       </c>
       <c r="R200" t="n">
-        <v>7062980</v>
+        <v>7062994</v>
       </c>
       <c r="S200" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -21680,12 +21690,12 @@
       </c>
       <c r="Y200" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -21700,19 +21710,19 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119851104</v>
+        <v>119850876</v>
       </c>
       <c r="B201" t="n">
         <v>79327</v>
@@ -21747,13 +21757,13 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>609085</v>
+        <v>609066</v>
       </c>
       <c r="R201" t="n">
-        <v>7062996</v>
+        <v>7062980</v>
       </c>
       <c r="S201" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -21783,11 +21793,6 @@
       <c r="AA201" t="inlineStr">
         <is>
           <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AC201" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -21814,7 +21819,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>125269804</v>
+        <v>119851104</v>
       </c>
       <c r="B202" t="n">
         <v>79327</v>
@@ -21849,13 +21854,13 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>609090</v>
+        <v>609085</v>
       </c>
       <c r="R202" t="n">
-        <v>7063026</v>
+        <v>7062996</v>
       </c>
       <c r="S202" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21879,12 +21884,17 @@
       </c>
       <c r="Y202" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -21899,19 +21909,19 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>125271814</v>
+        <v>125269804</v>
       </c>
       <c r="B203" t="n">
         <v>79327</v>
@@ -21946,10 +21956,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>609083</v>
+        <v>609090</v>
       </c>
       <c r="R203" t="n">
-        <v>7062960</v>
+        <v>7063026</v>
       </c>
       <c r="S203" t="n">
         <v>15</v>
@@ -22008,49 +22018,48 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>112419133</v>
+        <v>125271814</v>
       </c>
       <c r="B204" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="K204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Kyrkviken, Kyrkviken, Ång</t>
+          <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>609457</v>
+        <v>609083</v>
       </c>
       <c r="R204" t="n">
-        <v>7063014</v>
+        <v>7062960</v>
       </c>
       <c r="S204" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -22074,22 +22083,12 @@
       </c>
       <c r="Y204" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>14:08</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22104,19 +22103,19 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>112419155</v>
+        <v>112419133</v>
       </c>
       <c r="B205" t="n">
         <v>80432</v>
@@ -22152,10 +22151,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>609466</v>
+        <v>609457</v>
       </c>
       <c r="R205" t="n">
-        <v>7063029</v>
+        <v>7063014</v>
       </c>
       <c r="S205" t="n">
         <v>25</v>
@@ -22187,7 +22186,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22197,7 +22196,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22224,7 +22223,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>112419185</v>
+        <v>112419155</v>
       </c>
       <c r="B206" t="n">
         <v>80432</v>
@@ -22260,10 +22259,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>609429</v>
+        <v>609466</v>
       </c>
       <c r="R206" t="n">
-        <v>7063011</v>
+        <v>7063029</v>
       </c>
       <c r="S206" t="n">
         <v>25</v>
@@ -22295,7 +22294,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22305,7 +22304,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22332,7 +22331,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>112421986</v>
+        <v>112419185</v>
       </c>
       <c r="B207" t="n">
         <v>80432</v>
@@ -22368,10 +22367,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>609331</v>
+        <v>609429</v>
       </c>
       <c r="R207" t="n">
-        <v>7062965</v>
+        <v>7063011</v>
       </c>
       <c r="S207" t="n">
         <v>25</v>
@@ -22403,7 +22402,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22413,7 +22412,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22428,19 +22427,19 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119850850</v>
+        <v>112421986</v>
       </c>
       <c r="B208" t="n">
         <v>80432</v>
@@ -22469,19 +22468,20 @@
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="K208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Skalberget, Skalberget, Ång</t>
+          <t>Kyrkviken, Kyrkviken, Ång</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>609076</v>
+        <v>609331</v>
       </c>
       <c r="R208" t="n">
-        <v>7062968</v>
+        <v>7062965</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -22505,12 +22505,22 @@
       </c>
       <c r="Y208" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AB208" t="inlineStr">
+        <is>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -22525,19 +22535,19 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>125269793</v>
+        <v>119850850</v>
       </c>
       <c r="B209" t="n">
         <v>80432</v>
@@ -22572,13 +22582,13 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>609090</v>
+        <v>609076</v>
       </c>
       <c r="R209" t="n">
-        <v>7063026</v>
+        <v>7062968</v>
       </c>
       <c r="S209" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -22602,12 +22612,12 @@
       </c>
       <c r="Y209" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -22622,19 +22632,19 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>125269981</v>
+        <v>125269793</v>
       </c>
       <c r="B210" t="n">
         <v>80432</v>
@@ -22669,10 +22679,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>609081</v>
+        <v>609090</v>
       </c>
       <c r="R210" t="n">
-        <v>7063021</v>
+        <v>7063026</v>
       </c>
       <c r="S210" t="n">
         <v>15</v>
@@ -22731,32 +22741,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>125269977</v>
+        <v>125269981</v>
       </c>
       <c r="B211" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22766,10 +22776,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>609090</v>
+        <v>609081</v>
       </c>
       <c r="R211" t="n">
-        <v>7063013</v>
+        <v>7063021</v>
       </c>
       <c r="S211" t="n">
         <v>15</v>
@@ -22828,54 +22838,48 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>112419310</v>
+        <v>125269977</v>
       </c>
       <c r="B212" t="n">
-        <v>57953</v>
+        <v>80461</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="K212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Kyrkviken, Kläppsjö, Ång</t>
+          <t>Skalberget, Skalberget, Ång</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>609331</v>
+        <v>609090</v>
       </c>
       <c r="R212" t="n">
-        <v>7063001</v>
+        <v>7063013</v>
       </c>
       <c r="S212" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -22899,22 +22903,12 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="Z212" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AB212" t="inlineStr">
-        <is>
-          <t>14:16</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -22929,19 +22923,19 @@
       <c r="AT212" t="inlineStr"/>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>112421961</v>
+        <v>112419310</v>
       </c>
       <c r="B213" t="n">
         <v>57953</v>
@@ -22985,7 +22979,7 @@
         <v>609331</v>
       </c>
       <c r="R213" t="n">
-        <v>7062965</v>
+        <v>7063001</v>
       </c>
       <c r="S213" t="n">
         <v>25</v>
@@ -23017,7 +23011,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -23027,7 +23021,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23054,50 +23048,51 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>112418991</v>
+        <v>112421961</v>
       </c>
       <c r="B214" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr"/>
       <c r="K214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Kyrkviken, Kyrkviken, Ång</t>
+          <t>Kyrkviken, Kläppsjö, Ång</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>609464</v>
+        <v>609331</v>
       </c>
       <c r="R214" t="n">
-        <v>7063099</v>
+        <v>7062965</v>
       </c>
       <c r="S214" t="n">
         <v>25</v>
@@ -23129,7 +23124,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23139,7 +23134,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23154,19 +23149,19 @@
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>112419099</v>
+        <v>112418991</v>
       </c>
       <c r="B215" t="n">
         <v>99118</v>
@@ -23196,7 +23191,7 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -23206,10 +23201,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>609451</v>
+        <v>609464</v>
       </c>
       <c r="R215" t="n">
-        <v>7063031</v>
+        <v>7063099</v>
       </c>
       <c r="S215" t="n">
         <v>25</v>
@@ -23241,7 +23236,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23251,7 +23246,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23278,7 +23273,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>112419523</v>
+        <v>112419099</v>
       </c>
       <c r="B216" t="n">
         <v>99118</v>
@@ -23308,7 +23303,7 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -23318,10 +23313,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>609289</v>
+        <v>609451</v>
       </c>
       <c r="R216" t="n">
-        <v>7062953</v>
+        <v>7063031</v>
       </c>
       <c r="S216" t="n">
         <v>25</v>
@@ -23353,7 +23348,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23363,7 +23358,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23378,19 +23373,19 @@
       <c r="AT216" t="inlineStr"/>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119851185</v>
+        <v>112419523</v>
       </c>
       <c r="B217" t="n">
         <v>99118</v>
@@ -23418,20 +23413,25 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
       <c r="P217" t="inlineStr">
         <is>
-          <t>Skalberget, Skalberget, Ång</t>
+          <t>Kyrkviken, Kyrkviken, Ång</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>609097</v>
+        <v>609289</v>
       </c>
       <c r="R217" t="n">
-        <v>7062964</v>
+        <v>7062953</v>
       </c>
       <c r="S217" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -23455,12 +23455,22 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AB217" t="inlineStr">
+        <is>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -23475,19 +23485,19 @@
       <c r="AT217" t="inlineStr"/>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119851235</v>
+        <v>119851185</v>
       </c>
       <c r="B218" t="n">
         <v>99118</v>
@@ -23522,13 +23532,13 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>609101</v>
+        <v>609097</v>
       </c>
       <c r="R218" t="n">
-        <v>7062955</v>
+        <v>7062964</v>
       </c>
       <c r="S218" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -23552,12 +23562,12 @@
       </c>
       <c r="Y218" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -23584,32 +23594,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>125273101</v>
+        <v>119851235</v>
       </c>
       <c r="B219" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -23619,13 +23629,13 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>609053</v>
+        <v>609101</v>
       </c>
       <c r="R219" t="n">
-        <v>7063023</v>
+        <v>7062955</v>
       </c>
       <c r="S219" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -23649,12 +23659,12 @@
       </c>
       <c r="Y219" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -23669,15 +23679,112 @@
       <c r="AT219" t="inlineStr"/>
       <c r="AW219" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX219" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>125273101</v>
+      </c>
+      <c r="B220" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr"/>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Skalberget, Skalberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>609053</v>
+      </c>
+      <c r="R220" t="n">
+        <v>7063023</v>
+      </c>
+      <c r="S220" t="n">
+        <v>15</v>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y220" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG220" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT220" t="inlineStr"/>
+      <c r="AW220" t="inlineStr">
+        <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AX219" t="inlineStr">
+      <c r="AX220" t="inlineStr">
         <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AY219" t="inlineStr"/>
+      <c r="AY220" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY245"/>
+  <dimension ref="A1:AZ245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125780954</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849708</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849742</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850562</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125270531</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55947651</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1374,6 +1409,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55947655</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1471,6 +1511,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849721</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1568,6 +1613,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849755</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849829</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1762,6 +1817,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849903</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1859,6 +1919,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850220</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1956,6 +2021,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851251</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2053,6 +2123,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125269871</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2150,6 +2225,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125270505</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2247,6 +2327,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271430</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2344,6 +2429,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125272232</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2441,6 +2531,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125272971</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2548,6 +2643,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133684556</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2655,6 +2755,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686107</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2762,6 +2867,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670555</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2869,6 +2979,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670610</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2976,6 +3091,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670742</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3087,6 +3207,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120091070</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3184,6 +3309,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125269907</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3291,6 +3421,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133685643</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3388,6 +3523,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125272687</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3485,6 +3625,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125272751</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3592,6 +3737,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849905</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3699,6 +3849,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133685893</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3796,6 +3951,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271489</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3893,6 +4053,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271533</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4001,6 +4166,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419877</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4103,6 +4273,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849630</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4210,6 +4385,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849724</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4307,6 +4487,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850834</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4404,6 +4589,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850876</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4506,6 +4696,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851104</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4603,6 +4798,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125269804</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4700,6 +4900,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271636</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4797,6 +5002,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271814</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4904,6 +5114,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133684578</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5011,6 +5226,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133684732</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5118,6 +5338,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686288</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5225,6 +5450,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686911</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5332,6 +5562,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133687243</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5439,6 +5674,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688242</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5546,6 +5786,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688336</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5653,6 +5898,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670232</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5760,6 +6010,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670535</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5867,6 +6122,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672682</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5975,6 +6235,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420041</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6082,6 +6347,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686253</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6190,6 +6460,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419133</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6298,6 +6573,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419155</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6406,6 +6686,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419185</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6514,6 +6799,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419555</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6622,6 +6912,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420021</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6735,6 +7030,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420342</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6843,6 +7143,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420514</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6951,6 +7256,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420881</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7059,6 +7369,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112421986</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7160,6 +7475,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849952</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7257,6 +7577,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849971</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7354,6 +7679,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850006</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7451,6 +7781,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850321</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7548,6 +7883,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850384</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7645,6 +7985,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850850</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7752,6 +8097,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850955</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7859,6 +8209,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851290</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7956,6 +8311,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851361</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8063,6 +8423,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851377</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8160,6 +8525,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851421</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8257,6 +8627,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851618</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8354,6 +8729,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851664</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8451,6 +8831,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851684</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8548,6 +8933,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851732</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8645,6 +9035,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851802</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8742,6 +9137,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851861</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8839,6 +9239,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851878</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8936,6 +9341,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851928</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9033,6 +9443,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851950</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9130,6 +9545,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851973</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9227,6 +9647,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851993</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9324,6 +9749,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852025</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9421,6 +9851,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119852068</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9518,6 +9953,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125269793</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9615,6 +10055,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125269981</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9712,6 +10157,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125270100</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9809,6 +10259,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125270406</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9910,6 +10365,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125307927</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10017,6 +10477,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133685620</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10124,6 +10589,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133685656</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10231,6 +10701,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686056</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10338,6 +10813,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688184</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10445,6 +10925,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688254</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10552,6 +11037,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688330</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10659,6 +11149,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688381</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10766,6 +11261,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688474</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10873,6 +11373,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688563</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10980,6 +11485,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688622</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11087,6 +11597,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688785</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11194,6 +11709,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688914</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11291,6 +11811,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849973</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11388,6 +11913,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125269977</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11485,6 +12015,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271565</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11582,6 +12117,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271733</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11683,6 +12223,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125307928</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11780,6 +12325,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851428</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11877,6 +12427,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851641</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11974,6 +12529,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125270136</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12085,6 +12645,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132197278</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12197,6 +12762,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686930</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12310,6 +12880,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419310</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12423,6 +12998,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419640</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12536,6 +13116,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419724</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12649,6 +13234,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420008</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12762,6 +13352,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420060</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12875,6 +13470,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420223</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12988,6 +13588,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420901</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13101,6 +13706,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112421050</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13214,6 +13824,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112421961</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13326,6 +13941,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849658</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13438,6 +14058,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849717</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13550,6 +14175,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850459</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13662,6 +14292,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850926</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13774,6 +14409,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851160</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13886,6 +14526,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851274</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13998,6 +14643,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851413</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14105,6 +14755,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271349</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14215,6 +14870,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125307925</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14326,6 +14986,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132194001</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14452,6 +15117,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133684263</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14569,6 +15239,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133684699</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14686,6 +15361,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133685133</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14803,6 +15483,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133685279</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14920,6 +15605,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686454</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15037,6 +15727,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686474</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15154,6 +15849,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686575</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15271,6 +15971,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133687183</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15388,6 +16093,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688845</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15505,6 +16215,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133689109</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15622,6 +16337,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134671144</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15739,6 +16459,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134671312</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15856,6 +16581,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134671893</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15973,6 +16703,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672707</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16075,6 +16810,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851695</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16191,6 +16931,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670506</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16303,6 +17048,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133687576</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16410,6 +17160,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672396</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16522,6 +17277,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112418991</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16634,6 +17394,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419099</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16746,6 +17511,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419498</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16858,6 +17628,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419523</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16970,6 +17745,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419590</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17078,6 +17858,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419624</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17186,6 +17971,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419749</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17298,6 +18088,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419760</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17410,6 +18205,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419769</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17522,6 +18322,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419790</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17630,6 +18435,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419808</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17742,6 +18552,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112419869</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17850,6 +18665,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420038</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17958,6 +18778,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420139</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18066,6 +18891,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420271</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18174,6 +19004,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420373</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18282,6 +19117,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420400</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18394,6 +19234,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420438</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18502,6 +19347,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420522</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18610,6 +19460,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420547</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18722,6 +19577,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420597</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18830,6 +19690,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420639</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18938,6 +19803,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420648</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19046,6 +19916,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420671</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19154,6 +20029,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112420929</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19262,6 +20142,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112421093</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19370,6 +20255,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112421181</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19478,6 +20368,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112421234</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19586,6 +20481,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112421776</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19694,6 +20594,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112421825</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19805,6 +20710,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849740</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19916,6 +20826,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849858</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20027,6 +20942,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849966</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20138,6 +21058,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850096</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20235,6 +21160,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850115</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20332,6 +21262,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850188</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20429,6 +21364,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850411</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20526,6 +21466,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850436</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20623,6 +21568,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850519</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20720,6 +21670,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850568</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20817,6 +21772,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850656</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20928,6 +21888,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850720</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21030,6 +21995,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850752</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21141,6 +22111,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119850782</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21252,6 +22227,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851047</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21349,6 +22329,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851185</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21446,6 +22431,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851235</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21557,6 +22547,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851306</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21654,6 +22649,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851329</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21751,6 +22751,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119851502</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21857,6 +22862,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122742574</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21963,6 +22973,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122742575</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22069,6 +23084,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122742576</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22175,6 +23195,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122746839</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22276,6 +23301,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271158</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22377,6 +23407,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271258</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22478,6 +23513,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271462</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22579,6 +23619,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271702</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22680,6 +23725,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271717</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22781,6 +23831,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125271754</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22892,6 +23947,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133683883</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23008,6 +24068,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133684282</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23124,6 +24189,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133684689</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23235,6 +24305,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133684740</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23351,6 +24426,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686122</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23462,6 +24542,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686301</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23578,6 +24663,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686482</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23694,6 +24784,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686590</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23805,6 +24900,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686596</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -23921,6 +25021,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686675</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24032,6 +25137,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133687436</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24143,6 +25253,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133687570</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24259,6 +25374,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133687759</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24375,6 +25495,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688188</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24486,6 +25611,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133688603</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24593,6 +25723,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134530697</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24704,6 +25839,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670716</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24815,6 +25955,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670769</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -24926,6 +26071,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134671965</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25037,6 +26187,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672985</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25148,6 +26303,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134673367</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25264,6 +26424,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135105604</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25371,6 +26536,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672099</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25478,6 +26648,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672528</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25575,6 +26750,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125273101</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25682,6 +26862,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672961</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25789,6 +26974,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133686560</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25896,6 +27086,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133687756</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26003,6 +27198,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133687890</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26110,6 +27310,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133687934</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26217,6 +27422,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134670648</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26324,6 +27534,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672054</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26431,6 +27646,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672263</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26538,8 +27758,259 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134672772</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -26314,7 +26314,7 @@
         <v>135105604</v>
       </c>
       <c r="B233" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>

--- a/artfynd/A 57942-2021 artfynd.xlsx
+++ b/artfynd/A 57942-2021 artfynd.xlsx
@@ -26314,7 +26314,7 @@
         <v>135105604</v>
       </c>
       <c r="B233" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
